--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -586,22 +586,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.216</v>
+        <v>1.018</v>
       </c>
       <c r="H2" t="n">
-        <v>1.382</v>
+        <v>1.172</v>
       </c>
       <c r="I2" t="n">
-        <v>1.66</v>
+        <v>1.413</v>
       </c>
       <c r="J2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="K2" t="n">
-        <v>1.222</v>
+        <v>1.023</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.438</v>
+        <v>-0.389</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -614,29 +614,29 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>7218</v>
+        <v>7220</v>
       </c>
       <c r="V2" t="n">
         <v>0.727</v>
@@ -648,7 +648,7 @@
         <v>0.677</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.797</v>
+        <v>2.799</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -687,22 +687,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3.475</v>
+        <v>3.515</v>
       </c>
       <c r="H3" t="n">
-        <v>3.566</v>
+        <v>3.605</v>
       </c>
       <c r="I3" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="K3" t="n">
-        <v>3.478</v>
+        <v>3.515</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.122</v>
+        <v>-0.125</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -715,29 +715,29 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>14254</v>
+        <v>14256</v>
       </c>
       <c r="V3" t="n">
         <v>0.505</v>
@@ -749,7 +749,7 @@
         <v>0.503</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.509</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.752</v>
+        <v>3.184</v>
       </c>
       <c r="H4" t="n">
-        <v>2.999</v>
+        <v>3.43</v>
       </c>
       <c r="I4" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="J4" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="K4" t="n">
-        <v>2.824</v>
+        <v>3.255</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.356</v>
+        <v>-0.358</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -816,29 +816,29 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>13858</v>
+        <v>13860</v>
       </c>
       <c r="V4" t="n">
         <v>0.43</v>
@@ -889,22 +889,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5.465</v>
+        <v>5.618</v>
       </c>
       <c r="H5" t="n">
-        <v>5.691</v>
+        <v>5.844</v>
       </c>
       <c r="I5" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="K5" t="n">
-        <v>5.472</v>
+        <v>5.628</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.428</v>
+        <v>-0.427</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -917,29 +917,29 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>9861</v>
+        <v>9863</v>
       </c>
       <c r="V5" t="n">
         <v>0.041</v>
@@ -990,22 +990,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.088</v>
+        <v>1.42</v>
       </c>
       <c r="H6" t="n">
-        <v>8.250999999999999</v>
+        <v>8.285</v>
       </c>
       <c r="I6" t="n">
-        <v>105.891</v>
+        <v>106.202</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="K6" t="n">
-        <v>43.735</v>
+        <v>42.288</v>
       </c>
       <c r="L6" t="n">
-        <v>39.785</v>
+        <v>38.248</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1018,21 +1018,21 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>10052</v>
+        <v>10053</v>
       </c>
       <c r="V6" t="n">
         <v>0.137</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.723</v>
+        <v>-0.722</v>
       </c>
       <c r="X6" t="n">
         <v>0.137</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.275</v>
+        <v>36.287</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1190,22 +1190,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="H8" t="n">
-        <v>6.952</v>
+        <v>6.732</v>
       </c>
       <c r="I8" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="J8" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="K8" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="L8" t="n">
-        <v>0.077</v>
+        <v>0.099</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1218,29 +1218,29 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>6510</v>
+        <v>6513</v>
       </c>
       <c r="V8" t="n">
         <v>0.824</v>
@@ -1252,7 +1252,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.147</v>
+        <v>2.146</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4.062</v>
+        <v>3.527</v>
       </c>
       <c r="H9" t="n">
-        <v>4.315</v>
+        <v>3.795</v>
       </c>
       <c r="I9" t="n">
-        <v>4.735</v>
+        <v>4.251</v>
       </c>
       <c r="J9" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="K9" t="n">
-        <v>4.734</v>
+        <v>4.246</v>
       </c>
       <c r="L9" t="n">
-        <v>0.264</v>
+        <v>0.306</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1319,21 +1319,21 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>4176</v>
+        <v>4178</v>
       </c>
       <c r="V9" t="n">
         <v>0.834</v>
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="H20" t="n">
-        <v>6.542</v>
+        <v>6.582</v>
       </c>
       <c r="I20" t="n">
-        <v>6.841</v>
+        <v>6.851</v>
       </c>
       <c r="J20" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="K20" t="n">
-        <v>6.388</v>
+        <v>6.445</v>
       </c>
       <c r="L20" t="n">
-        <v>0.349</v>
+        <v>0.336</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2429,38 +2429,38 @@
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="S20" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>2722</v>
+        <v>2743</v>
       </c>
       <c r="V20" t="n">
-        <v>0.866</v>
+        <v>0.865</v>
       </c>
       <c r="W20" t="n">
-        <v>0.722</v>
+        <v>0.719</v>
       </c>
       <c r="X20" t="n">
-        <v>0.86</v>
+        <v>0.858</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.747</v>
+        <v>1.751</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2751,58 +2751,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="F2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.413</v>
       </c>
       <c r="H2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="I2" t="n">
-        <v>1.66</v>
+        <v>1.413</v>
       </c>
       <c r="J2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1.66</v>
+        <v>1.413</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.413</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="S2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -2810,25 +2810,25 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2850,58 +2850,58 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="F3" t="n">
-        <v>1.552</v>
+        <v>1.355</v>
       </c>
       <c r="G3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="H3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="I3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="J3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="K3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.659000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="M3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="N3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="O3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="P3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="R3" t="n">
-        <v>1.552</v>
+        <v>1.355</v>
       </c>
       <c r="S3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="T3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="U3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="V3" t="n">
-        <v>8.662000000000001</v>
+        <v>8.659000000000001</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -2909,25 +2909,25 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -2949,84 +2949,84 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.512</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.512</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8.512</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8.512</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7.304</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
         <v>1.412</v>
       </c>
-      <c r="F4" t="n">
-        <v>1.407</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.414</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8.522</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8.518000000000001</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8.523999999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>8.522</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8.523999999999999</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.414</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.407</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8.523999999999999</v>
-      </c>
-      <c r="T4" t="n">
-        <v>8.523999999999999</v>
-      </c>
-      <c r="U4" t="n">
-        <v>8.523</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.518000000000001</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>-7.11</v>
-      </c>
-      <c r="Y4" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3048,58 +3048,58 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.359</v>
+        <v>1.136</v>
       </c>
       <c r="F5" t="n">
-        <v>1.342</v>
+        <v>1.125</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.147</v>
       </c>
       <c r="H5" t="n">
-        <v>1.352</v>
+        <v>1.126</v>
       </c>
       <c r="I5" t="n">
-        <v>1.37</v>
+        <v>1.147</v>
       </c>
       <c r="J5" t="n">
-        <v>8.470000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="K5" t="n">
-        <v>8.452</v>
+        <v>8.429</v>
       </c>
       <c r="L5" t="n">
-        <v>8.481</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>8.462</v>
+        <v>8.429</v>
       </c>
       <c r="N5" t="n">
-        <v>8.481</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.147</v>
       </c>
       <c r="P5" t="n">
-        <v>1.37</v>
+        <v>1.147</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.355</v>
+        <v>1.126</v>
       </c>
       <c r="R5" t="n">
-        <v>1.342</v>
+        <v>1.125</v>
       </c>
       <c r="S5" t="n">
-        <v>8.481</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>8.481</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>8.465</v>
+        <v>8.429</v>
       </c>
       <c r="V5" t="n">
-        <v>8.452</v>
+        <v>8.429</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -3107,25 +3107,25 @@
         </is>
       </c>
       <c r="X5" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3147,58 +3147,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.243</v>
+        <v>1.045</v>
       </c>
       <c r="F6" t="n">
-        <v>1.239</v>
+        <v>1.043</v>
       </c>
       <c r="G6" t="n">
-        <v>1.246</v>
+        <v>1.047</v>
       </c>
       <c r="H6" t="n">
-        <v>1.241</v>
+        <v>1.044</v>
       </c>
       <c r="I6" t="n">
-        <v>1.245</v>
+        <v>1.046</v>
       </c>
       <c r="J6" t="n">
-        <v>8.353999999999999</v>
+        <v>8.349</v>
       </c>
       <c r="K6" t="n">
+        <v>8.347</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.351000000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="N6" t="n">
         <v>8.35</v>
       </c>
-      <c r="L6" t="n">
-        <v>8.356999999999999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8.352</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8.356</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.245</v>
+        <v>1.046</v>
       </c>
       <c r="P6" t="n">
-        <v>1.246</v>
+        <v>1.047</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.242</v>
+        <v>1.044</v>
       </c>
       <c r="R6" t="n">
-        <v>1.239</v>
+        <v>1.043</v>
       </c>
       <c r="S6" t="n">
-        <v>8.355</v>
+        <v>8.35</v>
       </c>
       <c r="T6" t="n">
-        <v>8.356999999999999</v>
+        <v>8.351000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>8.352</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>8.35</v>
+        <v>8.347</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -3206,25 +3206,25 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3246,58 +3246,58 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.227</v>
+        <v>1.026</v>
       </c>
       <c r="F7" t="n">
-        <v>1.223</v>
+        <v>1.023</v>
       </c>
       <c r="G7" t="n">
-        <v>1.235</v>
+        <v>1.031</v>
       </c>
       <c r="H7" t="n">
-        <v>1.223</v>
+        <v>1.024</v>
       </c>
       <c r="I7" t="n">
-        <v>1.228</v>
+        <v>1.027</v>
       </c>
       <c r="J7" t="n">
-        <v>8.337</v>
+        <v>8.329000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>8.333</v>
+        <v>8.327</v>
       </c>
       <c r="L7" t="n">
-        <v>8.345000000000001</v>
+        <v>8.334</v>
       </c>
       <c r="M7" t="n">
+        <v>8.327</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8.329000000000001</v>
+      </c>
+      <c r="T7" t="n">
         <v>8.334</v>
       </c>
-      <c r="N7" t="n">
-        <v>8.337999999999999</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8.335000000000001</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8.345000000000001</v>
-      </c>
       <c r="U7" t="n">
-        <v>8.333</v>
+        <v>8.327</v>
       </c>
       <c r="V7" t="n">
-        <v>8.334</v>
+        <v>8.327</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -3305,25 +3305,25 @@
         </is>
       </c>
       <c r="X7" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3345,58 +3345,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.222</v>
+        <v>1.023</v>
       </c>
       <c r="F8" t="n">
-        <v>1.216</v>
+        <v>1.018</v>
       </c>
       <c r="G8" t="n">
-        <v>1.228</v>
+        <v>1.027</v>
       </c>
       <c r="H8" t="n">
-        <v>1.22</v>
+        <v>1.021</v>
       </c>
       <c r="I8" t="n">
-        <v>1.225</v>
+        <v>1.025</v>
       </c>
       <c r="J8" t="n">
-        <v>8.332000000000001</v>
+        <v>8.326000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>8.326000000000001</v>
+        <v>8.321999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>8.337999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="M8" t="n">
+        <v>8.324</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8.327999999999999</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.324999999999999</v>
+      </c>
+      <c r="T8" t="n">
         <v>8.33</v>
       </c>
-      <c r="N8" t="n">
-        <v>8.335000000000001</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.221</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.228</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.216</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.224</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8.331</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8.337999999999999</v>
-      </c>
       <c r="U8" t="n">
-        <v>8.326000000000001</v>
+        <v>8.321999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>8.334</v>
+        <v>8.327999999999999</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3444,58 +3444,58 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="J9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="K9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="L9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="M9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="N9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="S9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="T9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="U9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="V9" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -3503,25 +3503,25 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3543,58 +3543,58 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="F10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="G10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="H10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="I10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="J10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="K10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="L10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="M10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="N10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="O10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="P10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="R10" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="S10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="T10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="U10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="V10" t="n">
-        <v>5.842</v>
+        <v>5.84</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -3602,25 +3602,25 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3642,58 +3642,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="F11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="G11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="H11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="I11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="J11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="K11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="L11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="M11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="N11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="O11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="P11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="R11" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="S11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="T11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="U11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="V11" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -3701,25 +3701,25 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3741,58 +3741,58 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="F12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="G12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="H12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="I12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="J12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="K12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="L12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="M12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="N12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="O12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="P12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="R12" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="S12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="T12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="U12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="V12" t="n">
-        <v>5.808</v>
+        <v>5.807</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -3800,25 +3800,25 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3840,19 +3840,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.56</v>
+        <v>3.601</v>
       </c>
       <c r="F13" t="n">
-        <v>3.56</v>
+        <v>3.601</v>
       </c>
       <c r="G13" t="n">
-        <v>3.561</v>
+        <v>3.602</v>
       </c>
       <c r="H13" t="n">
-        <v>3.56</v>
+        <v>3.601</v>
       </c>
       <c r="I13" t="n">
-        <v>3.561</v>
+        <v>3.601</v>
       </c>
       <c r="J13" t="n">
         <v>5.786</v>
@@ -3861,7 +3861,7 @@
         <v>5.786</v>
       </c>
       <c r="L13" t="n">
-        <v>5.787</v>
+        <v>5.786</v>
       </c>
       <c r="M13" t="n">
         <v>5.786</v>
@@ -3870,16 +3870,16 @@
         <v>5.786</v>
       </c>
       <c r="O13" t="n">
-        <v>3.56</v>
+        <v>3.601</v>
       </c>
       <c r="P13" t="n">
-        <v>3.561</v>
+        <v>3.601</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.561</v>
+        <v>3.602</v>
       </c>
       <c r="R13" t="n">
-        <v>3.56</v>
+        <v>3.601</v>
       </c>
       <c r="S13" t="n">
         <v>5.786</v>
@@ -3888,7 +3888,7 @@
         <v>5.786</v>
       </c>
       <c r="U13" t="n">
-        <v>5.787</v>
+        <v>5.786</v>
       </c>
       <c r="V13" t="n">
         <v>5.786</v>
@@ -3899,25 +3899,25 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -3939,58 +3939,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.528</v>
+        <v>3.567</v>
       </c>
       <c r="F14" t="n">
-        <v>3.527</v>
+        <v>3.566</v>
       </c>
       <c r="G14" t="n">
-        <v>3.528</v>
+        <v>3.567</v>
       </c>
       <c r="H14" t="n">
-        <v>3.528</v>
+        <v>3.566</v>
       </c>
       <c r="I14" t="n">
-        <v>3.528</v>
+        <v>3.567</v>
       </c>
       <c r="J14" t="n">
-        <v>5.754</v>
+        <v>5.751</v>
       </c>
       <c r="K14" t="n">
-        <v>5.753</v>
+        <v>5.751</v>
       </c>
       <c r="L14" t="n">
-        <v>5.754</v>
+        <v>5.751</v>
       </c>
       <c r="M14" t="n">
-        <v>5.753</v>
+        <v>5.751</v>
       </c>
       <c r="N14" t="n">
-        <v>5.754</v>
+        <v>5.751</v>
       </c>
       <c r="O14" t="n">
-        <v>3.528</v>
+        <v>3.566</v>
       </c>
       <c r="P14" t="n">
-        <v>3.528</v>
+        <v>3.567</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.528</v>
+        <v>3.567</v>
       </c>
       <c r="R14" t="n">
-        <v>3.527</v>
+        <v>3.566</v>
       </c>
       <c r="S14" t="n">
-        <v>5.754</v>
+        <v>5.751</v>
       </c>
       <c r="T14" t="n">
-        <v>5.754</v>
+        <v>5.751</v>
       </c>
       <c r="U14" t="n">
-        <v>5.754</v>
+        <v>5.751</v>
       </c>
       <c r="V14" t="n">
-        <v>5.753</v>
+        <v>5.751</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -3998,25 +3998,25 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4038,58 +4038,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.478</v>
+        <v>3.515</v>
       </c>
       <c r="F15" t="n">
-        <v>3.475</v>
+        <v>3.515</v>
       </c>
       <c r="G15" t="n">
-        <v>3.48</v>
+        <v>3.516</v>
       </c>
       <c r="H15" t="n">
-        <v>3.477</v>
+        <v>3.515</v>
       </c>
       <c r="I15" t="n">
-        <v>3.479</v>
+        <v>3.516</v>
       </c>
       <c r="J15" t="n">
-        <v>5.704</v>
+        <v>5.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.701</v>
+        <v>5.699</v>
       </c>
       <c r="L15" t="n">
-        <v>5.706</v>
+        <v>5.7</v>
       </c>
       <c r="M15" t="n">
-        <v>5.703</v>
+        <v>5.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.705</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.478</v>
+        <v>3.515</v>
       </c>
       <c r="P15" t="n">
-        <v>3.479</v>
+        <v>3.515</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>3.516</v>
       </c>
       <c r="R15" t="n">
-        <v>3.475</v>
+        <v>3.515</v>
       </c>
       <c r="S15" t="n">
-        <v>5.704</v>
+        <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>5.704</v>
+        <v>5.7</v>
       </c>
       <c r="U15" t="n">
-        <v>5.706</v>
+        <v>5.7</v>
       </c>
       <c r="V15" t="n">
-        <v>5.701</v>
+        <v>5.699</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -4097,25 +4097,25 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4137,58 +4137,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="F16" t="n">
-        <v>3.18</v>
+        <v>3.612</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="H16" t="n">
-        <v>3.18</v>
+        <v>3.612</v>
       </c>
       <c r="I16" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="J16" t="n">
-        <v>4.979</v>
+        <v>4.978</v>
       </c>
       <c r="K16" t="n">
+        <v>4.977</v>
+      </c>
+      <c r="L16" t="n">
         <v>4.978</v>
       </c>
-      <c r="L16" t="n">
-        <v>4.979</v>
-      </c>
       <c r="M16" t="n">
-        <v>4.979</v>
+        <v>4.977</v>
       </c>
       <c r="N16" t="n">
-        <v>4.979</v>
+        <v>4.978</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="P16" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>3.612</v>
       </c>
       <c r="R16" t="n">
-        <v>3.18</v>
+        <v>3.612</v>
       </c>
       <c r="S16" t="n">
-        <v>4.979</v>
+        <v>4.978</v>
       </c>
       <c r="T16" t="n">
-        <v>4.979</v>
+        <v>4.978</v>
       </c>
       <c r="U16" t="n">
-        <v>4.979</v>
+        <v>4.977</v>
       </c>
       <c r="V16" t="n">
-        <v>4.978</v>
+        <v>4.977</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -4196,25 +4196,25 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4236,58 +4236,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.133</v>
+        <v>3.564</v>
       </c>
       <c r="F17" t="n">
-        <v>3.129</v>
+        <v>3.561</v>
       </c>
       <c r="G17" t="n">
-        <v>3.138</v>
+        <v>3.567</v>
       </c>
       <c r="H17" t="n">
-        <v>3.131</v>
+        <v>3.562</v>
       </c>
       <c r="I17" t="n">
-        <v>3.135</v>
+        <v>3.565</v>
       </c>
       <c r="J17" t="n">
+        <v>4.929</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="L17" t="n">
         <v>4.932</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>4.928</v>
       </c>
-      <c r="L17" t="n">
-        <v>4.937</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>4.93</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.934</v>
-      </c>
       <c r="O17" t="n">
-        <v>3.134</v>
+        <v>3.564</v>
       </c>
       <c r="P17" t="n">
-        <v>3.138</v>
+        <v>3.567</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.132</v>
+        <v>3.563</v>
       </c>
       <c r="R17" t="n">
-        <v>3.129</v>
+        <v>3.561</v>
       </c>
       <c r="S17" t="n">
-        <v>4.933</v>
+        <v>4.929</v>
       </c>
       <c r="T17" t="n">
-        <v>4.937</v>
+        <v>4.932</v>
       </c>
       <c r="U17" t="n">
-        <v>4.931</v>
+        <v>4.928</v>
       </c>
       <c r="V17" t="n">
-        <v>4.928</v>
+        <v>4.926</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -4295,25 +4295,25 @@
         </is>
       </c>
       <c r="X17" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4335,58 +4335,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.053</v>
+        <v>3.484</v>
       </c>
       <c r="F18" t="n">
-        <v>3.043</v>
+        <v>3.474</v>
       </c>
       <c r="G18" t="n">
-        <v>3.063</v>
+        <v>3.495</v>
       </c>
       <c r="H18" t="n">
-        <v>3.047</v>
+        <v>3.476</v>
       </c>
       <c r="I18" t="n">
-        <v>3.061</v>
+        <v>3.491</v>
       </c>
       <c r="J18" t="n">
-        <v>4.852</v>
+        <v>4.849</v>
       </c>
       <c r="K18" t="n">
-        <v>4.842</v>
+        <v>4.839</v>
       </c>
       <c r="L18" t="n">
-        <v>4.862</v>
+        <v>4.86</v>
       </c>
       <c r="M18" t="n">
-        <v>4.845</v>
+        <v>4.841</v>
       </c>
       <c r="N18" t="n">
-        <v>4.859</v>
+        <v>4.856</v>
       </c>
       <c r="O18" t="n">
-        <v>3.06</v>
+        <v>3.489</v>
       </c>
       <c r="P18" t="n">
-        <v>3.063</v>
+        <v>3.495</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.048</v>
+        <v>3.476</v>
       </c>
       <c r="R18" t="n">
-        <v>3.043</v>
+        <v>3.474</v>
       </c>
       <c r="S18" t="n">
-        <v>4.858</v>
+        <v>4.854</v>
       </c>
       <c r="T18" t="n">
-        <v>4.862</v>
+        <v>4.86</v>
       </c>
       <c r="U18" t="n">
-        <v>4.847</v>
+        <v>4.841</v>
       </c>
       <c r="V18" t="n">
-        <v>4.842</v>
+        <v>4.839</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -4394,25 +4394,25 @@
         </is>
       </c>
       <c r="X18" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4434,58 +4434,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.998</v>
+        <v>3.427</v>
       </c>
       <c r="F19" t="n">
-        <v>2.965</v>
+        <v>3.395</v>
       </c>
       <c r="G19" t="n">
-        <v>3.024</v>
+        <v>3.454</v>
       </c>
       <c r="H19" t="n">
-        <v>2.987</v>
+        <v>3.418</v>
       </c>
       <c r="I19" t="n">
-        <v>3.011</v>
+        <v>3.44</v>
       </c>
       <c r="J19" t="n">
-        <v>4.796</v>
+        <v>4.792</v>
       </c>
       <c r="K19" t="n">
-        <v>4.764</v>
+        <v>4.76</v>
       </c>
       <c r="L19" t="n">
-        <v>4.823</v>
+        <v>4.819</v>
       </c>
       <c r="M19" t="n">
-        <v>4.786</v>
+        <v>4.783</v>
       </c>
       <c r="N19" t="n">
-        <v>4.81</v>
+        <v>4.805</v>
       </c>
       <c r="O19" t="n">
-        <v>3.007</v>
+        <v>3.435</v>
       </c>
       <c r="P19" t="n">
-        <v>3.024</v>
+        <v>3.454</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.994</v>
+        <v>3.425</v>
       </c>
       <c r="R19" t="n">
-        <v>2.965</v>
+        <v>3.395</v>
       </c>
       <c r="S19" t="n">
-        <v>4.806</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>4.823</v>
+        <v>4.819</v>
       </c>
       <c r="U19" t="n">
-        <v>4.793</v>
+        <v>4.79</v>
       </c>
       <c r="V19" t="n">
-        <v>4.764</v>
+        <v>4.76</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -4493,25 +4493,25 @@
         </is>
       </c>
       <c r="X19" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4533,58 +4533,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.935</v>
+        <v>3.365</v>
       </c>
       <c r="F20" t="n">
-        <v>2.891</v>
+        <v>3.317</v>
       </c>
       <c r="G20" t="n">
-        <v>2.965</v>
+        <v>3.395</v>
       </c>
       <c r="H20" t="n">
-        <v>2.929</v>
+        <v>3.359</v>
       </c>
       <c r="I20" t="n">
-        <v>2.948</v>
+        <v>3.379</v>
       </c>
       <c r="J20" t="n">
-        <v>4.734</v>
+        <v>4.73</v>
       </c>
       <c r="K20" t="n">
-        <v>4.69</v>
+        <v>4.682</v>
       </c>
       <c r="L20" t="n">
-        <v>4.764</v>
+        <v>4.761</v>
       </c>
       <c r="M20" t="n">
-        <v>4.727</v>
+        <v>4.724</v>
       </c>
       <c r="N20" t="n">
-        <v>4.747</v>
+        <v>4.745</v>
       </c>
       <c r="O20" t="n">
-        <v>2.941</v>
+        <v>3.373</v>
       </c>
       <c r="P20" t="n">
-        <v>2.965</v>
+        <v>3.395</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.943</v>
+        <v>3.374</v>
       </c>
       <c r="R20" t="n">
-        <v>2.891</v>
+        <v>3.317</v>
       </c>
       <c r="S20" t="n">
-        <v>4.74</v>
+        <v>4.738</v>
       </c>
       <c r="T20" t="n">
-        <v>4.764</v>
+        <v>4.761</v>
       </c>
       <c r="U20" t="n">
-        <v>4.741</v>
+        <v>4.739</v>
       </c>
       <c r="V20" t="n">
-        <v>4.69</v>
+        <v>4.682</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -4592,25 +4592,25 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4632,58 +4632,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.871</v>
+        <v>3.301</v>
       </c>
       <c r="F21" t="n">
-        <v>2.795</v>
+        <v>3.223</v>
       </c>
       <c r="G21" t="n">
-        <v>2.919</v>
+        <v>3.348</v>
       </c>
       <c r="H21" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="I21" t="n">
-        <v>2.907</v>
+        <v>3.338</v>
       </c>
       <c r="J21" t="n">
-        <v>4.67</v>
+        <v>4.666</v>
       </c>
       <c r="K21" t="n">
-        <v>4.594</v>
+        <v>4.588</v>
       </c>
       <c r="L21" t="n">
-        <v>4.718</v>
+        <v>4.713</v>
       </c>
       <c r="M21" t="n">
-        <v>4.649</v>
+        <v>4.645</v>
       </c>
       <c r="N21" t="n">
-        <v>4.705</v>
+        <v>4.703</v>
       </c>
       <c r="O21" t="n">
-        <v>2.868</v>
+        <v>3.299</v>
       </c>
       <c r="P21" t="n">
-        <v>2.919</v>
+        <v>3.348</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.902</v>
+        <v>3.335</v>
       </c>
       <c r="R21" t="n">
-        <v>2.795</v>
+        <v>3.223</v>
       </c>
       <c r="S21" t="n">
-        <v>4.667</v>
+        <v>4.664</v>
       </c>
       <c r="T21" t="n">
-        <v>4.718</v>
+        <v>4.713</v>
       </c>
       <c r="U21" t="n">
-        <v>4.701</v>
+        <v>4.7</v>
       </c>
       <c r="V21" t="n">
-        <v>4.594</v>
+        <v>4.588</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -4691,25 +4691,25 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4731,58 +4731,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.824</v>
+        <v>3.255</v>
       </c>
       <c r="F22" t="n">
-        <v>2.752</v>
+        <v>3.184</v>
       </c>
       <c r="G22" t="n">
-        <v>2.901</v>
+        <v>3.334</v>
       </c>
       <c r="H22" t="n">
-        <v>2.773</v>
+        <v>3.204</v>
       </c>
       <c r="I22" t="n">
-        <v>2.872</v>
+        <v>3.303</v>
       </c>
       <c r="J22" t="n">
-        <v>4.623</v>
+        <v>4.621</v>
       </c>
       <c r="K22" t="n">
-        <v>4.551</v>
+        <v>4.549</v>
       </c>
       <c r="L22" t="n">
-        <v>4.7</v>
+        <v>4.699</v>
       </c>
       <c r="M22" t="n">
-        <v>4.572</v>
+        <v>4.569</v>
       </c>
       <c r="N22" t="n">
-        <v>4.67</v>
+        <v>4.668</v>
       </c>
       <c r="O22" t="n">
-        <v>2.78</v>
+        <v>3.211</v>
       </c>
       <c r="P22" t="n">
-        <v>2.862</v>
+        <v>3.293</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.901</v>
+        <v>3.334</v>
       </c>
       <c r="R22" t="n">
-        <v>2.752</v>
+        <v>3.184</v>
       </c>
       <c r="S22" t="n">
-        <v>4.579</v>
+        <v>4.576</v>
       </c>
       <c r="T22" t="n">
-        <v>4.661</v>
+        <v>4.658</v>
       </c>
       <c r="U22" t="n">
-        <v>4.7</v>
+        <v>4.699</v>
       </c>
       <c r="V22" t="n">
-        <v>4.551</v>
+        <v>4.549</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4790,25 +4790,25 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -4830,58 +4830,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="F23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="H23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="J23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="K23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="L23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="M23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="N23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="O23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="P23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="R23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="S23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="T23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="U23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="V23" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4889,25 +4889,25 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4929,58 +4929,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="F24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="G24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="H24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="I24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="J24" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="K24" t="n">
-        <v>11.66</v>
+        <v>11.647</v>
       </c>
       <c r="L24" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="M24" t="n">
-        <v>11.66</v>
+        <v>11.647</v>
       </c>
       <c r="N24" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="O24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="P24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="R24" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="S24" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="T24" t="n">
-        <v>11.66</v>
+        <v>11.647</v>
       </c>
       <c r="U24" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="V24" t="n">
-        <v>11.66</v>
+        <v>11.647</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4988,25 +4988,25 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5028,58 +5028,58 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.807</v>
+        <v>5.958</v>
       </c>
       <c r="F25" t="n">
-        <v>5.807</v>
+        <v>5.957</v>
       </c>
       <c r="G25" t="n">
-        <v>5.807</v>
+        <v>5.958</v>
       </c>
       <c r="H25" t="n">
-        <v>5.807</v>
+        <v>5.957</v>
       </c>
       <c r="I25" t="n">
-        <v>5.807</v>
+        <v>5.958</v>
       </c>
       <c r="J25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="K25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="L25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="M25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="N25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="O25" t="n">
-        <v>5.807</v>
+        <v>5.958</v>
       </c>
       <c r="P25" t="n">
-        <v>5.807</v>
+        <v>5.957</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.807</v>
+        <v>5.958</v>
       </c>
       <c r="R25" t="n">
-        <v>5.807</v>
+        <v>5.957</v>
       </c>
       <c r="S25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="T25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="U25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="V25" t="n">
-        <v>11.596</v>
+        <v>11.581</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5127,58 +5127,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="F26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="G26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="H26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="I26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="J26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="K26" t="n">
-        <v>11.509</v>
+        <v>11.492</v>
       </c>
       <c r="L26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="M26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="N26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="O26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="P26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="R26" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="S26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="T26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="U26" t="n">
-        <v>11.509</v>
+        <v>11.493</v>
       </c>
       <c r="V26" t="n">
-        <v>11.509</v>
+        <v>11.492</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -5186,25 +5186,25 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5226,58 +5226,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5.58</v>
+        <v>5.727</v>
       </c>
       <c r="F27" t="n">
-        <v>5.574</v>
+        <v>5.725</v>
       </c>
       <c r="G27" t="n">
-        <v>5.582</v>
+        <v>5.728</v>
       </c>
       <c r="H27" t="n">
-        <v>5.58</v>
+        <v>5.727</v>
       </c>
       <c r="I27" t="n">
-        <v>5.582</v>
+        <v>5.728</v>
       </c>
       <c r="J27" t="n">
-        <v>11.368</v>
+        <v>11.351</v>
       </c>
       <c r="K27" t="n">
-        <v>11.362</v>
+        <v>11.349</v>
       </c>
       <c r="L27" t="n">
-        <v>11.371</v>
+        <v>11.352</v>
       </c>
       <c r="M27" t="n">
-        <v>11.368</v>
+        <v>11.351</v>
       </c>
       <c r="N27" t="n">
-        <v>11.371</v>
+        <v>11.352</v>
       </c>
       <c r="O27" t="n">
-        <v>5.582</v>
+        <v>5.727</v>
       </c>
       <c r="P27" t="n">
-        <v>5.582</v>
+        <v>5.728</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.582</v>
+        <v>5.728</v>
       </c>
       <c r="R27" t="n">
-        <v>5.574</v>
+        <v>5.725</v>
       </c>
       <c r="S27" t="n">
-        <v>11.37</v>
+        <v>11.351</v>
       </c>
       <c r="T27" t="n">
-        <v>11.371</v>
+        <v>11.352</v>
       </c>
       <c r="U27" t="n">
-        <v>11.371</v>
+        <v>11.352</v>
       </c>
       <c r="V27" t="n">
-        <v>11.362</v>
+        <v>11.349</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -5285,25 +5285,25 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y27" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5325,58 +5325,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5.488</v>
+        <v>5.647</v>
       </c>
       <c r="F28" t="n">
-        <v>5.484</v>
+        <v>5.641</v>
       </c>
       <c r="G28" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="H28" t="n">
-        <v>5.488</v>
+        <v>5.647</v>
       </c>
       <c r="I28" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="J28" t="n">
-        <v>11.276</v>
+        <v>11.271</v>
       </c>
       <c r="K28" t="n">
-        <v>11.272</v>
+        <v>11.265</v>
       </c>
       <c r="L28" t="n">
-        <v>11.278</v>
+        <v>11.273</v>
       </c>
       <c r="M28" t="n">
-        <v>11.276</v>
+        <v>11.271</v>
       </c>
       <c r="N28" t="n">
-        <v>11.278</v>
+        <v>11.273</v>
       </c>
       <c r="O28" t="n">
-        <v>5.489</v>
+        <v>5.649</v>
       </c>
       <c r="P28" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.49</v>
+        <v>5.649</v>
       </c>
       <c r="R28" t="n">
-        <v>5.484</v>
+        <v>5.641</v>
       </c>
       <c r="S28" t="n">
-        <v>11.277</v>
+        <v>11.273</v>
       </c>
       <c r="T28" t="n">
-        <v>11.278</v>
+        <v>11.273</v>
       </c>
       <c r="U28" t="n">
-        <v>11.278</v>
+        <v>11.273</v>
       </c>
       <c r="V28" t="n">
-        <v>11.272</v>
+        <v>11.265</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5384,25 +5384,25 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5424,58 +5424,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.472</v>
+        <v>5.628</v>
       </c>
       <c r="F29" t="n">
-        <v>5.465</v>
+        <v>5.618</v>
       </c>
       <c r="G29" t="n">
-        <v>5.475</v>
+        <v>5.632</v>
       </c>
       <c r="H29" t="n">
-        <v>5.471</v>
+        <v>5.628</v>
       </c>
       <c r="I29" t="n">
-        <v>5.474</v>
+        <v>5.632</v>
       </c>
       <c r="J29" t="n">
-        <v>11.26</v>
+        <v>11.252</v>
       </c>
       <c r="K29" t="n">
-        <v>11.253</v>
+        <v>11.242</v>
       </c>
       <c r="L29" t="n">
-        <v>11.263</v>
+        <v>11.256</v>
       </c>
       <c r="M29" t="n">
-        <v>11.259</v>
+        <v>11.252</v>
       </c>
       <c r="N29" t="n">
-        <v>11.262</v>
+        <v>11.255</v>
       </c>
       <c r="O29" t="n">
-        <v>5.473</v>
+        <v>5.631</v>
       </c>
       <c r="P29" t="n">
-        <v>5.475</v>
+        <v>5.632</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.473</v>
+        <v>5.631</v>
       </c>
       <c r="R29" t="n">
-        <v>5.465</v>
+        <v>5.618</v>
       </c>
       <c r="S29" t="n">
-        <v>11.262</v>
+        <v>11.255</v>
       </c>
       <c r="T29" t="n">
-        <v>11.263</v>
+        <v>11.256</v>
       </c>
       <c r="U29" t="n">
-        <v>11.261</v>
+        <v>11.255</v>
       </c>
       <c r="V29" t="n">
-        <v>11.253</v>
+        <v>11.242</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5483,25 +5483,25 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA29" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="AB29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5523,58 +5523,58 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="F30" t="n">
-        <v>3.911</v>
+        <v>3.975</v>
       </c>
       <c r="G30" t="n">
-        <v>4.051</v>
+        <v>4.208</v>
       </c>
       <c r="H30" t="n">
-        <v>3.911</v>
+        <v>3.975</v>
       </c>
       <c r="I30" t="n">
-        <v>3.958</v>
+        <v>4.053</v>
       </c>
       <c r="J30" t="n">
-        <v>5.014</v>
+        <v>4.777</v>
       </c>
       <c r="K30" t="n">
-        <v>4.975</v>
+        <v>4.712</v>
       </c>
       <c r="L30" t="n">
-        <v>5.116</v>
+        <v>4.946</v>
       </c>
       <c r="M30" t="n">
-        <v>4.975</v>
+        <v>4.713</v>
       </c>
       <c r="N30" t="n">
-        <v>5.022</v>
+        <v>4.791</v>
       </c>
       <c r="O30" t="n">
-        <v>3.911</v>
+        <v>3.975</v>
       </c>
       <c r="P30" t="n">
-        <v>3.911</v>
+        <v>3.975</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.926</v>
+        <v>4.002</v>
       </c>
       <c r="R30" t="n">
-        <v>4.051</v>
+        <v>4.208</v>
       </c>
       <c r="S30" t="n">
-        <v>4.975</v>
+        <v>4.712</v>
       </c>
       <c r="T30" t="n">
-        <v>4.976</v>
+        <v>4.713</v>
       </c>
       <c r="U30" t="n">
-        <v>4.99</v>
+        <v>4.739</v>
       </c>
       <c r="V30" t="n">
-        <v>5.116</v>
+        <v>4.946</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -5582,21 +5582,21 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5622,58 +5622,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.465</v>
+        <v>2.794</v>
       </c>
       <c r="F31" t="n">
-        <v>2.368</v>
+        <v>2.698</v>
       </c>
       <c r="G31" t="n">
-        <v>2.602</v>
+        <v>2.931</v>
       </c>
       <c r="H31" t="n">
-        <v>2.409</v>
+        <v>2.739</v>
       </c>
       <c r="I31" t="n">
-        <v>2.499</v>
+        <v>2.83</v>
       </c>
       <c r="J31" t="n">
-        <v>3.529</v>
+        <v>3.532</v>
       </c>
       <c r="K31" t="n">
-        <v>3.432</v>
+        <v>3.435</v>
       </c>
       <c r="L31" t="n">
-        <v>3.666</v>
+        <v>3.668</v>
       </c>
       <c r="M31" t="n">
-        <v>3.473</v>
+        <v>3.476</v>
       </c>
       <c r="N31" t="n">
-        <v>3.564</v>
+        <v>3.567</v>
       </c>
       <c r="O31" t="n">
-        <v>2.368</v>
+        <v>2.698</v>
       </c>
       <c r="P31" t="n">
-        <v>2.423</v>
+        <v>2.753</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.465</v>
+        <v>2.796</v>
       </c>
       <c r="R31" t="n">
-        <v>2.602</v>
+        <v>2.931</v>
       </c>
       <c r="S31" t="n">
-        <v>3.432</v>
+        <v>3.435</v>
       </c>
       <c r="T31" t="n">
-        <v>3.487</v>
+        <v>3.49</v>
       </c>
       <c r="U31" t="n">
-        <v>3.529</v>
+        <v>3.534</v>
       </c>
       <c r="V31" t="n">
-        <v>3.666</v>
+        <v>3.668</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -5721,58 +5721,58 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.096</v>
+        <v>2.424</v>
       </c>
       <c r="F32" t="n">
-        <v>2.042</v>
+        <v>2.369</v>
       </c>
       <c r="G32" t="n">
-        <v>2.135</v>
+        <v>2.464</v>
       </c>
       <c r="H32" t="n">
-        <v>2.069</v>
+        <v>2.397</v>
       </c>
       <c r="I32" t="n">
-        <v>2.131</v>
+        <v>2.46</v>
       </c>
       <c r="J32" t="n">
-        <v>3.16</v>
+        <v>3.162</v>
       </c>
       <c r="K32" t="n">
-        <v>3.106</v>
+        <v>3.107</v>
       </c>
       <c r="L32" t="n">
-        <v>3.199</v>
+        <v>3.201</v>
       </c>
       <c r="M32" t="n">
-        <v>3.133</v>
+        <v>3.135</v>
       </c>
       <c r="N32" t="n">
-        <v>3.195</v>
+        <v>3.197</v>
       </c>
       <c r="O32" t="n">
-        <v>2.042</v>
+        <v>2.369</v>
       </c>
       <c r="P32" t="n">
-        <v>2.13</v>
+        <v>2.458</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.078</v>
+        <v>2.407</v>
       </c>
       <c r="R32" t="n">
-        <v>2.135</v>
+        <v>2.464</v>
       </c>
       <c r="S32" t="n">
-        <v>3.106</v>
+        <v>3.107</v>
       </c>
       <c r="T32" t="n">
-        <v>3.194</v>
+        <v>3.196</v>
       </c>
       <c r="U32" t="n">
-        <v>3.142</v>
+        <v>3.144</v>
       </c>
       <c r="V32" t="n">
-        <v>3.199</v>
+        <v>3.201</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -5780,21 +5780,21 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -5820,58 +5820,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.714</v>
+        <v>2.042</v>
       </c>
       <c r="F33" t="n">
-        <v>1.522</v>
+        <v>1.849</v>
       </c>
       <c r="G33" t="n">
-        <v>2.049</v>
+        <v>2.377</v>
       </c>
       <c r="H33" t="n">
-        <v>1.601</v>
+        <v>1.928</v>
       </c>
       <c r="I33" t="n">
-        <v>1.757</v>
+        <v>2.084</v>
       </c>
       <c r="J33" t="n">
         <v>2.779</v>
       </c>
       <c r="K33" t="n">
-        <v>2.586</v>
+        <v>2.587</v>
       </c>
       <c r="L33" t="n">
-        <v>3.113</v>
+        <v>3.115</v>
       </c>
       <c r="M33" t="n">
-        <v>2.665</v>
+        <v>2.666</v>
       </c>
       <c r="N33" t="n">
-        <v>2.821</v>
+        <v>2.822</v>
       </c>
       <c r="O33" t="n">
-        <v>1.522</v>
+        <v>1.849</v>
       </c>
       <c r="P33" t="n">
-        <v>2.049</v>
+        <v>2.377</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.627</v>
+        <v>1.954</v>
       </c>
       <c r="R33" t="n">
-        <v>1.659</v>
+        <v>1.986</v>
       </c>
       <c r="S33" t="n">
-        <v>2.586</v>
+        <v>2.587</v>
       </c>
       <c r="T33" t="n">
-        <v>3.113</v>
+        <v>3.115</v>
       </c>
       <c r="U33" t="n">
-        <v>2.691</v>
+        <v>2.692</v>
       </c>
       <c r="V33" t="n">
-        <v>2.723</v>
+        <v>2.724</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="X33" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -5919,58 +5919,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.605</v>
+        <v>1.935</v>
       </c>
       <c r="F34" t="n">
-        <v>1.349</v>
+        <v>1.679</v>
       </c>
       <c r="G34" t="n">
-        <v>2.221</v>
+        <v>2.549</v>
       </c>
       <c r="H34" t="n">
-        <v>1.376</v>
+        <v>1.707</v>
       </c>
       <c r="I34" t="n">
-        <v>1.655</v>
+        <v>1.985</v>
       </c>
       <c r="J34" t="n">
-        <v>2.669</v>
+        <v>2.673</v>
       </c>
       <c r="K34" t="n">
-        <v>2.413</v>
+        <v>2.417</v>
       </c>
       <c r="L34" t="n">
-        <v>3.285</v>
+        <v>3.286</v>
       </c>
       <c r="M34" t="n">
-        <v>2.44</v>
+        <v>2.444</v>
       </c>
       <c r="N34" t="n">
-        <v>2.719</v>
+        <v>2.723</v>
       </c>
       <c r="O34" t="n">
-        <v>1.349</v>
+        <v>1.679</v>
       </c>
       <c r="P34" t="n">
-        <v>2.221</v>
+        <v>2.549</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.467</v>
+        <v>1.797</v>
       </c>
       <c r="R34" t="n">
-        <v>1.385</v>
+        <v>1.716</v>
       </c>
       <c r="S34" t="n">
-        <v>2.413</v>
+        <v>2.417</v>
       </c>
       <c r="T34" t="n">
-        <v>3.285</v>
+        <v>3.286</v>
       </c>
       <c r="U34" t="n">
-        <v>2.531</v>
+        <v>2.535</v>
       </c>
       <c r="V34" t="n">
-        <v>2.449</v>
+        <v>2.453</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -5978,21 +5978,21 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA34" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -6018,58 +6018,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.194</v>
+        <v>2.471</v>
       </c>
       <c r="F35" t="n">
-        <v>1.088</v>
+        <v>1.42</v>
       </c>
       <c r="G35" t="n">
-        <v>4.881</v>
+        <v>4.997</v>
       </c>
       <c r="H35" t="n">
-        <v>1.291</v>
+        <v>1.622</v>
       </c>
       <c r="I35" t="n">
-        <v>2.306</v>
+        <v>2.583</v>
       </c>
       <c r="J35" t="n">
-        <v>3.258</v>
+        <v>3.209</v>
       </c>
       <c r="K35" t="n">
-        <v>2.153</v>
+        <v>2.158</v>
       </c>
       <c r="L35" t="n">
-        <v>5.946</v>
+        <v>5.735</v>
       </c>
       <c r="M35" t="n">
-        <v>2.355</v>
+        <v>2.359</v>
       </c>
       <c r="N35" t="n">
-        <v>3.37</v>
+        <v>3.321</v>
       </c>
       <c r="O35" t="n">
-        <v>1.359</v>
+        <v>1.689</v>
       </c>
       <c r="P35" t="n">
-        <v>4.881</v>
+        <v>4.997</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.448</v>
+        <v>1.778</v>
       </c>
       <c r="R35" t="n">
-        <v>1.088</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.423</v>
+        <v>2.427</v>
       </c>
       <c r="T35" t="n">
-        <v>5.946</v>
+        <v>5.735</v>
       </c>
       <c r="U35" t="n">
-        <v>2.512</v>
+        <v>2.516</v>
       </c>
       <c r="V35" t="n">
-        <v>2.153</v>
+        <v>2.158</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6077,21 +6077,21 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -6117,58 +6117,58 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>43.735</v>
+        <v>42.288</v>
       </c>
       <c r="F36" t="n">
-        <v>1.487</v>
+        <v>1.817</v>
       </c>
       <c r="G36" t="n">
-        <v>105.891</v>
+        <v>106.202</v>
       </c>
       <c r="H36" t="n">
-        <v>1.513</v>
+        <v>1.841</v>
       </c>
       <c r="I36" t="n">
-        <v>76.003</v>
+        <v>71.01300000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>44.799</v>
+        <v>43.025</v>
       </c>
       <c r="K36" t="n">
-        <v>2.551</v>
+        <v>2.555</v>
       </c>
       <c r="L36" t="n">
-        <v>106.955</v>
+        <v>106.939</v>
       </c>
       <c r="M36" t="n">
-        <v>2.577</v>
+        <v>2.578</v>
       </c>
       <c r="N36" t="n">
-        <v>77.06699999999999</v>
+        <v>71.75</v>
       </c>
       <c r="O36" t="n">
-        <v>105.891</v>
+        <v>106.202</v>
       </c>
       <c r="P36" t="n">
-        <v>66.04000000000001</v>
+        <v>59.283</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.522</v>
+        <v>1.849</v>
       </c>
       <c r="R36" t="n">
-        <v>1.487</v>
+        <v>1.817</v>
       </c>
       <c r="S36" t="n">
-        <v>106.955</v>
+        <v>106.939</v>
       </c>
       <c r="T36" t="n">
-        <v>67.104</v>
+        <v>60.02</v>
       </c>
       <c r="U36" t="n">
         <v>2.586</v>
       </c>
       <c r="V36" t="n">
-        <v>2.551</v>
+        <v>2.555</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6176,21 +6176,21 @@
         </is>
       </c>
       <c r="X36" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -6895,58 +6895,58 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="F44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="G44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="H44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="I44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="J44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="P44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="R44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="S44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="U44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="V44" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -6954,25 +6954,25 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA44" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -6994,58 +6994,58 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="F45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="G45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="H45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="I45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="J45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="P45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="R45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="S45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="T45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="U45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="V45" t="n">
-        <v>8.417999999999999</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -7053,25 +7053,25 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7093,58 +7093,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="F46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="G46" t="n">
-        <v>6.922</v>
+        <v>6.695</v>
       </c>
       <c r="H46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="I46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="J46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="K46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="L46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="M46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="N46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="O46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="P46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.922</v>
+        <v>6.695</v>
       </c>
       <c r="R46" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="S46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="T46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="U46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="V46" t="n">
-        <v>8.43</v>
+        <v>8.407</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -7152,25 +7152,25 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA46" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7192,58 +7192,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="F47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="G47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="H47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="I47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="J47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="K47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="L47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="M47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="N47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="O47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="P47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="R47" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="S47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="T47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="U47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="V47" t="n">
-        <v>8.476000000000001</v>
+        <v>8.455</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -7251,25 +7251,25 @@
         </is>
       </c>
       <c r="X47" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7291,58 +7291,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="F48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="G48" t="n">
-        <v>6.983</v>
+        <v>6.771</v>
       </c>
       <c r="H48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="I48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="J48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>8.491</v>
+        <v>8.481999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="P48" t="n">
-        <v>6.983</v>
+        <v>6.771</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="R48" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="S48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="T48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="U48" t="n">
-        <v>8.491</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="V48" t="n">
-        <v>8.491</v>
+        <v>8.481999999999999</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -7350,25 +7350,25 @@
         </is>
       </c>
       <c r="X48" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA48" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7390,58 +7390,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="F49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="G49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="H49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="I49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="J49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="P49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="R49" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="S49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="T49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="V49" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -7449,25 +7449,25 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA49" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7489,58 +7489,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="F50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="G50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="H50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="I50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="J50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.491</v>
       </c>
       <c r="L50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.491</v>
       </c>
       <c r="N50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="P50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="R50" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
       <c r="S50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.491</v>
       </c>
       <c r="T50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="U50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.491</v>
       </c>
       <c r="V50" t="n">
-        <v>8.494999999999999</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -7548,25 +7548,25 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA50" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="AB50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -7588,58 +7588,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="F51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="G51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="H51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="I51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="J51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="K51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="L51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="M51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="N51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="O51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="P51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="R51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="S51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="T51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="U51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="V51" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -7647,21 +7647,21 @@
         </is>
       </c>
       <c r="X51" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA51" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -7687,58 +7687,58 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="F52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="G52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="H52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="I52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="J52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="K52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="L52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="M52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="N52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="O52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="P52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="R52" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="S52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="T52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="U52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="V52" t="n">
-        <v>4.883</v>
+        <v>4.807</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -7746,21 +7746,21 @@
         </is>
       </c>
       <c r="X52" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA52" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -7786,58 +7786,58 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="F53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="G53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="H53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="I53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="J53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="K53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="L53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="M53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="N53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="O53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="P53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="R53" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="S53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="T53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="U53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="V53" t="n">
-        <v>4.675</v>
+        <v>4.645</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -7845,21 +7845,21 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA53" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -7885,58 +7885,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.063</v>
+        <v>3.527</v>
       </c>
       <c r="F54" t="n">
-        <v>4.062</v>
+        <v>3.527</v>
       </c>
       <c r="G54" t="n">
-        <v>4.063</v>
+        <v>3.527</v>
       </c>
       <c r="H54" t="n">
-        <v>4.062</v>
+        <v>3.527</v>
       </c>
       <c r="I54" t="n">
-        <v>4.063</v>
+        <v>3.527</v>
       </c>
       <c r="J54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="K54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="L54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="M54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="N54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="O54" t="n">
-        <v>4.063</v>
+        <v>3.527</v>
       </c>
       <c r="P54" t="n">
-        <v>4.063</v>
+        <v>3.527</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.062</v>
+        <v>3.527</v>
       </c>
       <c r="R54" t="n">
-        <v>4.062</v>
+        <v>3.527</v>
       </c>
       <c r="S54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="T54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="U54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="V54" t="n">
-        <v>4.644</v>
+        <v>4.585</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -7944,21 +7944,21 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA54" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -7984,58 +7984,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="F55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="G55" t="n">
-        <v>4.091</v>
+        <v>3.583</v>
       </c>
       <c r="H55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="I55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="J55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="K55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="L55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="M55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="N55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="O55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="P55" t="n">
-        <v>4.091</v>
+        <v>3.583</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="R55" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="S55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="T55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="U55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="V55" t="n">
-        <v>4.672</v>
+        <v>4.64</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -8043,21 +8043,21 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA55" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -8083,58 +8083,58 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.449</v>
+        <v>3.93</v>
       </c>
       <c r="F56" t="n">
-        <v>4.447</v>
+        <v>3.929</v>
       </c>
       <c r="G56" t="n">
-        <v>4.451</v>
+        <v>3.933</v>
       </c>
       <c r="H56" t="n">
-        <v>4.448</v>
+        <v>3.929</v>
       </c>
       <c r="I56" t="n">
-        <v>4.449</v>
+        <v>3.93</v>
       </c>
       <c r="J56" t="n">
-        <v>5.03</v>
+        <v>4.988</v>
       </c>
       <c r="K56" t="n">
-        <v>5.028</v>
+        <v>4.986</v>
       </c>
       <c r="L56" t="n">
-        <v>5.032</v>
+        <v>4.99</v>
       </c>
       <c r="M56" t="n">
-        <v>5.029</v>
+        <v>4.987</v>
       </c>
       <c r="N56" t="n">
-        <v>5.031</v>
+        <v>4.988</v>
       </c>
       <c r="O56" t="n">
-        <v>4.449</v>
+        <v>3.929</v>
       </c>
       <c r="P56" t="n">
-        <v>4.451</v>
+        <v>3.933</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.448</v>
+        <v>3.929</v>
       </c>
       <c r="R56" t="n">
-        <v>4.447</v>
+        <v>3.929</v>
       </c>
       <c r="S56" t="n">
-        <v>5.03</v>
+        <v>4.987</v>
       </c>
       <c r="T56" t="n">
-        <v>5.032</v>
+        <v>4.99</v>
       </c>
       <c r="U56" t="n">
-        <v>5.03</v>
+        <v>4.987</v>
       </c>
       <c r="V56" t="n">
-        <v>5.028</v>
+        <v>4.986</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -8142,21 +8142,21 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA56" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -8182,58 +8182,58 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.734</v>
+        <v>4.246</v>
       </c>
       <c r="F57" t="n">
-        <v>4.733</v>
+        <v>4.24</v>
       </c>
       <c r="G57" t="n">
-        <v>4.735</v>
+        <v>4.251</v>
       </c>
       <c r="H57" t="n">
-        <v>4.733</v>
+        <v>4.245</v>
       </c>
       <c r="I57" t="n">
-        <v>4.734</v>
+        <v>4.248</v>
       </c>
       <c r="J57" t="n">
-        <v>5.315</v>
+        <v>5.304</v>
       </c>
       <c r="K57" t="n">
-        <v>5.314</v>
+        <v>5.298</v>
       </c>
       <c r="L57" t="n">
-        <v>5.316</v>
+        <v>5.309</v>
       </c>
       <c r="M57" t="n">
-        <v>5.314</v>
+        <v>5.303</v>
       </c>
       <c r="N57" t="n">
-        <v>5.315</v>
+        <v>5.306</v>
       </c>
       <c r="O57" t="n">
-        <v>4.734</v>
+        <v>4.246</v>
       </c>
       <c r="P57" t="n">
-        <v>4.735</v>
+        <v>4.251</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.734</v>
+        <v>4.247</v>
       </c>
       <c r="R57" t="n">
-        <v>4.733</v>
+        <v>4.24</v>
       </c>
       <c r="S57" t="n">
-        <v>5.315</v>
+        <v>5.304</v>
       </c>
       <c r="T57" t="n">
-        <v>5.316</v>
+        <v>5.309</v>
       </c>
       <c r="U57" t="n">
-        <v>5.315</v>
+        <v>5.305</v>
       </c>
       <c r="V57" t="n">
-        <v>5.314</v>
+        <v>5.298</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -8241,21 +8241,21 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="AA57" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="AB57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -15197,58 +15197,58 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="F128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="G128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="H128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="I128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="J128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="K128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="L128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="M128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="N128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="O128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="P128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="Q128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="R128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="S128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="T128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="U128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="V128" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -15257,22 +15257,22 @@
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA128" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB128" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -15294,58 +15294,58 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="F129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="G129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="H129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="I129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="J129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="K129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="L129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="M129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="N129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="O129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="P129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="Q129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="R129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="S129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="T129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="U129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="V129" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="W129" t="inlineStr">
         <is>
@@ -15354,22 +15354,22 @@
       </c>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA129" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB129" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -15391,58 +15391,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="F130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="G130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="H130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="I130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="J130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="K130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="L130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="M130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="N130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="O130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="P130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="Q130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="R130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="S130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="T130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="U130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="V130" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="W130" t="inlineStr">
         <is>
@@ -15451,22 +15451,22 @@
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA130" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB130" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -15488,58 +15488,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6.837</v>
+        <v>6.851</v>
       </c>
       <c r="F131" t="n">
-        <v>6.832</v>
+        <v>6.851</v>
       </c>
       <c r="G131" t="n">
-        <v>6.841</v>
+        <v>6.851</v>
       </c>
       <c r="H131" t="n">
-        <v>6.836</v>
+        <v>6.851</v>
       </c>
       <c r="I131" t="n">
-        <v>6.84</v>
+        <v>6.851</v>
       </c>
       <c r="J131" t="n">
-        <v>6.837</v>
+        <v>6.851</v>
       </c>
       <c r="K131" t="n">
-        <v>6.832</v>
+        <v>6.851</v>
       </c>
       <c r="L131" t="n">
-        <v>6.841</v>
+        <v>6.851</v>
       </c>
       <c r="M131" t="n">
-        <v>6.836</v>
+        <v>6.851</v>
       </c>
       <c r="N131" t="n">
-        <v>6.84</v>
+        <v>6.851</v>
       </c>
       <c r="O131" t="n">
-        <v>6.837</v>
+        <v>6.851</v>
       </c>
       <c r="P131" t="n">
-        <v>6.841</v>
+        <v>6.851</v>
       </c>
       <c r="Q131" t="n">
-        <v>6.839</v>
+        <v>6.851</v>
       </c>
       <c r="R131" t="n">
-        <v>6.832</v>
+        <v>6.851</v>
       </c>
       <c r="S131" t="n">
-        <v>6.837</v>
+        <v>6.851</v>
       </c>
       <c r="T131" t="n">
-        <v>6.841</v>
+        <v>6.851</v>
       </c>
       <c r="U131" t="n">
-        <v>6.839</v>
+        <v>6.851</v>
       </c>
       <c r="V131" t="n">
-        <v>6.832</v>
+        <v>6.851</v>
       </c>
       <c r="W131" t="inlineStr">
         <is>
@@ -15548,22 +15548,22 @@
       </c>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA131" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB131" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -15585,58 +15585,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6.776</v>
+        <v>6.829</v>
       </c>
       <c r="F132" t="n">
-        <v>6.771</v>
+        <v>6.82</v>
       </c>
       <c r="G132" t="n">
-        <v>6.781</v>
+        <v>6.841</v>
       </c>
       <c r="H132" t="n">
-        <v>6.773</v>
+        <v>6.825</v>
       </c>
       <c r="I132" t="n">
-        <v>6.777</v>
+        <v>6.832</v>
       </c>
       <c r="J132" t="n">
-        <v>6.776</v>
+        <v>6.829</v>
       </c>
       <c r="K132" t="n">
-        <v>6.771</v>
+        <v>6.82</v>
       </c>
       <c r="L132" t="n">
-        <v>6.781</v>
+        <v>6.841</v>
       </c>
       <c r="M132" t="n">
-        <v>6.773</v>
+        <v>6.825</v>
       </c>
       <c r="N132" t="n">
-        <v>6.777</v>
+        <v>6.832</v>
       </c>
       <c r="O132" t="n">
-        <v>6.774</v>
+        <v>6.826</v>
       </c>
       <c r="P132" t="n">
-        <v>6.781</v>
+        <v>6.841</v>
       </c>
       <c r="Q132" t="n">
-        <v>6.776</v>
+        <v>6.829</v>
       </c>
       <c r="R132" t="n">
-        <v>6.771</v>
+        <v>6.82</v>
       </c>
       <c r="S132" t="n">
-        <v>6.774</v>
+        <v>6.826</v>
       </c>
       <c r="T132" t="n">
-        <v>6.781</v>
+        <v>6.841</v>
       </c>
       <c r="U132" t="n">
-        <v>6.776</v>
+        <v>6.829</v>
       </c>
       <c r="V132" t="n">
-        <v>6.771</v>
+        <v>6.82</v>
       </c>
       <c r="W132" t="inlineStr">
         <is>
@@ -15645,22 +15645,22 @@
       </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA132" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB132" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -15682,58 +15682,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6.646</v>
+        <v>6.605</v>
       </c>
       <c r="F133" t="n">
-        <v>6.579</v>
+        <v>6.54</v>
       </c>
       <c r="G133" t="n">
-        <v>6.714</v>
+        <v>6.705</v>
       </c>
       <c r="H133" t="n">
-        <v>6.628</v>
+        <v>6.575</v>
       </c>
       <c r="I133" t="n">
-        <v>6.663</v>
+        <v>6.617</v>
       </c>
       <c r="J133" t="n">
-        <v>6.646</v>
+        <v>6.605</v>
       </c>
       <c r="K133" t="n">
-        <v>6.579</v>
+        <v>6.54</v>
       </c>
       <c r="L133" t="n">
-        <v>6.714</v>
+        <v>6.705</v>
       </c>
       <c r="M133" t="n">
-        <v>6.628</v>
+        <v>6.575</v>
       </c>
       <c r="N133" t="n">
-        <v>6.663</v>
+        <v>6.617</v>
       </c>
       <c r="O133" t="n">
-        <v>6.646</v>
+        <v>6.588</v>
       </c>
       <c r="P133" t="n">
-        <v>6.714</v>
+        <v>6.705</v>
       </c>
       <c r="Q133" t="n">
-        <v>6.644</v>
+        <v>6.586</v>
       </c>
       <c r="R133" t="n">
-        <v>6.579</v>
+        <v>6.54</v>
       </c>
       <c r="S133" t="n">
-        <v>6.646</v>
+        <v>6.588</v>
       </c>
       <c r="T133" t="n">
-        <v>6.714</v>
+        <v>6.705</v>
       </c>
       <c r="U133" t="n">
-        <v>6.644</v>
+        <v>6.586</v>
       </c>
       <c r="V133" t="n">
-        <v>6.579</v>
+        <v>6.54</v>
       </c>
       <c r="W133" t="inlineStr">
         <is>
@@ -15742,22 +15742,22 @@
       </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA133" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB133" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -15779,58 +15779,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6.388</v>
+        <v>6.445</v>
       </c>
       <c r="F134" t="n">
-        <v>6.312</v>
+        <v>6.415</v>
       </c>
       <c r="G134" t="n">
-        <v>6.5</v>
+        <v>6.488</v>
       </c>
       <c r="H134" t="n">
-        <v>6.347</v>
+        <v>6.429</v>
       </c>
       <c r="I134" t="n">
-        <v>6.411</v>
+        <v>6.456</v>
       </c>
       <c r="J134" t="n">
-        <v>6.388</v>
+        <v>6.445</v>
       </c>
       <c r="K134" t="n">
-        <v>6.312</v>
+        <v>6.415</v>
       </c>
       <c r="L134" t="n">
-        <v>6.5</v>
+        <v>6.488</v>
       </c>
       <c r="M134" t="n">
-        <v>6.347</v>
+        <v>6.429</v>
       </c>
       <c r="N134" t="n">
-        <v>6.411</v>
+        <v>6.456</v>
       </c>
       <c r="O134" t="n">
-        <v>6.381</v>
+        <v>6.445</v>
       </c>
       <c r="P134" t="n">
-        <v>6.5</v>
+        <v>6.488</v>
       </c>
       <c r="Q134" t="n">
-        <v>6.359</v>
+        <v>6.434</v>
       </c>
       <c r="R134" t="n">
-        <v>6.312</v>
+        <v>6.415</v>
       </c>
       <c r="S134" t="n">
-        <v>6.381</v>
+        <v>6.445</v>
       </c>
       <c r="T134" t="n">
-        <v>6.5</v>
+        <v>6.488</v>
       </c>
       <c r="U134" t="n">
-        <v>6.359</v>
+        <v>6.434</v>
       </c>
       <c r="V134" t="n">
-        <v>6.312</v>
+        <v>6.415</v>
       </c>
       <c r="W134" t="inlineStr">
         <is>
@@ -15839,22 +15839,22 @@
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="AA134" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="AB134" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -16608,25 +16608,25 @@
         <v>9043370</v>
       </c>
       <c r="C2" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="D2" t="n">
-        <v>1.552</v>
+        <v>1.356</v>
       </c>
       <c r="E2" t="n">
-        <v>1.412</v>
+        <v>1.208</v>
       </c>
       <c r="F2" t="n">
-        <v>1.359</v>
+        <v>1.136</v>
       </c>
       <c r="G2" t="n">
-        <v>1.243</v>
+        <v>1.045</v>
       </c>
       <c r="H2" t="n">
-        <v>1.227</v>
+        <v>1.026</v>
       </c>
       <c r="I2" t="n">
-        <v>1.222</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="3">
@@ -16639,25 +16639,25 @@
         <v>9036028</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="D3" t="n">
-        <v>3.616</v>
+        <v>3.655</v>
       </c>
       <c r="E3" t="n">
-        <v>3.597</v>
+        <v>3.637</v>
       </c>
       <c r="F3" t="n">
-        <v>3.582</v>
+        <v>3.623</v>
       </c>
       <c r="G3" t="n">
-        <v>3.56</v>
+        <v>3.601</v>
       </c>
       <c r="H3" t="n">
-        <v>3.528</v>
+        <v>3.567</v>
       </c>
       <c r="I3" t="n">
-        <v>3.478</v>
+        <v>3.515</v>
       </c>
     </row>
     <row r="4">
@@ -16670,25 +16670,25 @@
         <v>9040208</v>
       </c>
       <c r="C4" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="D4" t="n">
-        <v>3.133</v>
+        <v>3.564</v>
       </c>
       <c r="E4" t="n">
-        <v>3.053</v>
+        <v>3.484</v>
       </c>
       <c r="F4" t="n">
-        <v>2.998</v>
+        <v>3.427</v>
       </c>
       <c r="G4" t="n">
-        <v>2.935</v>
+        <v>3.365</v>
       </c>
       <c r="H4" t="n">
-        <v>2.871</v>
+        <v>3.301</v>
       </c>
       <c r="I4" t="n">
-        <v>2.824</v>
+        <v>3.255</v>
       </c>
     </row>
     <row r="5">
@@ -16701,25 +16701,25 @@
         <v>9053555</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="D5" t="n">
-        <v>5.872</v>
+        <v>6.024</v>
       </c>
       <c r="E5" t="n">
-        <v>5.807</v>
+        <v>5.958</v>
       </c>
       <c r="F5" t="n">
-        <v>5.721</v>
+        <v>5.869</v>
       </c>
       <c r="G5" t="n">
-        <v>5.58</v>
+        <v>5.727</v>
       </c>
       <c r="H5" t="n">
-        <v>5.488</v>
+        <v>5.647</v>
       </c>
       <c r="I5" t="n">
-        <v>5.472</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="6">
@@ -16732,25 +16732,25 @@
         <v>9038134</v>
       </c>
       <c r="C6" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="D6" t="n">
-        <v>2.465</v>
+        <v>2.794</v>
       </c>
       <c r="E6" t="n">
-        <v>2.096</v>
+        <v>2.424</v>
       </c>
       <c r="F6" t="n">
-        <v>1.714</v>
+        <v>2.042</v>
       </c>
       <c r="G6" t="n">
-        <v>1.605</v>
+        <v>1.935</v>
       </c>
       <c r="H6" t="n">
-        <v>2.194</v>
+        <v>2.471</v>
       </c>
       <c r="I6" t="n">
-        <v>43.735</v>
+        <v>42.288</v>
       </c>
     </row>
     <row r="7">
@@ -16794,25 +16794,25 @@
         <v>9042214</v>
       </c>
       <c r="C8" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="D8" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="E8" t="n">
-        <v>6.922</v>
+        <v>6.694</v>
       </c>
       <c r="F8" t="n">
-        <v>6.968</v>
+        <v>6.743</v>
       </c>
       <c r="G8" t="n">
-        <v>6.983</v>
+        <v>6.77</v>
       </c>
       <c r="H8" t="n">
-        <v>6.987</v>
+        <v>6.78</v>
       </c>
       <c r="I8" t="n">
-        <v>6.987</v>
+        <v>6.779</v>
       </c>
     </row>
     <row r="9">
@@ -16825,25 +16825,25 @@
         <v>9043597</v>
       </c>
       <c r="C9" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="D9" t="n">
-        <v>4.302</v>
+        <v>3.75</v>
       </c>
       <c r="E9" t="n">
-        <v>4.094</v>
+        <v>3.587</v>
       </c>
       <c r="F9" t="n">
-        <v>4.063</v>
+        <v>3.527</v>
       </c>
       <c r="G9" t="n">
-        <v>4.091</v>
+        <v>3.582</v>
       </c>
       <c r="H9" t="n">
-        <v>4.449</v>
+        <v>3.93</v>
       </c>
       <c r="I9" t="n">
-        <v>4.734</v>
+        <v>4.246</v>
       </c>
     </row>
     <row r="10">
@@ -17166,25 +17166,25 @@
         <v>9036459</v>
       </c>
       <c r="C20" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="D20" t="n">
-        <v>6.345</v>
+        <v>6.428</v>
       </c>
       <c r="E20" t="n">
-        <v>6.765</v>
+        <v>6.808</v>
       </c>
       <c r="F20" t="n">
-        <v>6.837</v>
+        <v>6.851</v>
       </c>
       <c r="G20" t="n">
-        <v>6.776</v>
+        <v>6.829</v>
       </c>
       <c r="H20" t="n">
-        <v>6.646</v>
+        <v>6.605</v>
       </c>
       <c r="I20" t="n">
-        <v>6.388</v>
+        <v>6.445</v>
       </c>
     </row>
     <row r="21">
@@ -17351,25 +17351,25 @@
         <v>46306</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="F3" t="n">
-        <v>5.826</v>
+        <v>5.824</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.226</v>
+        <v>-2.184</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Offset alto: -2.23 m. Revisar estación.</t>
+          <t>Offset alto: -2.18 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -17395,21 +17395,21 @@
         <v>46306</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="E4" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="F4" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 28 días</t>
+          <t>Observado muy antiguo para ajuste: 9 días</t>
         </is>
       </c>
     </row>
@@ -17523,25 +17523,25 @@
         <v>46306</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E7" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="F7" t="n">
-        <v>5.014</v>
+        <v>4.777</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.064</v>
+        <v>-0.737</v>
       </c>
       <c r="H7" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -17699,25 +17699,25 @@
         <v>46306</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="E11" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="F11" t="n">
-        <v>4.979</v>
+        <v>4.978</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.799</v>
+        <v>-1.365</v>
       </c>
       <c r="H11" t="n">
-        <v>3.18</v>
+        <v>3.613</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Offset alto: -1.80 m. Revisar estación.</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -17871,25 +17871,25 @@
         <v>46306</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="E15" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="F15" t="n">
-        <v>8.417999999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.508</v>
+        <v>-1.712</v>
       </c>
       <c r="H15" t="n">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Offset alto: -1.51 m. Revisar estación.</t>
+          <t>Offset alto: -1.71 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -17915,26 +17915,26 @@
         <v>46306</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="E16" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="F16" t="n">
-        <v>8.77</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.11</v>
+        <v>-7.304</v>
       </c>
       <c r="H16" t="n">
-        <v>1.66</v>
+        <v>1.412</v>
       </c>
       <c r="I16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Offset alto: -7.11 m. Revisar estación.</t>
+          <t>Offset alto: -7.30 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -18003,25 +18003,25 @@
         <v>46306</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="E18" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="F18" t="n">
-        <v>5.051</v>
+        <v>4.998</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.581</v>
+        <v>-1.058</v>
       </c>
       <c r="H18" t="n">
-        <v>4.47</v>
+        <v>3.94</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -18127,25 +18127,25 @@
         <v>46306</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="F21" t="n">
-        <v>11.688</v>
+        <v>11.679</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.788</v>
+        <v>-5.624</v>
       </c>
       <c r="H21" t="n">
-        <v>5.9</v>
+        <v>6.055</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Offset alto: -5.79 m. Revisar estación.</t>
+          <t>Offset alto: -5.62 m. Revisar estación.</t>
         </is>
       </c>
     </row>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>3.031</v>
+        <v>2.799</v>
       </c>
       <c r="I18" t="n">
-        <v>3.478</v>
+        <v>3.233</v>
       </c>
       <c r="J18" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="K18" t="n">
-        <v>3.409</v>
+        <v>3.175</v>
       </c>
       <c r="L18" t="n">
-        <v>0.659</v>
+        <v>0.655</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>10280</v>
+        <v>10282</v>
       </c>
       <c r="V18" t="n">
         <v>0.868</v>
@@ -2260,7 +2260,7 @@
         <v>0.847</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.681</v>
+        <v>1.68</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2299,22 +2299,22 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.866</v>
+        <v>1.727</v>
       </c>
       <c r="H19" t="n">
-        <v>1.897</v>
+        <v>1.757</v>
       </c>
       <c r="I19" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="K19" t="n">
-        <v>1.867</v>
+        <v>1.728</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.033</v>
+        <v>-0.032</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2327,29 +2327,29 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>14646</v>
+        <v>14649</v>
       </c>
       <c r="V19" t="n">
         <v>0.782</v>
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6.41</v>
+        <v>5.845</v>
       </c>
       <c r="H20" t="n">
-        <v>6.763</v>
+        <v>6.101</v>
       </c>
       <c r="I20" t="n">
-        <v>7.025</v>
+        <v>6.525</v>
       </c>
       <c r="J20" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="K20" t="n">
-        <v>6.763</v>
+        <v>6.17</v>
       </c>
       <c r="L20" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2424,43 +2424,45 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="P20" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>2743</v>
+        <v>2752</v>
       </c>
       <c r="V20" t="n">
         <v>0.865</v>
       </c>
       <c r="W20" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="X20" t="n">
         <v>0.858</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.751</v>
+        <v>1.748</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2499,22 +2501,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="H21" t="n">
-        <v>128.953</v>
+        <v>129.54</v>
       </c>
       <c r="I21" t="n">
-        <v>129.272</v>
+        <v>129.838</v>
       </c>
       <c r="J21" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="K21" t="n">
-        <v>129.191</v>
+        <v>129.759</v>
       </c>
       <c r="L21" t="n">
-        <v>0.61</v>
+        <v>0.609</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2523,31 +2525,33 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.605</v>
+      </c>
       <c r="P21" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>10258</v>
+        <v>10267</v>
       </c>
       <c r="V21" t="n">
         <v>0.865</v>
@@ -2556,10 +2560,10 @@
         <v>0.731</v>
       </c>
       <c r="X21" t="n">
-        <v>0.864</v>
+        <v>0.865</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.046</v>
+        <v>1.045</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -13811,58 +13815,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="F114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="G114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="H114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="I114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="J114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="K114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="L114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="M114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="N114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="O114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="P114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="R114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="S114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="T114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="U114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="V114" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -13870,21 +13874,21 @@
         </is>
       </c>
       <c r="X114" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y114" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA114" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -13910,58 +13914,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2.803</v>
+        <v>2.569</v>
       </c>
       <c r="F115" t="n">
-        <v>2.802</v>
+        <v>2.567</v>
       </c>
       <c r="G115" t="n">
-        <v>2.804</v>
+        <v>2.57</v>
       </c>
       <c r="H115" t="n">
-        <v>2.803</v>
+        <v>2.569</v>
       </c>
       <c r="I115" t="n">
-        <v>2.804</v>
+        <v>2.57</v>
       </c>
       <c r="J115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="K115" t="n">
-        <v>3.418</v>
+        <v>3.412</v>
       </c>
       <c r="L115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="M115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="N115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="O115" t="n">
-        <v>2.804</v>
+        <v>2.57</v>
       </c>
       <c r="P115" t="n">
-        <v>2.804</v>
+        <v>2.57</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.804</v>
+        <v>2.57</v>
       </c>
       <c r="R115" t="n">
-        <v>2.802</v>
+        <v>2.567</v>
       </c>
       <c r="S115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="T115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="U115" t="n">
-        <v>3.42</v>
+        <v>3.414</v>
       </c>
       <c r="V115" t="n">
-        <v>3.418</v>
+        <v>3.412</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -13969,21 +13973,21 @@
         </is>
       </c>
       <c r="X115" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y115" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA115" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -14009,58 +14013,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2.9</v>
+        <v>2.669</v>
       </c>
       <c r="F116" t="n">
-        <v>2.898</v>
+        <v>2.667</v>
       </c>
       <c r="G116" t="n">
-        <v>2.902</v>
+        <v>2.671</v>
       </c>
       <c r="H116" t="n">
-        <v>2.899</v>
+        <v>2.668</v>
       </c>
       <c r="I116" t="n">
-        <v>2.901</v>
+        <v>2.669</v>
       </c>
       <c r="J116" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3.511</v>
+      </c>
+      <c r="L116" t="n">
         <v>3.516</v>
       </c>
-      <c r="K116" t="n">
+      <c r="M116" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="N116" t="n">
         <v>3.514</v>
       </c>
-      <c r="L116" t="n">
-        <v>3.519</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="N116" t="n">
-        <v>3.517</v>
-      </c>
       <c r="O116" t="n">
-        <v>2.9</v>
+        <v>2.669</v>
       </c>
       <c r="P116" t="n">
-        <v>2.902</v>
+        <v>2.671</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.899</v>
+        <v>2.668</v>
       </c>
       <c r="R116" t="n">
-        <v>2.898</v>
+        <v>2.667</v>
       </c>
       <c r="S116" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="T116" t="n">
         <v>3.516</v>
       </c>
-      <c r="T116" t="n">
-        <v>3.519</v>
-      </c>
       <c r="U116" t="n">
-        <v>3.515</v>
+        <v>3.512</v>
       </c>
       <c r="V116" t="n">
-        <v>3.514</v>
+        <v>3.511</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -14068,21 +14072,21 @@
         </is>
       </c>
       <c r="X116" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y116" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA116" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -14108,58 +14112,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2.995</v>
+        <v>2.765</v>
       </c>
       <c r="F117" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="G117" t="n">
-        <v>2.997</v>
+        <v>2.767</v>
       </c>
       <c r="H117" t="n">
-        <v>2.994</v>
+        <v>2.764</v>
       </c>
       <c r="I117" t="n">
-        <v>2.996</v>
+        <v>2.766</v>
       </c>
       <c r="J117" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3.604</v>
+      </c>
+      <c r="L117" t="n">
+        <v>3.612</v>
+      </c>
+      <c r="M117" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="N117" t="n">
         <v>3.611</v>
       </c>
-      <c r="K117" t="n">
-        <v>3.607</v>
-      </c>
-      <c r="L117" t="n">
-        <v>3.614</v>
-      </c>
-      <c r="M117" t="n">
+      <c r="O117" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="P117" t="n">
+        <v>2.767</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="R117" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="T117" t="n">
+        <v>3.612</v>
+      </c>
+      <c r="U117" t="n">
         <v>3.611</v>
       </c>
-      <c r="N117" t="n">
-        <v>3.613</v>
-      </c>
-      <c r="O117" t="n">
-        <v>2.996</v>
-      </c>
-      <c r="P117" t="n">
-        <v>2.997</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>2.996</v>
-      </c>
-      <c r="R117" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="S117" t="n">
-        <v>3.612</v>
-      </c>
-      <c r="T117" t="n">
-        <v>3.614</v>
-      </c>
-      <c r="U117" t="n">
-        <v>3.612</v>
-      </c>
       <c r="V117" t="n">
-        <v>3.607</v>
+        <v>3.604</v>
       </c>
       <c r="W117" t="inlineStr">
         <is>
@@ -14167,21 +14171,21 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y117" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA117" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -14207,58 +14211,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3.119</v>
+        <v>2.887</v>
       </c>
       <c r="F118" t="n">
-        <v>3.116</v>
+        <v>2.884</v>
       </c>
       <c r="G118" t="n">
-        <v>3.121</v>
+        <v>2.889</v>
       </c>
       <c r="H118" t="n">
-        <v>3.119</v>
+        <v>2.887</v>
       </c>
       <c r="I118" t="n">
-        <v>3.121</v>
+        <v>2.889</v>
       </c>
       <c r="J118" t="n">
-        <v>3.736</v>
+        <v>3.732</v>
       </c>
       <c r="K118" t="n">
-        <v>3.733</v>
+        <v>3.729</v>
       </c>
       <c r="L118" t="n">
-        <v>3.737</v>
+        <v>3.734</v>
       </c>
       <c r="M118" t="n">
-        <v>3.735</v>
+        <v>3.731</v>
       </c>
       <c r="N118" t="n">
-        <v>3.737</v>
+        <v>3.734</v>
       </c>
       <c r="O118" t="n">
-        <v>3.119</v>
+        <v>2.887</v>
       </c>
       <c r="P118" t="n">
-        <v>3.121</v>
+        <v>2.889</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.121</v>
+        <v>2.889</v>
       </c>
       <c r="R118" t="n">
-        <v>3.116</v>
+        <v>2.884</v>
       </c>
       <c r="S118" t="n">
-        <v>3.736</v>
+        <v>3.732</v>
       </c>
       <c r="T118" t="n">
-        <v>3.737</v>
+        <v>3.734</v>
       </c>
       <c r="U118" t="n">
-        <v>3.737</v>
+        <v>3.734</v>
       </c>
       <c r="V118" t="n">
-        <v>3.733</v>
+        <v>3.729</v>
       </c>
       <c r="W118" t="inlineStr">
         <is>
@@ -14266,21 +14270,21 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y118" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA118" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
@@ -14306,58 +14310,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3.24</v>
+        <v>3.01</v>
       </c>
       <c r="F119" t="n">
-        <v>3.239</v>
+        <v>3.009</v>
       </c>
       <c r="G119" t="n">
-        <v>3.241</v>
+        <v>3.012</v>
       </c>
       <c r="H119" t="n">
-        <v>3.239</v>
+        <v>3.009</v>
       </c>
       <c r="I119" t="n">
-        <v>3.24</v>
+        <v>3.011</v>
       </c>
       <c r="J119" t="n">
+        <v>3.855</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="L119" t="n">
         <v>3.856</v>
       </c>
-      <c r="K119" t="n">
-        <v>3.855</v>
-      </c>
-      <c r="L119" t="n">
-        <v>3.857</v>
-      </c>
       <c r="M119" t="n">
-        <v>3.855</v>
+        <v>3.853</v>
       </c>
       <c r="N119" t="n">
-        <v>3.857</v>
+        <v>3.856</v>
       </c>
       <c r="O119" t="n">
-        <v>3.241</v>
+        <v>3.012</v>
       </c>
       <c r="P119" t="n">
-        <v>3.24</v>
+        <v>3.011</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.239</v>
+        <v>3.009</v>
       </c>
       <c r="R119" t="n">
-        <v>3.239</v>
+        <v>3.009</v>
       </c>
       <c r="S119" t="n">
-        <v>3.857</v>
+        <v>3.856</v>
       </c>
       <c r="T119" t="n">
         <v>3.856</v>
       </c>
       <c r="U119" t="n">
-        <v>3.855</v>
+        <v>3.853</v>
       </c>
       <c r="V119" t="n">
-        <v>3.855</v>
+        <v>3.853</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -14365,21 +14369,21 @@
         </is>
       </c>
       <c r="X119" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y119" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA119" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
@@ -14405,58 +14409,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3.409</v>
+        <v>3.175</v>
       </c>
       <c r="F120" t="n">
-        <v>3.339</v>
+        <v>3.107</v>
       </c>
       <c r="G120" t="n">
-        <v>3.478</v>
+        <v>3.233</v>
       </c>
       <c r="H120" t="n">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="I120" t="n">
-        <v>3.43</v>
+        <v>3.196</v>
       </c>
       <c r="J120" t="n">
-        <v>4.026</v>
+        <v>4.02</v>
       </c>
       <c r="K120" t="n">
-        <v>3.955</v>
+        <v>3.952</v>
       </c>
       <c r="L120" t="n">
-        <v>4.094</v>
+        <v>4.078</v>
       </c>
       <c r="M120" t="n">
-        <v>4.007</v>
+        <v>4.004</v>
       </c>
       <c r="N120" t="n">
-        <v>4.046</v>
+        <v>4.041</v>
       </c>
       <c r="O120" t="n">
-        <v>3.478</v>
+        <v>3.233</v>
       </c>
       <c r="P120" t="n">
-        <v>3.413</v>
+        <v>3.183</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.339</v>
+        <v>3.107</v>
       </c>
       <c r="R120" t="n">
-        <v>3.407</v>
+        <v>3.177</v>
       </c>
       <c r="S120" t="n">
-        <v>4.094</v>
+        <v>4.078</v>
       </c>
       <c r="T120" t="n">
-        <v>4.03</v>
+        <v>4.028</v>
       </c>
       <c r="U120" t="n">
-        <v>3.955</v>
+        <v>3.952</v>
       </c>
       <c r="V120" t="n">
-        <v>4.024</v>
+        <v>4.022</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -14464,21 +14468,21 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="Y120" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="AA120" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AB120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
@@ -14504,58 +14508,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="F121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="G121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="H121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="J121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="K121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="L121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="M121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="N121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="O121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="P121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="R121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="S121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="T121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="U121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="V121" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="W121" t="inlineStr">
         <is>
@@ -14563,25 +14567,25 @@
         </is>
       </c>
       <c r="X121" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y121" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA121" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -14603,58 +14607,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="F122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="G122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="H122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="I122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="J122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="K122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="L122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="M122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="N122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="O122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="P122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="R122" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="S122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="T122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="U122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="V122" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="W122" t="inlineStr">
         <is>
@@ -14662,25 +14666,25 @@
         </is>
       </c>
       <c r="X122" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y122" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA122" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -14702,58 +14706,58 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="F123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="G123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="H123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="I123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="J123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="K123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="L123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="M123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="N123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="O123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="P123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="Q123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="R123" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="S123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="T123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="U123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="V123" t="n">
-        <v>3.331</v>
+        <v>3.329</v>
       </c>
       <c r="W123" t="inlineStr">
         <is>
@@ -14761,25 +14765,25 @@
         </is>
       </c>
       <c r="X123" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y123" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA123" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -14801,58 +14805,58 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1.906</v>
+        <v>1.766</v>
       </c>
       <c r="F124" t="n">
-        <v>1.906</v>
+        <v>1.765</v>
       </c>
       <c r="G124" t="n">
-        <v>1.906</v>
+        <v>1.766</v>
       </c>
       <c r="H124" t="n">
-        <v>1.906</v>
+        <v>1.765</v>
       </c>
       <c r="I124" t="n">
-        <v>1.906</v>
+        <v>1.766</v>
       </c>
       <c r="J124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="K124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="L124" t="n">
-        <v>3.329</v>
+        <v>3.326</v>
       </c>
       <c r="M124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="N124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="O124" t="n">
-        <v>1.906</v>
+        <v>1.765</v>
       </c>
       <c r="P124" t="n">
-        <v>1.906</v>
+        <v>1.766</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.906</v>
+        <v>1.765</v>
       </c>
       <c r="R124" t="n">
-        <v>1.906</v>
+        <v>1.765</v>
       </c>
       <c r="S124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="T124" t="n">
-        <v>3.329</v>
+        <v>3.326</v>
       </c>
       <c r="U124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="V124" t="n">
-        <v>3.328</v>
+        <v>3.325</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -14860,25 +14864,25 @@
         </is>
       </c>
       <c r="X124" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y124" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA124" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -14900,19 +14904,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="F125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="G125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="H125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="I125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="J125" t="n">
         <v>3.319</v>
@@ -14930,16 +14934,16 @@
         <v>3.319</v>
       </c>
       <c r="O125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="P125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="R125" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="S125" t="n">
         <v>3.319</v>
@@ -14959,25 +14963,25 @@
         </is>
       </c>
       <c r="X125" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y125" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA125" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB125" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -14999,84 +15003,84 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1.884</v>
+        <v>1.743</v>
       </c>
       <c r="F126" t="n">
-        <v>1.877</v>
+        <v>1.738</v>
       </c>
       <c r="G126" t="n">
-        <v>1.889</v>
+        <v>1.748</v>
       </c>
       <c r="H126" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="I126" t="n">
-        <v>1.888</v>
+        <v>1.747</v>
       </c>
       <c r="J126" t="n">
-        <v>3.306</v>
+        <v>3.303</v>
       </c>
       <c r="K126" t="n">
+        <v>3.298</v>
+      </c>
+      <c r="L126" t="n">
+        <v>3.308</v>
+      </c>
+      <c r="M126" t="n">
         <v>3.3</v>
       </c>
-      <c r="L126" t="n">
-        <v>3.311</v>
-      </c>
-      <c r="M126" t="n">
-        <v>3.302</v>
-      </c>
       <c r="N126" t="n">
-        <v>3.311</v>
+        <v>3.307</v>
       </c>
       <c r="O126" t="n">
-        <v>1.889</v>
+        <v>1.748</v>
       </c>
       <c r="P126" t="n">
-        <v>1.888</v>
+        <v>1.747</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.877</v>
+        <v>1.738</v>
       </c>
       <c r="R126" t="n">
-        <v>1.881</v>
+        <v>1.74</v>
       </c>
       <c r="S126" t="n">
-        <v>3.311</v>
+        <v>3.308</v>
       </c>
       <c r="T126" t="n">
-        <v>3.31</v>
+        <v>3.307</v>
       </c>
       <c r="U126" t="n">
+        <v>3.298</v>
+      </c>
+      <c r="V126" t="n">
         <v>3.3</v>
       </c>
-      <c r="V126" t="n">
-        <v>3.303</v>
-      </c>
       <c r="W126" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="X126" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y126" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA126" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -15098,84 +15102,84 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1.867</v>
+        <v>1.728</v>
       </c>
       <c r="F127" t="n">
-        <v>1.866</v>
+        <v>1.727</v>
       </c>
       <c r="G127" t="n">
-        <v>1.87</v>
+        <v>1.731</v>
       </c>
       <c r="H127" t="n">
-        <v>1.866</v>
+        <v>1.727</v>
       </c>
       <c r="I127" t="n">
-        <v>1.868</v>
+        <v>1.729</v>
       </c>
       <c r="J127" t="n">
-        <v>3.29</v>
+        <v>3.288</v>
       </c>
       <c r="K127" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3.289</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="T127" t="n">
         <v>3.288</v>
       </c>
-      <c r="L127" t="n">
-        <v>3.292</v>
-      </c>
-      <c r="M127" t="n">
-        <v>3.289</v>
-      </c>
-      <c r="N127" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="O127" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P127" t="n">
-        <v>1.867</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>1.866</v>
-      </c>
-      <c r="R127" t="n">
-        <v>1.866</v>
-      </c>
-      <c r="S127" t="n">
-        <v>3.292</v>
-      </c>
-      <c r="T127" t="n">
-        <v>3.289</v>
-      </c>
       <c r="U127" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="V127" t="n">
         <v>3.288</v>
       </c>
-      <c r="V127" t="n">
-        <v>3.289</v>
-      </c>
       <c r="W127" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="X127" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="Y127" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA127" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -15197,82 +15201,84 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="F128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="G128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="H128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="I128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="J128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="K128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="L128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="M128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="N128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="O128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="P128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="Q128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="R128" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="S128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="T128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="U128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="V128" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X128" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y128" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA128" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15294,82 +15300,84 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6.817</v>
+        <v>6.015</v>
       </c>
       <c r="F129" t="n">
-        <v>6.816</v>
+        <v>6.014</v>
       </c>
       <c r="G129" t="n">
-        <v>6.817</v>
+        <v>6.015</v>
       </c>
       <c r="H129" t="n">
-        <v>6.816</v>
+        <v>6.014</v>
       </c>
       <c r="I129" t="n">
-        <v>6.817</v>
+        <v>6.015</v>
       </c>
       <c r="J129" t="n">
-        <v>6.817</v>
+        <v>6.494</v>
       </c>
       <c r="K129" t="n">
-        <v>6.816</v>
+        <v>6.494</v>
       </c>
       <c r="L129" t="n">
-        <v>6.817</v>
+        <v>6.495</v>
       </c>
       <c r="M129" t="n">
-        <v>6.816</v>
+        <v>6.494</v>
       </c>
       <c r="N129" t="n">
-        <v>6.817</v>
+        <v>6.494</v>
       </c>
       <c r="O129" t="n">
-        <v>6.816</v>
+        <v>6.015</v>
       </c>
       <c r="P129" t="n">
-        <v>6.817</v>
+        <v>6.015</v>
       </c>
       <c r="Q129" t="n">
-        <v>6.816</v>
+        <v>6.014</v>
       </c>
       <c r="R129" t="n">
-        <v>6.816</v>
+        <v>6.014</v>
       </c>
       <c r="S129" t="n">
-        <v>6.816</v>
+        <v>6.494</v>
       </c>
       <c r="T129" t="n">
-        <v>6.817</v>
+        <v>6.495</v>
       </c>
       <c r="U129" t="n">
-        <v>6.816</v>
+        <v>6.494</v>
       </c>
       <c r="V129" t="n">
-        <v>6.816</v>
+        <v>6.494</v>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X129" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y129" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA129" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB129" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15391,82 +15399,84 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6.854</v>
+        <v>6.203</v>
       </c>
       <c r="F130" t="n">
-        <v>6.852</v>
+        <v>6.191</v>
       </c>
       <c r="G130" t="n">
-        <v>6.857</v>
+        <v>6.229</v>
       </c>
       <c r="H130" t="n">
-        <v>6.852</v>
+        <v>6.192</v>
       </c>
       <c r="I130" t="n">
-        <v>6.854</v>
+        <v>6.206</v>
       </c>
       <c r="J130" t="n">
-        <v>6.854</v>
+        <v>6.682</v>
       </c>
       <c r="K130" t="n">
-        <v>6.852</v>
+        <v>6.67</v>
       </c>
       <c r="L130" t="n">
-        <v>6.857</v>
+        <v>6.709</v>
       </c>
       <c r="M130" t="n">
-        <v>6.852</v>
+        <v>6.672</v>
       </c>
       <c r="N130" t="n">
-        <v>6.854</v>
+        <v>6.686</v>
       </c>
       <c r="O130" t="n">
-        <v>6.852</v>
+        <v>6.199</v>
       </c>
       <c r="P130" t="n">
-        <v>6.857</v>
+        <v>6.229</v>
       </c>
       <c r="Q130" t="n">
-        <v>6.852</v>
+        <v>6.193</v>
       </c>
       <c r="R130" t="n">
-        <v>6.852</v>
+        <v>6.191</v>
       </c>
       <c r="S130" t="n">
-        <v>6.852</v>
+        <v>6.678</v>
       </c>
       <c r="T130" t="n">
-        <v>6.857</v>
+        <v>6.709</v>
       </c>
       <c r="U130" t="n">
-        <v>6.852</v>
+        <v>6.672</v>
       </c>
       <c r="V130" t="n">
-        <v>6.852</v>
+        <v>6.67</v>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X130" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y130" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA130" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB130" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15488,82 +15498,84 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6.864</v>
+        <v>6.186</v>
       </c>
       <c r="F131" t="n">
-        <v>6.851</v>
+        <v>6.112</v>
       </c>
       <c r="G131" t="n">
-        <v>6.903</v>
+        <v>6.3</v>
       </c>
       <c r="H131" t="n">
-        <v>6.851</v>
+        <v>6.132</v>
       </c>
       <c r="I131" t="n">
-        <v>6.865</v>
+        <v>6.221</v>
       </c>
       <c r="J131" t="n">
-        <v>6.864</v>
+        <v>6.666</v>
       </c>
       <c r="K131" t="n">
-        <v>6.851</v>
+        <v>6.591</v>
       </c>
       <c r="L131" t="n">
-        <v>6.903</v>
+        <v>6.779</v>
       </c>
       <c r="M131" t="n">
-        <v>6.851</v>
+        <v>6.612</v>
       </c>
       <c r="N131" t="n">
-        <v>6.865</v>
+        <v>6.7</v>
       </c>
       <c r="O131" t="n">
-        <v>6.852</v>
+        <v>6.195</v>
       </c>
       <c r="P131" t="n">
-        <v>6.903</v>
+        <v>6.3</v>
       </c>
       <c r="Q131" t="n">
-        <v>6.851</v>
+        <v>6.139</v>
       </c>
       <c r="R131" t="n">
-        <v>6.851</v>
+        <v>6.112</v>
       </c>
       <c r="S131" t="n">
-        <v>6.852</v>
+        <v>6.674</v>
       </c>
       <c r="T131" t="n">
-        <v>6.903</v>
+        <v>6.779</v>
       </c>
       <c r="U131" t="n">
-        <v>6.851</v>
+        <v>6.619</v>
       </c>
       <c r="V131" t="n">
-        <v>6.851</v>
+        <v>6.591</v>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X131" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y131" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA131" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB131" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15585,82 +15597,84 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6.844</v>
+        <v>6.124</v>
       </c>
       <c r="F132" t="n">
-        <v>6.801</v>
+        <v>6.007</v>
       </c>
       <c r="G132" t="n">
-        <v>6.903</v>
+        <v>6.301</v>
       </c>
       <c r="H132" t="n">
-        <v>6.815</v>
+        <v>6.015</v>
       </c>
       <c r="I132" t="n">
-        <v>6.865</v>
+        <v>6.203</v>
       </c>
       <c r="J132" t="n">
-        <v>6.844</v>
+        <v>6.603</v>
       </c>
       <c r="K132" t="n">
-        <v>6.801</v>
+        <v>6.486</v>
       </c>
       <c r="L132" t="n">
-        <v>6.903</v>
+        <v>6.78</v>
       </c>
       <c r="M132" t="n">
-        <v>6.815</v>
+        <v>6.494</v>
       </c>
       <c r="N132" t="n">
-        <v>6.865</v>
+        <v>6.682</v>
       </c>
       <c r="O132" t="n">
-        <v>6.852</v>
+        <v>6.171</v>
       </c>
       <c r="P132" t="n">
-        <v>6.903</v>
+        <v>6.301</v>
       </c>
       <c r="Q132" t="n">
-        <v>6.82</v>
+        <v>6.018</v>
       </c>
       <c r="R132" t="n">
-        <v>6.801</v>
+        <v>6.007</v>
       </c>
       <c r="S132" t="n">
-        <v>6.852</v>
+        <v>6.65</v>
       </c>
       <c r="T132" t="n">
-        <v>6.903</v>
+        <v>6.78</v>
       </c>
       <c r="U132" t="n">
-        <v>6.82</v>
+        <v>6.497</v>
       </c>
       <c r="V132" t="n">
-        <v>6.801</v>
+        <v>6.486</v>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X132" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y132" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA132" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB132" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15682,82 +15696,84 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6.768</v>
+        <v>6.137</v>
       </c>
       <c r="F133" t="n">
-        <v>6.485</v>
+        <v>5.911</v>
       </c>
       <c r="G133" t="n">
-        <v>6.924</v>
+        <v>6.333</v>
       </c>
       <c r="H133" t="n">
-        <v>6.683</v>
+        <v>5.968</v>
       </c>
       <c r="I133" t="n">
-        <v>6.917</v>
+        <v>6.322</v>
       </c>
       <c r="J133" t="n">
-        <v>6.768</v>
+        <v>6.617</v>
       </c>
       <c r="K133" t="n">
-        <v>6.485</v>
+        <v>6.391</v>
       </c>
       <c r="L133" t="n">
-        <v>6.924</v>
+        <v>6.812</v>
       </c>
       <c r="M133" t="n">
-        <v>6.683</v>
+        <v>6.448</v>
       </c>
       <c r="N133" t="n">
-        <v>6.917</v>
+        <v>6.801</v>
       </c>
       <c r="O133" t="n">
-        <v>6.924</v>
+        <v>6.333</v>
       </c>
       <c r="P133" t="n">
-        <v>6.915</v>
+        <v>6.318</v>
       </c>
       <c r="Q133" t="n">
-        <v>6.748</v>
+        <v>5.987</v>
       </c>
       <c r="R133" t="n">
-        <v>6.485</v>
+        <v>5.911</v>
       </c>
       <c r="S133" t="n">
-        <v>6.924</v>
+        <v>6.812</v>
       </c>
       <c r="T133" t="n">
-        <v>6.915</v>
+        <v>6.798</v>
       </c>
       <c r="U133" t="n">
-        <v>6.748</v>
+        <v>6.467</v>
       </c>
       <c r="V133" t="n">
-        <v>6.485</v>
+        <v>6.391</v>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X133" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y133" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA133" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB133" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15779,82 +15795,84 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6.763</v>
+        <v>6.17</v>
       </c>
       <c r="F134" t="n">
-        <v>6.41</v>
+        <v>5.845</v>
       </c>
       <c r="G134" t="n">
-        <v>7.025</v>
+        <v>6.525</v>
       </c>
       <c r="H134" t="n">
-        <v>6.568</v>
+        <v>5.916</v>
       </c>
       <c r="I134" t="n">
-        <v>7.003</v>
+        <v>6.411</v>
       </c>
       <c r="J134" t="n">
-        <v>6.763</v>
+        <v>6.65</v>
       </c>
       <c r="K134" t="n">
-        <v>6.41</v>
+        <v>6.324</v>
       </c>
       <c r="L134" t="n">
-        <v>7.025</v>
+        <v>7.005</v>
       </c>
       <c r="M134" t="n">
-        <v>6.568</v>
+        <v>6.395</v>
       </c>
       <c r="N134" t="n">
-        <v>7.003</v>
+        <v>6.89</v>
       </c>
       <c r="O134" t="n">
-        <v>7.025</v>
+        <v>6.525</v>
       </c>
       <c r="P134" t="n">
-        <v>6.995</v>
+        <v>6.372</v>
       </c>
       <c r="Q134" t="n">
-        <v>6.621</v>
+        <v>5.939</v>
       </c>
       <c r="R134" t="n">
-        <v>6.41</v>
+        <v>5.845</v>
       </c>
       <c r="S134" t="n">
-        <v>7.025</v>
+        <v>7.005</v>
       </c>
       <c r="T134" t="n">
-        <v>6.995</v>
+        <v>6.852</v>
       </c>
       <c r="U134" t="n">
-        <v>6.621</v>
+        <v>6.419</v>
       </c>
       <c r="V134" t="n">
-        <v>6.41</v>
+        <v>6.324</v>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X134" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="Y134" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA134" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="AB134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15876,82 +15894,84 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="F135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="G135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="H135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="I135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="J135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="K135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="L135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="M135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="N135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="O135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="P135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="Q135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="R135" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="S135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="T135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="U135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="V135" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X135" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y135" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA135" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB135" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -15973,82 +15993,84 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="F136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="G136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="H136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="I136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="J136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="K136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="L136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="M136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="N136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="O136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="P136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="Q136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="R136" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="S136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="T136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="U136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="V136" t="n">
-        <v>128.658</v>
+        <v>128.643</v>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X136" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y136" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA136" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB136" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -16070,82 +16092,84 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="F137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="G137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="H137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="I137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="J137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="K137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="L137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="M137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="N137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="O137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="P137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="Q137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="R137" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="S137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="T137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="U137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="V137" t="n">
-        <v>128.803</v>
+        <v>128.799</v>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X137" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y137" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA137" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB137" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -16167,82 +16191,84 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="F138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="G138" t="n">
-        <v>129.05</v>
+        <v>129.646</v>
       </c>
       <c r="H138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="I138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="J138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="K138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="L138" t="n">
-        <v>129.05</v>
+        <v>129.042</v>
       </c>
       <c r="M138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="N138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="O138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="P138" t="n">
-        <v>129.05</v>
+        <v>129.646</v>
       </c>
       <c r="Q138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="R138" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="S138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="T138" t="n">
-        <v>129.05</v>
+        <v>129.042</v>
       </c>
       <c r="U138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="V138" t="n">
-        <v>129.049</v>
+        <v>129.041</v>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X138" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y138" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA138" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB138" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -16264,82 +16290,84 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>129.193</v>
+        <v>129.787</v>
       </c>
       <c r="F139" t="n">
-        <v>129.191</v>
+        <v>129.784</v>
       </c>
       <c r="G139" t="n">
-        <v>129.198</v>
+        <v>129.791</v>
       </c>
       <c r="H139" t="n">
-        <v>129.191</v>
+        <v>129.784</v>
       </c>
       <c r="I139" t="n">
-        <v>129.195</v>
+        <v>129.788</v>
       </c>
       <c r="J139" t="n">
-        <v>129.193</v>
+        <v>129.182</v>
       </c>
       <c r="K139" t="n">
-        <v>129.191</v>
+        <v>129.179</v>
       </c>
       <c r="L139" t="n">
-        <v>129.198</v>
+        <v>129.186</v>
       </c>
       <c r="M139" t="n">
-        <v>129.191</v>
+        <v>129.179</v>
       </c>
       <c r="N139" t="n">
-        <v>129.195</v>
+        <v>129.184</v>
       </c>
       <c r="O139" t="n">
-        <v>129.194</v>
+        <v>129.788</v>
       </c>
       <c r="P139" t="n">
-        <v>129.198</v>
+        <v>129.791</v>
       </c>
       <c r="Q139" t="n">
-        <v>129.191</v>
+        <v>129.784</v>
       </c>
       <c r="R139" t="n">
-        <v>129.191</v>
+        <v>129.784</v>
       </c>
       <c r="S139" t="n">
-        <v>129.194</v>
+        <v>129.183</v>
       </c>
       <c r="T139" t="n">
-        <v>129.198</v>
+        <v>129.186</v>
       </c>
       <c r="U139" t="n">
-        <v>129.191</v>
+        <v>129.18</v>
       </c>
       <c r="V139" t="n">
-        <v>129.191</v>
+        <v>129.179</v>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X139" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y139" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA139" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB139" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -16361,82 +16389,84 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>129.193</v>
+        <v>129.783</v>
       </c>
       <c r="F140" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="G140" t="n">
+        <v>129.795</v>
+      </c>
+      <c r="H140" t="n">
+        <v>129.777</v>
+      </c>
+      <c r="I140" t="n">
+        <v>129.789</v>
+      </c>
+      <c r="J140" t="n">
+        <v>129.178</v>
+      </c>
+      <c r="K140" t="n">
+        <v>129.165</v>
+      </c>
+      <c r="L140" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="M140" t="n">
+        <v>129.172</v>
+      </c>
+      <c r="N140" t="n">
+        <v>129.184</v>
+      </c>
+      <c r="O140" t="n">
+        <v>129.787</v>
+      </c>
+      <c r="P140" t="n">
+        <v>129.795</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>129.78</v>
+      </c>
+      <c r="R140" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="S140" t="n">
         <v>129.182</v>
       </c>
-      <c r="G140" t="n">
-        <v>129.209</v>
-      </c>
-      <c r="H140" t="n">
-        <v>129.186</v>
-      </c>
-      <c r="I140" t="n">
-        <v>129.197</v>
-      </c>
-      <c r="J140" t="n">
-        <v>129.193</v>
-      </c>
-      <c r="K140" t="n">
-        <v>129.182</v>
-      </c>
-      <c r="L140" t="n">
-        <v>129.209</v>
-      </c>
-      <c r="M140" t="n">
-        <v>129.186</v>
-      </c>
-      <c r="N140" t="n">
-        <v>129.197</v>
-      </c>
-      <c r="O140" t="n">
-        <v>129.194</v>
-      </c>
-      <c r="P140" t="n">
-        <v>129.209</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>129.187</v>
-      </c>
-      <c r="R140" t="n">
-        <v>129.182</v>
-      </c>
-      <c r="S140" t="n">
-        <v>129.194</v>
-      </c>
       <c r="T140" t="n">
-        <v>129.209</v>
+        <v>129.19</v>
       </c>
       <c r="U140" t="n">
-        <v>129.187</v>
+        <v>129.175</v>
       </c>
       <c r="V140" t="n">
-        <v>129.182</v>
+        <v>129.165</v>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X140" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y140" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA140" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB140" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -16458,82 +16488,84 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>129.191</v>
+        <v>129.759</v>
       </c>
       <c r="F141" t="n">
-        <v>129.091</v>
+        <v>129.664</v>
       </c>
       <c r="G141" t="n">
-        <v>129.272</v>
+        <v>129.838</v>
       </c>
       <c r="H141" t="n">
-        <v>129.141</v>
+        <v>129.714</v>
       </c>
       <c r="I141" t="n">
-        <v>129.251</v>
+        <v>129.814</v>
       </c>
       <c r="J141" t="n">
-        <v>129.191</v>
+        <v>129.155</v>
       </c>
       <c r="K141" t="n">
-        <v>129.091</v>
+        <v>129.059</v>
       </c>
       <c r="L141" t="n">
-        <v>129.272</v>
+        <v>129.233</v>
       </c>
       <c r="M141" t="n">
-        <v>129.141</v>
+        <v>129.109</v>
       </c>
       <c r="N141" t="n">
-        <v>129.251</v>
+        <v>129.209</v>
       </c>
       <c r="O141" t="n">
-        <v>129.245</v>
+        <v>129.805</v>
       </c>
       <c r="P141" t="n">
-        <v>129.272</v>
+        <v>129.838</v>
       </c>
       <c r="Q141" t="n">
-        <v>129.158</v>
+        <v>129.73</v>
       </c>
       <c r="R141" t="n">
-        <v>129.091</v>
+        <v>129.664</v>
       </c>
       <c r="S141" t="n">
-        <v>129.245</v>
+        <v>129.201</v>
       </c>
       <c r="T141" t="n">
-        <v>129.272</v>
+        <v>129.233</v>
       </c>
       <c r="U141" t="n">
-        <v>129.158</v>
+        <v>129.125</v>
       </c>
       <c r="V141" t="n">
-        <v>129.091</v>
+        <v>129.059</v>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X141" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y141" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="AA141" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="AB141" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -17104,25 +17136,25 @@
         <v>9039635</v>
       </c>
       <c r="C18" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="D18" t="n">
-        <v>2.803</v>
+        <v>2.569</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9</v>
+        <v>2.669</v>
       </c>
       <c r="F18" t="n">
-        <v>2.995</v>
+        <v>2.765</v>
       </c>
       <c r="G18" t="n">
-        <v>3.119</v>
+        <v>2.887</v>
       </c>
       <c r="H18" t="n">
-        <v>3.24</v>
+        <v>3.01</v>
       </c>
       <c r="I18" t="n">
-        <v>3.409</v>
+        <v>3.175</v>
       </c>
     </row>
     <row r="19">
@@ -17135,25 +17167,25 @@
         <v>9038269</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="D19" t="n">
-        <v>1.914</v>
+        <v>1.772</v>
       </c>
       <c r="E19" t="n">
-        <v>1.908</v>
+        <v>1.769</v>
       </c>
       <c r="F19" t="n">
-        <v>1.906</v>
+        <v>1.766</v>
       </c>
       <c r="G19" t="n">
-        <v>1.897</v>
+        <v>1.759</v>
       </c>
       <c r="H19" t="n">
-        <v>1.884</v>
+        <v>1.743</v>
       </c>
       <c r="I19" t="n">
-        <v>1.867</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="20">
@@ -17166,25 +17198,25 @@
         <v>9036459</v>
       </c>
       <c r="C20" t="n">
-        <v>6.43</v>
+        <v>5.87</v>
       </c>
       <c r="D20" t="n">
-        <v>6.817</v>
+        <v>6.015</v>
       </c>
       <c r="E20" t="n">
-        <v>6.854</v>
+        <v>6.203</v>
       </c>
       <c r="F20" t="n">
-        <v>6.864</v>
+        <v>6.186</v>
       </c>
       <c r="G20" t="n">
-        <v>6.844</v>
+        <v>6.124</v>
       </c>
       <c r="H20" t="n">
-        <v>6.768</v>
+        <v>6.137</v>
       </c>
       <c r="I20" t="n">
-        <v>6.763</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="21">
@@ -17197,25 +17229,25 @@
         <v>9046779</v>
       </c>
       <c r="C21" t="n">
-        <v>128.581</v>
+        <v>129.15</v>
       </c>
       <c r="D21" t="n">
-        <v>128.658</v>
+        <v>129.248</v>
       </c>
       <c r="E21" t="n">
-        <v>128.803</v>
+        <v>129.404</v>
       </c>
       <c r="F21" t="n">
-        <v>129.049</v>
+        <v>129.646</v>
       </c>
       <c r="G21" t="n">
-        <v>129.193</v>
+        <v>129.787</v>
       </c>
       <c r="H21" t="n">
-        <v>129.193</v>
+        <v>129.783</v>
       </c>
       <c r="I21" t="n">
-        <v>129.191</v>
+        <v>129.759</v>
       </c>
     </row>
   </sheetData>
@@ -17395,30 +17427,34 @@
         <v>46307</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="E4" t="n">
-        <v>6.38</v>
+        <v>5.87</v>
       </c>
       <c r="F4" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>6.349</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.479</v>
+      </c>
       <c r="H4" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>5.87</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>
@@ -17567,25 +17603,25 @@
         <v>46307</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="F8" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.422</v>
+        <v>-1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -17594,7 +17630,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ajuste aplicado</t>
+          <t>Offset alto: -1.56 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -17655,25 +17691,25 @@
         <v>46307</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="E10" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="F10" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.616</v>
+        <v>-0.845</v>
       </c>
       <c r="H10" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -18087,30 +18123,34 @@
         <v>46307</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46297</v>
+        <v>46307</v>
       </c>
       <c r="E20" t="n">
-        <v>129.46</v>
+        <v>129.15</v>
       </c>
       <c r="F20" t="n">
-        <v>128.581</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>128.545</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.605</v>
+      </c>
       <c r="H20" t="n">
-        <v>128.581</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>129.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Observado muy antiguo para ajuste: 10 días</t>
+          <t>Ajuste aplicado</t>
         </is>
       </c>
     </row>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -993,19 +993,19 @@
         <v>3.078</v>
       </c>
       <c r="H6" t="n">
-        <v>4.381</v>
+        <v>4.38</v>
       </c>
       <c r="I6" t="n">
-        <v>8.157</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>4.04</v>
       </c>
       <c r="K6" t="n">
-        <v>5.832</v>
+        <v>5.826</v>
       </c>
       <c r="L6" t="n">
-        <v>1.792</v>
+        <v>1.786</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1043,16 +1043,16 @@
         <v>10053</v>
       </c>
       <c r="V6" t="n">
-        <v>0.153</v>
+        <v>0.855</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.611</v>
+        <v>0.71</v>
       </c>
       <c r="X6" t="n">
-        <v>0.151</v>
+        <v>0.855</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.975</v>
+        <v>1.616</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Buena</t>
         </is>
       </c>
     </row>
@@ -6121,37 +6121,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.832</v>
+        <v>5.826</v>
       </c>
       <c r="F36" t="n">
         <v>3.842</v>
       </c>
       <c r="G36" t="n">
-        <v>8.157</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="H36" t="n">
         <v>4.06</v>
       </c>
       <c r="I36" t="n">
-        <v>7.435</v>
+        <v>7.43</v>
       </c>
       <c r="J36" t="n">
-        <v>3.492</v>
+        <v>3.486</v>
       </c>
       <c r="K36" t="n">
         <v>1.502</v>
       </c>
       <c r="L36" t="n">
-        <v>5.817</v>
+        <v>5.796</v>
       </c>
       <c r="M36" t="n">
         <v>1.72</v>
       </c>
       <c r="N36" t="n">
-        <v>5.095</v>
+        <v>5.09</v>
       </c>
       <c r="O36" t="n">
-        <v>8.157</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="P36" t="n">
         <v>7.194</v>
@@ -6163,7 +6163,7 @@
         <v>3.842</v>
       </c>
       <c r="S36" t="n">
-        <v>5.817</v>
+        <v>5.796</v>
       </c>
       <c r="T36" t="n">
         <v>4.854</v>
@@ -16782,7 +16782,7 @@
         <v>5.262</v>
       </c>
       <c r="I6" t="n">
-        <v>5.832</v>
+        <v>5.826</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -1898,19 +1898,19 @@
         <v>4.567</v>
       </c>
       <c r="H15" t="n">
-        <v>4.855</v>
+        <v>4.856</v>
       </c>
       <c r="I15" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="J15" t="n">
         <v>4.568</v>
       </c>
       <c r="K15" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="L15" t="n">
-        <v>0.866</v>
+        <v>0.87</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>46315</v>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y93" s="1" t="n">
         <v>46315</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y94" s="1" t="n">
         <v>46315</v>
@@ -11934,58 +11934,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="F95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="G95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="H95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="I95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="J95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="K95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="L95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="M95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="N95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="O95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="P95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="R95" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="S95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="T95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="U95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="V95" t="n">
-        <v>3.723</v>
+        <v>3.724</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y95" s="1" t="n">
         <v>46315</v>
@@ -12033,58 +12033,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4.752</v>
+        <v>4.755</v>
       </c>
       <c r="F96" t="n">
-        <v>4.752</v>
+        <v>4.755</v>
       </c>
       <c r="G96" t="n">
-        <v>4.753</v>
+        <v>4.755</v>
       </c>
       <c r="H96" t="n">
-        <v>4.752</v>
+        <v>4.755</v>
       </c>
       <c r="I96" t="n">
-        <v>4.753</v>
+        <v>4.755</v>
       </c>
       <c r="J96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="K96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="L96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="M96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="N96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="O96" t="n">
-        <v>4.753</v>
+        <v>4.755</v>
       </c>
       <c r="P96" t="n">
-        <v>4.753</v>
+        <v>4.755</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.753</v>
+        <v>4.755</v>
       </c>
       <c r="R96" t="n">
-        <v>4.752</v>
+        <v>4.755</v>
       </c>
       <c r="S96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="T96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="U96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="V96" t="n">
-        <v>3.811</v>
+        <v>3.814</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="X96" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y96" s="1" t="n">
         <v>46315</v>
@@ -12147,19 +12147,19 @@
         <v>4.887</v>
       </c>
       <c r="J97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="K97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="L97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="M97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="N97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="O97" t="n">
         <v>4.887</v>
@@ -12174,16 +12174,16 @@
         <v>4.887</v>
       </c>
       <c r="S97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="T97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="U97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="V97" t="n">
-        <v>3.945</v>
+        <v>3.946</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y97" s="1" t="n">
         <v>46315</v>
@@ -12231,58 +12231,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="F98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="G98" t="n">
         <v>5.089</v>
       </c>
       <c r="H98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="I98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="J98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="K98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="L98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="M98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="N98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="O98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="P98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="Q98" t="n">
         <v>5.089</v>
       </c>
       <c r="R98" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="S98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="T98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="U98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="V98" t="n">
-        <v>4.147</v>
+        <v>4.148</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="X98" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y98" s="1" t="n">
         <v>46315</v>
@@ -12330,58 +12330,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="F99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="G99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="H99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="I99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="J99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="K99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="L99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="M99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="N99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="O99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="P99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="R99" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
       <c r="S99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="T99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="U99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="V99" t="n">
-        <v>4.492</v>
+        <v>4.497</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="X99" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y99" s="1" t="n">
         <v>46315</v>
@@ -17049,19 +17049,19 @@
         <v>4.592</v>
       </c>
       <c r="E15" t="n">
-        <v>4.664</v>
+        <v>4.665</v>
       </c>
       <c r="F15" t="n">
-        <v>4.752</v>
+        <v>4.755</v>
       </c>
       <c r="G15" t="n">
         <v>4.887</v>
       </c>
       <c r="H15" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="I15" t="n">
-        <v>5.434</v>
+        <v>5.438</v>
       </c>
     </row>
     <row r="16">
@@ -17788,7 +17788,7 @@
         <v>3.626</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>4.568</v>

--- a/outputs/pronostico_nivel_7dias_estaciones.xlsx
+++ b/outputs/pronostico_nivel_7dias_estaciones.xlsx
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="P3" s="1" t="n">
         <v>46315</v>
@@ -791,7 +791,7 @@
         <v>3.617</v>
       </c>
       <c r="H4" t="n">
-        <v>3.793</v>
+        <v>3.792</v>
       </c>
       <c r="I4" t="n">
         <v>3.89</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6.267</v>
+        <v>6.269</v>
       </c>
       <c r="H5" t="n">
-        <v>6.636</v>
+        <v>6.637</v>
       </c>
       <c r="I5" t="n">
         <v>6.975</v>
@@ -901,10 +901,10 @@
         <v>6.975</v>
       </c>
       <c r="K5" t="n">
-        <v>6.274</v>
+        <v>6.275</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.701</v>
+        <v>-0.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>46315</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -990,22 +990,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.577</v>
+        <v>3.574</v>
       </c>
       <c r="H6" t="n">
-        <v>4.207</v>
+        <v>4.205</v>
       </c>
       <c r="I6" t="n">
-        <v>4.749</v>
+        <v>4.744</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.884</v>
+        <v>3.881</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.216</v>
+        <v>-0.219</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>46315</v>
@@ -1043,13 +1043,13 @@
         <v>16728</v>
       </c>
       <c r="V6" t="n">
-        <v>0.715</v>
+        <v>0.716</v>
       </c>
       <c r="W6" t="n">
         <v>0.431</v>
       </c>
       <c r="X6" t="n">
-        <v>0.715</v>
+        <v>0.716</v>
       </c>
       <c r="Y6" t="n">
         <v>1.869</v>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6.018</v>
+        <v>6.017</v>
       </c>
       <c r="H8" t="n">
-        <v>6.206</v>
+        <v>6.205</v>
       </c>
       <c r="I8" t="n">
         <v>6.4</v>
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="H9" t="n">
-        <v>5.153</v>
+        <v>5.157</v>
       </c>
       <c r="I9" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="J9" t="n">
         <v>5.103</v>
       </c>
       <c r="K9" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.248</v>
+        <v>0.253</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>46315</v>
@@ -1395,19 +1395,19 @@
         <v>4.612</v>
       </c>
       <c r="H10" t="n">
-        <v>4.701</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="J10" t="n">
         <v>4.612</v>
       </c>
       <c r="K10" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="L10" t="n">
-        <v>0.222</v>
+        <v>0.221</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>46315</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.124</v>
+        <v>2.126</v>
       </c>
       <c r="H12" t="n">
-        <v>3.31</v>
+        <v>3.309</v>
       </c>
       <c r="I12" t="n">
         <v>3.649</v>
@@ -1606,10 +1606,10 @@
         <v>3.478</v>
       </c>
       <c r="K12" t="n">
-        <v>2.602</v>
+        <v>2.603</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.876</v>
+        <v>-0.875</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>46315</v>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5.057</v>
+        <v>5.056</v>
       </c>
       <c r="H13" t="n">
-        <v>5.206</v>
+        <v>5.204</v>
       </c>
       <c r="I13" t="n">
         <v>5.495</v>
@@ -1898,19 +1898,19 @@
         <v>4.567</v>
       </c>
       <c r="H15" t="n">
-        <v>4.856</v>
+        <v>4.858</v>
       </c>
       <c r="I15" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="J15" t="n">
         <v>4.568</v>
       </c>
       <c r="K15" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="L15" t="n">
-        <v>0.87</v>
+        <v>0.874</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>46315</v>
@@ -1999,7 +1999,7 @@
         <v>5.445</v>
       </c>
       <c r="H16" t="n">
-        <v>5.572</v>
+        <v>5.571</v>
       </c>
       <c r="I16" t="n">
         <v>5.793</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>46315</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U16" t="n">
@@ -2097,22 +2097,22 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3.407</v>
+        <v>3.654</v>
       </c>
       <c r="H17" t="n">
-        <v>4.233</v>
+        <v>4.482</v>
       </c>
       <c r="I17" t="n">
-        <v>4.469</v>
+        <v>4.719</v>
       </c>
       <c r="J17" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="K17" t="n">
-        <v>3.719</v>
+        <v>3.968</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.721</v>
+        <v>-0.722</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>46315</v>
@@ -2136,14 +2136,14 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -2201,7 +2201,7 @@
         <v>1.95</v>
       </c>
       <c r="H18" t="n">
-        <v>2.067</v>
+        <v>2.066</v>
       </c>
       <c r="I18" t="n">
         <v>2.184</v>
@@ -2210,10 +2210,10 @@
         <v>1.95</v>
       </c>
       <c r="K18" t="n">
-        <v>2.167</v>
+        <v>2.166</v>
       </c>
       <c r="L18" t="n">
-        <v>0.217</v>
+        <v>0.216</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>46315</v>
@@ -2260,7 +2260,7 @@
         <v>0.793</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.962</v>
+        <v>1.961</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2302,19 +2302,19 @@
         <v>1.481</v>
       </c>
       <c r="H19" t="n">
-        <v>1.536</v>
+        <v>1.535</v>
       </c>
       <c r="I19" t="n">
-        <v>1.653</v>
+        <v>1.651</v>
       </c>
       <c r="J19" t="n">
         <v>1.51</v>
       </c>
       <c r="K19" t="n">
-        <v>1.649</v>
+        <v>1.648</v>
       </c>
       <c r="L19" t="n">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>46315</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>46315</v>
@@ -3463,19 +3463,19 @@
         <v>3.23</v>
       </c>
       <c r="J9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="K9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="L9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="M9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="N9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="O9" t="n">
         <v>3.23</v>
@@ -3490,16 +3490,16 @@
         <v>3.23</v>
       </c>
       <c r="S9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="T9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="U9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="V9" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y9" s="1" t="n">
         <v>46315</v>
@@ -3562,7 +3562,7 @@
         <v>3.226</v>
       </c>
       <c r="J10" t="n">
-        <v>5.566</v>
+        <v>5.565</v>
       </c>
       <c r="K10" t="n">
         <v>5.565</v>
@@ -3571,7 +3571,7 @@
         <v>5.566</v>
       </c>
       <c r="M10" t="n">
-        <v>5.566</v>
+        <v>5.565</v>
       </c>
       <c r="N10" t="n">
         <v>5.566</v>
@@ -3589,13 +3589,13 @@
         <v>3.226</v>
       </c>
       <c r="S10" t="n">
-        <v>5.566</v>
+        <v>5.565</v>
       </c>
       <c r="T10" t="n">
         <v>5.566</v>
       </c>
       <c r="U10" t="n">
-        <v>5.566</v>
+        <v>5.565</v>
       </c>
       <c r="V10" t="n">
         <v>5.565</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>46315</v>
@@ -3661,19 +3661,19 @@
         <v>3.229</v>
       </c>
       <c r="J11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="K11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="L11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="M11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="N11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="O11" t="n">
         <v>3.229</v>
@@ -3688,16 +3688,16 @@
         <v>3.229</v>
       </c>
       <c r="S11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="T11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="U11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="V11" t="n">
-        <v>5.569</v>
+        <v>5.568</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>46315</v>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.239</v>
+        <v>3.24</v>
       </c>
       <c r="F12" t="n">
         <v>3.239</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24</v>
+        <v>3.241</v>
       </c>
       <c r="H12" t="n">
         <v>3.239</v>
@@ -3763,7 +3763,7 @@
         <v>5.579</v>
       </c>
       <c r="K12" t="n">
-        <v>5.579</v>
+        <v>5.578</v>
       </c>
       <c r="L12" t="n">
         <v>5.58</v>
@@ -3778,13 +3778,13 @@
         <v>3.239</v>
       </c>
       <c r="P12" t="n">
-        <v>3.239</v>
+        <v>3.24</v>
       </c>
       <c r="Q12" t="n">
         <v>3.239</v>
       </c>
       <c r="R12" t="n">
-        <v>3.24</v>
+        <v>3.241</v>
       </c>
       <c r="S12" t="n">
         <v>5.579</v>
@@ -3793,7 +3793,7 @@
         <v>5.579</v>
       </c>
       <c r="U12" t="n">
-        <v>5.579</v>
+        <v>5.578</v>
       </c>
       <c r="V12" t="n">
         <v>5.58</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>46315</v>
@@ -3862,7 +3862,7 @@
         <v>5.604</v>
       </c>
       <c r="K13" t="n">
-        <v>5.603</v>
+        <v>5.602</v>
       </c>
       <c r="L13" t="n">
         <v>5.606</v>
@@ -3871,13 +3871,13 @@
         <v>5.603</v>
       </c>
       <c r="N13" t="n">
-        <v>5.605</v>
+        <v>5.604</v>
       </c>
       <c r="O13" t="n">
         <v>3.264</v>
       </c>
       <c r="P13" t="n">
-        <v>3.264</v>
+        <v>3.265</v>
       </c>
       <c r="Q13" t="n">
         <v>3.263</v>
@@ -3892,7 +3892,7 @@
         <v>5.604</v>
       </c>
       <c r="U13" t="n">
-        <v>5.603</v>
+        <v>5.602</v>
       </c>
       <c r="V13" t="n">
         <v>5.606</v>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>46315</v>
@@ -3949,7 +3949,7 @@
         <v>3.294</v>
       </c>
       <c r="G14" t="n">
-        <v>3.309</v>
+        <v>3.308</v>
       </c>
       <c r="H14" t="n">
         <v>3.295</v>
@@ -3958,19 +3958,19 @@
         <v>3.301</v>
       </c>
       <c r="J14" t="n">
-        <v>5.639</v>
+        <v>5.638</v>
       </c>
       <c r="K14" t="n">
         <v>5.634</v>
       </c>
       <c r="L14" t="n">
-        <v>5.649</v>
+        <v>5.647</v>
       </c>
       <c r="M14" t="n">
         <v>5.635</v>
       </c>
       <c r="N14" t="n">
-        <v>5.641</v>
+        <v>5.64</v>
       </c>
       <c r="O14" t="n">
         <v>3.296</v>
@@ -3982,10 +3982,10 @@
         <v>3.294</v>
       </c>
       <c r="R14" t="n">
-        <v>3.309</v>
+        <v>3.308</v>
       </c>
       <c r="S14" t="n">
-        <v>5.636</v>
+        <v>5.635</v>
       </c>
       <c r="T14" t="n">
         <v>5.638</v>
@@ -3994,7 +3994,7 @@
         <v>5.634</v>
       </c>
       <c r="V14" t="n">
-        <v>5.649</v>
+        <v>5.647</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>46315</v>
@@ -4051,31 +4051,31 @@
         <v>3.357</v>
       </c>
       <c r="H15" t="n">
+        <v>3.351</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.354</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.692</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.689</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.696</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.691</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.693</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.352</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.355</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.693</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5.697</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.692</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.694</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>3.353</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.354</v>
       </c>
       <c r="Q15" t="n">
         <v>3.35</v>
@@ -4084,16 +4084,16 @@
         <v>3.357</v>
       </c>
       <c r="S15" t="n">
+        <v>5.691</v>
+      </c>
+      <c r="T15" t="n">
         <v>5.692</v>
       </c>
-      <c r="T15" t="n">
-        <v>5.694</v>
-      </c>
       <c r="U15" t="n">
-        <v>5.69</v>
+        <v>5.689</v>
       </c>
       <c r="V15" t="n">
-        <v>5.697</v>
+        <v>5.696</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>46315</v>
@@ -4156,19 +4156,19 @@
         <v>3.618</v>
       </c>
       <c r="J16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="K16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="L16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="M16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="N16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="O16" t="n">
         <v>3.618</v>
@@ -4183,16 +4183,16 @@
         <v>3.617</v>
       </c>
       <c r="S16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="T16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="U16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="V16" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>5.765</v>
       </c>
       <c r="K17" t="n">
-        <v>5.763</v>
+        <v>5.762</v>
       </c>
       <c r="L17" t="n">
         <v>5.767</v>
@@ -4267,7 +4267,7 @@
         <v>5.764</v>
       </c>
       <c r="N17" t="n">
-        <v>5.767</v>
+        <v>5.766</v>
       </c>
       <c r="O17" t="n">
         <v>3.799</v>
@@ -4282,16 +4282,16 @@
         <v>3.795</v>
       </c>
       <c r="S17" t="n">
-        <v>5.767</v>
+        <v>5.766</v>
       </c>
       <c r="T17" t="n">
         <v>5.767</v>
       </c>
       <c r="U17" t="n">
-        <v>5.765</v>
+        <v>5.764</v>
       </c>
       <c r="V17" t="n">
-        <v>5.763</v>
+        <v>5.762</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -4339,31 +4339,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.868</v>
+        <v>3.867</v>
       </c>
       <c r="F18" t="n">
-        <v>3.848</v>
+        <v>3.845</v>
       </c>
       <c r="G18" t="n">
         <v>3.885</v>
       </c>
       <c r="H18" t="n">
-        <v>3.854</v>
+        <v>3.853</v>
       </c>
       <c r="I18" t="n">
         <v>3.883</v>
       </c>
       <c r="J18" t="n">
-        <v>5.836</v>
+        <v>5.835</v>
       </c>
       <c r="K18" t="n">
-        <v>5.817</v>
+        <v>5.813</v>
       </c>
       <c r="L18" t="n">
-        <v>5.853</v>
+        <v>5.852</v>
       </c>
       <c r="M18" t="n">
-        <v>5.822</v>
+        <v>5.821</v>
       </c>
       <c r="N18" t="n">
         <v>5.851</v>
@@ -4378,19 +4378,19 @@
         <v>3.856</v>
       </c>
       <c r="R18" t="n">
-        <v>3.848</v>
+        <v>3.845</v>
       </c>
       <c r="S18" t="n">
-        <v>5.851</v>
+        <v>5.85</v>
       </c>
       <c r="T18" t="n">
-        <v>5.853</v>
+        <v>5.852</v>
       </c>
       <c r="U18" t="n">
-        <v>5.824</v>
+        <v>5.823</v>
       </c>
       <c r="V18" t="n">
-        <v>5.817</v>
+        <v>5.813</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.866</v>
+        <v>3.865</v>
       </c>
       <c r="F19" t="n">
         <v>3.831</v>
@@ -4453,22 +4453,22 @@
         <v>3.887</v>
       </c>
       <c r="J19" t="n">
-        <v>5.834</v>
+        <v>5.833</v>
       </c>
       <c r="K19" t="n">
-        <v>5.799</v>
+        <v>5.798</v>
       </c>
       <c r="L19" t="n">
-        <v>5.859</v>
+        <v>5.858</v>
       </c>
       <c r="M19" t="n">
         <v>5.817</v>
       </c>
       <c r="N19" t="n">
-        <v>5.855</v>
+        <v>5.854</v>
       </c>
       <c r="O19" t="n">
-        <v>3.886</v>
+        <v>3.885</v>
       </c>
       <c r="P19" t="n">
         <v>3.89</v>
@@ -4480,16 +4480,16 @@
         <v>3.831</v>
       </c>
       <c r="S19" t="n">
-        <v>5.854</v>
+        <v>5.853</v>
       </c>
       <c r="T19" t="n">
-        <v>5.859</v>
+        <v>5.858</v>
       </c>
       <c r="U19" t="n">
         <v>5.823</v>
       </c>
       <c r="V19" t="n">
-        <v>5.799</v>
+        <v>5.798</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -4552,19 +4552,19 @@
         <v>3.835</v>
       </c>
       <c r="J20" t="n">
-        <v>5.797</v>
+        <v>5.796</v>
       </c>
       <c r="K20" t="n">
-        <v>5.782</v>
+        <v>5.781</v>
       </c>
       <c r="L20" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="M20" t="n">
-        <v>5.785</v>
+        <v>5.784</v>
       </c>
       <c r="N20" t="n">
-        <v>5.804</v>
+        <v>5.803</v>
       </c>
       <c r="O20" t="n">
         <v>3.829</v>
@@ -4579,16 +4579,16 @@
         <v>3.817</v>
       </c>
       <c r="S20" t="n">
-        <v>5.797</v>
+        <v>5.796</v>
       </c>
       <c r="T20" t="n">
-        <v>5.823</v>
+        <v>5.822</v>
       </c>
       <c r="U20" t="n">
-        <v>5.782</v>
+        <v>5.781</v>
       </c>
       <c r="V20" t="n">
-        <v>5.786</v>
+        <v>5.785</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.801</v>
+        <v>3.8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.784</v>
+        <v>3.782</v>
       </c>
       <c r="G21" t="n">
         <v>3.816</v>
@@ -4651,19 +4651,19 @@
         <v>3.807</v>
       </c>
       <c r="J21" t="n">
-        <v>5.769</v>
+        <v>5.768</v>
       </c>
       <c r="K21" t="n">
-        <v>5.752</v>
+        <v>5.75</v>
       </c>
       <c r="L21" t="n">
         <v>5.784</v>
       </c>
       <c r="M21" t="n">
-        <v>5.763</v>
+        <v>5.762</v>
       </c>
       <c r="N21" t="n">
-        <v>5.775</v>
+        <v>5.774</v>
       </c>
       <c r="O21" t="n">
         <v>3.799</v>
@@ -4672,10 +4672,10 @@
         <v>3.816</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.784</v>
+        <v>3.782</v>
       </c>
       <c r="R21" t="n">
-        <v>3.804</v>
+        <v>3.803</v>
       </c>
       <c r="S21" t="n">
         <v>5.767</v>
@@ -4684,10 +4684,10 @@
         <v>5.784</v>
       </c>
       <c r="U21" t="n">
-        <v>5.752</v>
+        <v>5.75</v>
       </c>
       <c r="V21" t="n">
-        <v>5.772</v>
+        <v>5.771</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -4744,31 +4744,31 @@
         <v>3.798</v>
       </c>
       <c r="H22" t="n">
-        <v>3.761</v>
+        <v>3.762</v>
       </c>
       <c r="I22" t="n">
         <v>3.783</v>
       </c>
       <c r="J22" t="n">
-        <v>5.739</v>
+        <v>5.738</v>
       </c>
       <c r="K22" t="n">
         <v>5.704</v>
       </c>
       <c r="L22" t="n">
-        <v>5.766</v>
+        <v>5.765</v>
       </c>
       <c r="M22" t="n">
         <v>5.729</v>
       </c>
       <c r="N22" t="n">
-        <v>5.752</v>
+        <v>5.751</v>
       </c>
       <c r="O22" t="n">
         <v>3.736</v>
       </c>
       <c r="P22" t="n">
-        <v>3.779</v>
+        <v>3.778</v>
       </c>
       <c r="Q22" t="n">
         <v>3.77</v>
@@ -4780,13 +4780,13 @@
         <v>5.704</v>
       </c>
       <c r="T22" t="n">
-        <v>5.747</v>
+        <v>5.746</v>
       </c>
       <c r="U22" t="n">
         <v>5.738</v>
       </c>
       <c r="V22" t="n">
-        <v>5.766</v>
+        <v>5.765</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4849,19 +4849,19 @@
         <v>6.975</v>
       </c>
       <c r="J23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148</v>
       </c>
       <c r="L23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>6.975</v>
@@ -4876,16 +4876,16 @@
         <v>6.975</v>
       </c>
       <c r="S23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y23" s="1" t="n">
         <v>46315</v>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -4933,58 +4933,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.899</v>
+        <v>6.897</v>
       </c>
       <c r="F24" t="n">
-        <v>6.899</v>
+        <v>6.897</v>
       </c>
       <c r="G24" t="n">
-        <v>6.899</v>
+        <v>6.898</v>
       </c>
       <c r="H24" t="n">
-        <v>6.899</v>
+        <v>6.897</v>
       </c>
       <c r="I24" t="n">
-        <v>6.899</v>
+        <v>6.898</v>
       </c>
       <c r="J24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="K24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="L24" t="n">
-        <v>9.081</v>
+        <v>9.071</v>
       </c>
       <c r="M24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="N24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="O24" t="n">
-        <v>6.899</v>
+        <v>6.898</v>
       </c>
       <c r="P24" t="n">
-        <v>6.899</v>
+        <v>6.898</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.899</v>
+        <v>6.897</v>
       </c>
       <c r="R24" t="n">
-        <v>6.899</v>
+        <v>6.897</v>
       </c>
       <c r="S24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="T24" t="n">
-        <v>9.081</v>
+        <v>9.071</v>
       </c>
       <c r="U24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="V24" t="n">
-        <v>9.08</v>
+        <v>9.071</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y24" s="1" t="n">
         <v>46315</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5032,58 +5032,58 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="F25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="G25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="H25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="I25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="J25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="K25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="L25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="M25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="N25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="O25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="P25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="R25" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="S25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="T25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="U25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="V25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.885</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y25" s="1" t="n">
         <v>46315</v>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5131,58 +5131,58 @@
         </is>
       </c>
       <c r="E26" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="F26" t="n">
         <v>6.647</v>
       </c>
-      <c r="F26" t="n">
-        <v>6.644</v>
-      </c>
       <c r="G26" t="n">
-        <v>6.648</v>
+        <v>6.651</v>
       </c>
       <c r="H26" t="n">
-        <v>6.646</v>
+        <v>6.649</v>
       </c>
       <c r="I26" t="n">
-        <v>6.648</v>
+        <v>6.65</v>
       </c>
       <c r="J26" t="n">
-        <v>8.827999999999999</v>
+        <v>8.823</v>
       </c>
       <c r="K26" t="n">
-        <v>8.826000000000001</v>
+        <v>8.821</v>
       </c>
       <c r="L26" t="n">
-        <v>8.83</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>8.827</v>
+        <v>8.823</v>
       </c>
       <c r="N26" t="n">
-        <v>8.829000000000001</v>
+        <v>8.824</v>
       </c>
       <c r="O26" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6.651</v>
+      </c>
+      <c r="R26" t="n">
         <v>6.647</v>
       </c>
-      <c r="P26" t="n">
-        <v>6.647</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.648</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6.644</v>
-      </c>
       <c r="S26" t="n">
-        <v>8.827999999999999</v>
+        <v>8.823</v>
       </c>
       <c r="T26" t="n">
-        <v>8.827999999999999</v>
+        <v>8.824</v>
       </c>
       <c r="U26" t="n">
-        <v>8.83</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>8.826000000000001</v>
+        <v>8.821</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y26" s="1" t="n">
         <v>46315</v>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5230,58 +5230,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.532</v>
+        <v>6.53</v>
       </c>
       <c r="F27" t="n">
-        <v>6.52</v>
+        <v>6.505</v>
       </c>
       <c r="G27" t="n">
-        <v>6.536</v>
+        <v>6.539</v>
       </c>
       <c r="H27" t="n">
-        <v>6.531</v>
+        <v>6.529</v>
       </c>
       <c r="I27" t="n">
-        <v>6.536</v>
+        <v>6.539</v>
       </c>
       <c r="J27" t="n">
+        <v>8.704000000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8.679</v>
+      </c>
+      <c r="L27" t="n">
         <v>8.712999999999999</v>
       </c>
-      <c r="K27" t="n">
-        <v>8.701000000000001</v>
-      </c>
-      <c r="L27" t="n">
-        <v>8.718</v>
-      </c>
       <c r="M27" t="n">
+        <v>8.702999999999999</v>
+      </c>
+      <c r="N27" t="n">
         <v>8.712</v>
       </c>
-      <c r="N27" t="n">
-        <v>8.717000000000001</v>
-      </c>
       <c r="O27" t="n">
-        <v>6.534</v>
+        <v>6.537</v>
       </c>
       <c r="P27" t="n">
-        <v>6.536</v>
+        <v>6.538</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.536</v>
+        <v>6.539</v>
       </c>
       <c r="R27" t="n">
-        <v>6.52</v>
+        <v>6.505</v>
       </c>
       <c r="S27" t="n">
-        <v>8.715999999999999</v>
+        <v>8.711</v>
       </c>
       <c r="T27" t="n">
-        <v>8.717000000000001</v>
+        <v>8.712</v>
       </c>
       <c r="U27" t="n">
-        <v>8.718</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>8.701000000000001</v>
+        <v>8.679</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y27" s="1" t="n">
         <v>46315</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5329,58 +5329,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.415</v>
+        <v>6.417</v>
       </c>
       <c r="F28" t="n">
-        <v>6.405</v>
+        <v>6.408</v>
       </c>
       <c r="G28" t="n">
         <v>6.43</v>
       </c>
       <c r="H28" t="n">
-        <v>6.407</v>
+        <v>6.41</v>
       </c>
       <c r="I28" t="n">
-        <v>6.421</v>
+        <v>6.422</v>
       </c>
       <c r="J28" t="n">
-        <v>8.597</v>
+        <v>8.590999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>8.586</v>
+        <v>8.581</v>
       </c>
       <c r="L28" t="n">
-        <v>8.611000000000001</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>8.589</v>
+        <v>8.584</v>
       </c>
       <c r="N28" t="n">
-        <v>8.603</v>
+        <v>8.596</v>
       </c>
       <c r="O28" t="n">
-        <v>6.408</v>
+        <v>6.411</v>
       </c>
       <c r="P28" t="n">
         <v>6.43</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.419</v>
+        <v>6.42</v>
       </c>
       <c r="R28" t="n">
-        <v>6.405</v>
+        <v>6.408</v>
       </c>
       <c r="S28" t="n">
-        <v>8.59</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>8.611000000000001</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>8.6</v>
+        <v>8.593</v>
       </c>
       <c r="V28" t="n">
-        <v>8.586</v>
+        <v>8.581</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>46315</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5428,58 +5428,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.274</v>
+        <v>6.275</v>
       </c>
       <c r="F29" t="n">
-        <v>6.267</v>
+        <v>6.269</v>
       </c>
       <c r="G29" t="n">
         <v>6.284</v>
       </c>
       <c r="H29" t="n">
-        <v>6.267</v>
+        <v>6.27</v>
       </c>
       <c r="I29" t="n">
-        <v>6.28</v>
+        <v>6.278</v>
       </c>
       <c r="J29" t="n">
-        <v>8.455</v>
+        <v>8.448</v>
       </c>
       <c r="K29" t="n">
-        <v>8.448</v>
+        <v>8.443</v>
       </c>
       <c r="L29" t="n">
-        <v>8.465</v>
+        <v>8.458</v>
       </c>
       <c r="M29" t="n">
-        <v>8.448</v>
+        <v>8.443</v>
       </c>
       <c r="N29" t="n">
-        <v>8.461</v>
+        <v>8.452</v>
       </c>
       <c r="O29" t="n">
-        <v>6.267</v>
+        <v>6.269</v>
       </c>
       <c r="P29" t="n">
-        <v>6.278</v>
+        <v>6.276</v>
       </c>
       <c r="Q29" t="n">
         <v>6.284</v>
       </c>
       <c r="R29" t="n">
-        <v>6.267</v>
+        <v>6.27</v>
       </c>
       <c r="S29" t="n">
-        <v>8.448</v>
+        <v>8.443</v>
       </c>
       <c r="T29" t="n">
-        <v>8.459</v>
+        <v>8.449</v>
       </c>
       <c r="U29" t="n">
-        <v>8.465</v>
+        <v>8.458</v>
       </c>
       <c r="V29" t="n">
-        <v>8.448</v>
+        <v>8.443</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>46315</v>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -5530,55 +5530,55 @@
         <v>4.1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.063</v>
+        <v>4.064</v>
       </c>
       <c r="G30" t="n">
-        <v>4.153</v>
+        <v>4.154</v>
       </c>
       <c r="H30" t="n">
         <v>4.065</v>
       </c>
       <c r="I30" t="n">
-        <v>4.127</v>
+        <v>4.126</v>
       </c>
       <c r="J30" t="n">
-        <v>5.339</v>
+        <v>5.336</v>
       </c>
       <c r="K30" t="n">
-        <v>5.303</v>
+        <v>5.3</v>
       </c>
       <c r="L30" t="n">
-        <v>5.392</v>
+        <v>5.39</v>
       </c>
       <c r="M30" t="n">
-        <v>5.304</v>
+        <v>5.301</v>
       </c>
       <c r="N30" t="n">
-        <v>5.367</v>
+        <v>5.362</v>
       </c>
       <c r="O30" t="n">
-        <v>4.065</v>
+        <v>4.066</v>
       </c>
       <c r="P30" t="n">
-        <v>4.153</v>
+        <v>4.154</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.119</v>
+        <v>4.117</v>
       </c>
       <c r="R30" t="n">
-        <v>4.063</v>
+        <v>4.064</v>
       </c>
       <c r="S30" t="n">
-        <v>5.305</v>
+        <v>5.302</v>
       </c>
       <c r="T30" t="n">
-        <v>5.392</v>
+        <v>5.39</v>
       </c>
       <c r="U30" t="n">
-        <v>5.358</v>
+        <v>5.353</v>
       </c>
       <c r="V30" t="n">
-        <v>5.303</v>
+        <v>5.3</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>46315</v>
@@ -5629,10 +5629,10 @@
         <v>4.183</v>
       </c>
       <c r="F31" t="n">
-        <v>4.003</v>
+        <v>4.005</v>
       </c>
       <c r="G31" t="n">
-        <v>4.347</v>
+        <v>4.346</v>
       </c>
       <c r="H31" t="n">
         <v>4.117</v>
@@ -5641,43 +5641,43 @@
         <v>4.258</v>
       </c>
       <c r="J31" t="n">
-        <v>5.423</v>
+        <v>5.42</v>
       </c>
       <c r="K31" t="n">
-        <v>5.243</v>
+        <v>5.241</v>
       </c>
       <c r="L31" t="n">
-        <v>5.586</v>
+        <v>5.583</v>
       </c>
       <c r="M31" t="n">
-        <v>5.356</v>
+        <v>5.353</v>
       </c>
       <c r="N31" t="n">
-        <v>5.497</v>
+        <v>5.494</v>
       </c>
       <c r="O31" t="n">
-        <v>4.155</v>
+        <v>4.154</v>
       </c>
       <c r="P31" t="n">
-        <v>4.347</v>
+        <v>4.346</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.228</v>
+        <v>4.229</v>
       </c>
       <c r="R31" t="n">
-        <v>4.003</v>
+        <v>4.005</v>
       </c>
       <c r="S31" t="n">
-        <v>5.394</v>
+        <v>5.39</v>
       </c>
       <c r="T31" t="n">
-        <v>5.586</v>
+        <v>5.583</v>
       </c>
       <c r="U31" t="n">
-        <v>5.467</v>
+        <v>5.465</v>
       </c>
       <c r="V31" t="n">
-        <v>5.243</v>
+        <v>5.241</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>46315</v>
@@ -5728,28 +5728,28 @@
         <v>4.266</v>
       </c>
       <c r="F32" t="n">
-        <v>3.899</v>
+        <v>3.896</v>
       </c>
       <c r="G32" t="n">
-        <v>4.56</v>
+        <v>4.561</v>
       </c>
       <c r="H32" t="n">
         <v>4.12</v>
       </c>
       <c r="I32" t="n">
-        <v>4.448</v>
+        <v>4.45</v>
       </c>
       <c r="J32" t="n">
-        <v>5.505</v>
+        <v>5.502</v>
       </c>
       <c r="K32" t="n">
-        <v>5.138</v>
+        <v>5.133</v>
       </c>
       <c r="L32" t="n">
-        <v>5.8</v>
+        <v>5.797</v>
       </c>
       <c r="M32" t="n">
-        <v>5.36</v>
+        <v>5.356</v>
       </c>
       <c r="N32" t="n">
         <v>5.687</v>
@@ -5758,25 +5758,25 @@
         <v>4.194</v>
       </c>
       <c r="P32" t="n">
-        <v>4.56</v>
+        <v>4.561</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.411</v>
+        <v>4.414</v>
       </c>
       <c r="R32" t="n">
-        <v>3.899</v>
+        <v>3.896</v>
       </c>
       <c r="S32" t="n">
-        <v>5.433</v>
+        <v>5.431</v>
       </c>
       <c r="T32" t="n">
-        <v>5.8</v>
+        <v>5.797</v>
       </c>
       <c r="U32" t="n">
         <v>5.65</v>
       </c>
       <c r="V32" t="n">
-        <v>5.138</v>
+        <v>5.133</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>46315</v>
@@ -5824,58 +5824,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.376</v>
+        <v>4.374</v>
       </c>
       <c r="F33" t="n">
-        <v>4.037</v>
+        <v>4.038</v>
       </c>
       <c r="G33" t="n">
-        <v>4.661</v>
+        <v>4.655</v>
       </c>
       <c r="H33" t="n">
         <v>4.163</v>
       </c>
       <c r="I33" t="n">
-        <v>4.616</v>
+        <v>4.611</v>
       </c>
       <c r="J33" t="n">
-        <v>5.615</v>
+        <v>5.61</v>
       </c>
       <c r="K33" t="n">
-        <v>5.276</v>
+        <v>5.274</v>
       </c>
       <c r="L33" t="n">
-        <v>5.901</v>
+        <v>5.892</v>
       </c>
       <c r="M33" t="n">
-        <v>5.402</v>
+        <v>5.399</v>
       </c>
       <c r="N33" t="n">
-        <v>5.855</v>
+        <v>5.847</v>
       </c>
       <c r="O33" t="n">
         <v>4.205</v>
       </c>
       <c r="P33" t="n">
-        <v>4.661</v>
+        <v>4.655</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.601</v>
+        <v>4.596</v>
       </c>
       <c r="R33" t="n">
-        <v>4.037</v>
+        <v>4.038</v>
       </c>
       <c r="S33" t="n">
-        <v>5.445</v>
+        <v>5.441</v>
       </c>
       <c r="T33" t="n">
-        <v>5.901</v>
+        <v>5.892</v>
       </c>
       <c r="U33" t="n">
-        <v>5.84</v>
+        <v>5.833</v>
       </c>
       <c r="V33" t="n">
-        <v>5.276</v>
+        <v>5.274</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="X33" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y33" s="1" t="n">
         <v>46315</v>
@@ -5923,58 +5923,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.409</v>
+        <v>4.408</v>
       </c>
       <c r="F34" t="n">
         <v>4.072</v>
       </c>
       <c r="G34" t="n">
-        <v>4.749</v>
+        <v>4.744</v>
       </c>
       <c r="H34" t="n">
         <v>4.208</v>
       </c>
       <c r="I34" t="n">
-        <v>4.61</v>
+        <v>4.609</v>
       </c>
       <c r="J34" t="n">
-        <v>5.649</v>
+        <v>5.644</v>
       </c>
       <c r="K34" t="n">
-        <v>5.312</v>
+        <v>5.308</v>
       </c>
       <c r="L34" t="n">
-        <v>5.989</v>
+        <v>5.98</v>
       </c>
       <c r="M34" t="n">
-        <v>5.447</v>
+        <v>5.445</v>
       </c>
       <c r="N34" t="n">
-        <v>5.849</v>
+        <v>5.845</v>
       </c>
       <c r="O34" t="n">
-        <v>4.253</v>
+        <v>4.254</v>
       </c>
       <c r="P34" t="n">
-        <v>4.749</v>
+        <v>4.744</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.563</v>
+        <v>4.564</v>
       </c>
       <c r="R34" t="n">
         <v>4.072</v>
       </c>
       <c r="S34" t="n">
-        <v>5.492</v>
+        <v>5.49</v>
       </c>
       <c r="T34" t="n">
-        <v>5.989</v>
+        <v>5.98</v>
       </c>
       <c r="U34" t="n">
-        <v>5.803</v>
+        <v>5.8</v>
       </c>
       <c r="V34" t="n">
-        <v>5.312</v>
+        <v>5.308</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>46315</v>
@@ -6022,58 +6022,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.228</v>
+        <v>4.225</v>
       </c>
       <c r="F35" t="n">
-        <v>3.856</v>
+        <v>3.853</v>
       </c>
       <c r="G35" t="n">
-        <v>4.683</v>
+        <v>4.679</v>
       </c>
       <c r="H35" t="n">
-        <v>4.056</v>
+        <v>4.053</v>
       </c>
       <c r="I35" t="n">
-        <v>4.359</v>
+        <v>4.357</v>
       </c>
       <c r="J35" t="n">
-        <v>5.467</v>
+        <v>5.462</v>
       </c>
       <c r="K35" t="n">
-        <v>5.095</v>
+        <v>5.089</v>
       </c>
       <c r="L35" t="n">
-        <v>5.922</v>
+        <v>5.915</v>
       </c>
       <c r="M35" t="n">
-        <v>5.296</v>
+        <v>5.289</v>
       </c>
       <c r="N35" t="n">
-        <v>5.598</v>
+        <v>5.593</v>
       </c>
       <c r="O35" t="n">
-        <v>4.123</v>
+        <v>4.12</v>
       </c>
       <c r="P35" t="n">
-        <v>4.683</v>
+        <v>4.679</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.251</v>
+        <v>4.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.856</v>
+        <v>3.853</v>
       </c>
       <c r="S35" t="n">
-        <v>5.363</v>
+        <v>5.356</v>
       </c>
       <c r="T35" t="n">
-        <v>5.922</v>
+        <v>5.915</v>
       </c>
       <c r="U35" t="n">
-        <v>5.49</v>
+        <v>5.486</v>
       </c>
       <c r="V35" t="n">
-        <v>5.095</v>
+        <v>5.089</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>46315</v>
@@ -6121,58 +6121,58 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.884</v>
+        <v>3.881</v>
       </c>
       <c r="F36" t="n">
-        <v>3.577</v>
+        <v>3.574</v>
       </c>
       <c r="G36" t="n">
-        <v>4.368</v>
+        <v>4.362</v>
       </c>
       <c r="H36" t="n">
         <v>3.737</v>
       </c>
       <c r="I36" t="n">
-        <v>3.943</v>
+        <v>3.939</v>
       </c>
       <c r="J36" t="n">
-        <v>5.124</v>
+        <v>5.117</v>
       </c>
       <c r="K36" t="n">
-        <v>4.817</v>
+        <v>4.81</v>
       </c>
       <c r="L36" t="n">
-        <v>5.608</v>
+        <v>5.598</v>
       </c>
       <c r="M36" t="n">
-        <v>4.976</v>
+        <v>4.973</v>
       </c>
       <c r="N36" t="n">
-        <v>5.183</v>
+        <v>5.175</v>
       </c>
       <c r="O36" t="n">
-        <v>3.79</v>
+        <v>3.791</v>
       </c>
       <c r="P36" t="n">
-        <v>4.368</v>
+        <v>4.362</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.801</v>
+        <v>3.798</v>
       </c>
       <c r="R36" t="n">
-        <v>3.577</v>
+        <v>3.574</v>
       </c>
       <c r="S36" t="n">
-        <v>5.029</v>
+        <v>5.027</v>
       </c>
       <c r="T36" t="n">
-        <v>5.608</v>
+        <v>5.598</v>
       </c>
       <c r="U36" t="n">
-        <v>5.041</v>
+        <v>5.034</v>
       </c>
       <c r="V36" t="n">
-        <v>4.817</v>
+        <v>4.81</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="X36" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="Y36" s="1" t="n">
         <v>46315</v>
@@ -7013,16 +7013,16 @@
         <v>6.348</v>
       </c>
       <c r="J45" t="n">
+        <v>7.029</v>
+      </c>
+      <c r="K45" t="n">
+        <v>7.029</v>
+      </c>
+      <c r="L45" t="n">
         <v>7.03</v>
       </c>
-      <c r="K45" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="L45" t="n">
-        <v>7.031</v>
-      </c>
       <c r="M45" t="n">
-        <v>7.03</v>
+        <v>7.029</v>
       </c>
       <c r="N45" t="n">
         <v>7.03</v>
@@ -7040,16 +7040,16 @@
         <v>6.348</v>
       </c>
       <c r="S45" t="n">
-        <v>7.031</v>
+        <v>7.03</v>
       </c>
       <c r="T45" t="n">
-        <v>7.03</v>
+        <v>7.029</v>
       </c>
       <c r="U45" t="n">
-        <v>7.03</v>
+        <v>7.029</v>
       </c>
       <c r="V45" t="n">
-        <v>7.03</v>
+        <v>7.029</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -7097,58 +7097,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.283</v>
+        <v>6.282</v>
       </c>
       <c r="F46" t="n">
+        <v>6.281</v>
+      </c>
+      <c r="G46" t="n">
         <v>6.282</v>
       </c>
-      <c r="G46" t="n">
-        <v>6.283</v>
-      </c>
       <c r="H46" t="n">
-        <v>6.283</v>
+        <v>6.281</v>
       </c>
       <c r="I46" t="n">
-        <v>6.283</v>
+        <v>6.282</v>
       </c>
       <c r="J46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="K46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="L46" t="n">
-        <v>6.965</v>
+        <v>6.964</v>
       </c>
       <c r="M46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="N46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="O46" t="n">
-        <v>6.283</v>
+        <v>6.282</v>
       </c>
       <c r="P46" t="n">
-        <v>6.283</v>
+        <v>6.282</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.283</v>
+        <v>6.281</v>
       </c>
       <c r="R46" t="n">
-        <v>6.282</v>
+        <v>6.281</v>
       </c>
       <c r="S46" t="n">
-        <v>6.965</v>
+        <v>6.964</v>
       </c>
       <c r="T46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="U46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="V46" t="n">
-        <v>6.965</v>
+        <v>6.963</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.225</v>
+        <v>6.224</v>
       </c>
       <c r="F47" t="n">
         <v>6.222</v>
@@ -7205,25 +7205,25 @@
         <v>6.226</v>
       </c>
       <c r="H47" t="n">
-        <v>6.224</v>
+        <v>6.223</v>
       </c>
       <c r="I47" t="n">
-        <v>6.226</v>
+        <v>6.225</v>
       </c>
       <c r="J47" t="n">
+        <v>6.906</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6.904</v>
+      </c>
+      <c r="L47" t="n">
         <v>6.907</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>6.905</v>
       </c>
-      <c r="L47" t="n">
-        <v>6.908</v>
-      </c>
-      <c r="M47" t="n">
-        <v>6.906</v>
-      </c>
       <c r="N47" t="n">
-        <v>6.908</v>
+        <v>6.907</v>
       </c>
       <c r="O47" t="n">
         <v>6.226</v>
@@ -7235,19 +7235,19 @@
         <v>6.222</v>
       </c>
       <c r="R47" t="n">
-        <v>6.226</v>
+        <v>6.225</v>
       </c>
       <c r="S47" t="n">
-        <v>6.908</v>
+        <v>6.907</v>
       </c>
       <c r="T47" t="n">
+        <v>6.905</v>
+      </c>
+      <c r="U47" t="n">
+        <v>6.904</v>
+      </c>
+      <c r="V47" t="n">
         <v>6.907</v>
-      </c>
-      <c r="U47" t="n">
-        <v>6.905</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6.908</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6.107</v>
+        <v>6.108</v>
       </c>
       <c r="F48" t="n">
         <v>6.107</v>
@@ -7304,13 +7304,13 @@
         <v>6.108</v>
       </c>
       <c r="H48" t="n">
-        <v>6.107</v>
+        <v>6.108</v>
       </c>
       <c r="I48" t="n">
-        <v>6.107</v>
+        <v>6.108</v>
       </c>
       <c r="J48" t="n">
-        <v>6.79</v>
+        <v>6.789</v>
       </c>
       <c r="K48" t="n">
         <v>6.789</v>
@@ -7325,10 +7325,10 @@
         <v>6.79</v>
       </c>
       <c r="O48" t="n">
-        <v>6.107</v>
+        <v>6.108</v>
       </c>
       <c r="P48" t="n">
-        <v>6.107</v>
+        <v>6.108</v>
       </c>
       <c r="Q48" t="n">
         <v>6.107</v>
@@ -7337,10 +7337,10 @@
         <v>6.108</v>
       </c>
       <c r="S48" t="n">
-        <v>6.79</v>
+        <v>6.789</v>
       </c>
       <c r="T48" t="n">
-        <v>6.79</v>
+        <v>6.789</v>
       </c>
       <c r="U48" t="n">
         <v>6.789</v>
@@ -7397,7 +7397,7 @@
         <v>6.047</v>
       </c>
       <c r="F49" t="n">
-        <v>6.045</v>
+        <v>6.044</v>
       </c>
       <c r="G49" t="n">
         <v>6.048</v>
@@ -7412,7 +7412,7 @@
         <v>6.729</v>
       </c>
       <c r="K49" t="n">
-        <v>6.727</v>
+        <v>6.726</v>
       </c>
       <c r="L49" t="n">
         <v>6.73</v>
@@ -7421,7 +7421,7 @@
         <v>6.729</v>
       </c>
       <c r="N49" t="n">
-        <v>6.73</v>
+        <v>6.729</v>
       </c>
       <c r="O49" t="n">
         <v>6.048</v>
@@ -7430,22 +7430,22 @@
         <v>6.048</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.045</v>
+        <v>6.044</v>
       </c>
       <c r="R49" t="n">
         <v>6.048</v>
       </c>
       <c r="S49" t="n">
-        <v>6.73</v>
+        <v>6.729</v>
       </c>
       <c r="T49" t="n">
         <v>6.73</v>
       </c>
       <c r="U49" t="n">
-        <v>6.727</v>
+        <v>6.726</v>
       </c>
       <c r="V49" t="n">
-        <v>6.73</v>
+        <v>6.729</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -7496,13 +7496,13 @@
         <v>6.029</v>
       </c>
       <c r="F50" t="n">
-        <v>6.018</v>
+        <v>6.017</v>
       </c>
       <c r="G50" t="n">
         <v>6.033</v>
       </c>
       <c r="H50" t="n">
-        <v>6.029</v>
+        <v>6.028</v>
       </c>
       <c r="I50" t="n">
         <v>6.033</v>
@@ -7511,13 +7511,13 @@
         <v>6.711</v>
       </c>
       <c r="K50" t="n">
-        <v>6.7</v>
+        <v>6.699</v>
       </c>
       <c r="L50" t="n">
-        <v>6.716</v>
+        <v>6.715</v>
       </c>
       <c r="M50" t="n">
-        <v>6.711</v>
+        <v>6.71</v>
       </c>
       <c r="N50" t="n">
         <v>6.715</v>
@@ -7529,7 +7529,7 @@
         <v>6.033</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.018</v>
+        <v>6.017</v>
       </c>
       <c r="R50" t="n">
         <v>6.032</v>
@@ -7538,10 +7538,10 @@
         <v>6.715</v>
       </c>
       <c r="T50" t="n">
-        <v>6.716</v>
+        <v>6.715</v>
       </c>
       <c r="U50" t="n">
-        <v>6.7</v>
+        <v>6.699</v>
       </c>
       <c r="V50" t="n">
         <v>6.714</v>
@@ -7607,19 +7607,19 @@
         <v>5.103</v>
       </c>
       <c r="J51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="K51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="L51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="M51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="N51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="O51" t="n">
         <v>5.103</v>
@@ -7634,16 +7634,16 @@
         <v>5.102</v>
       </c>
       <c r="S51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="T51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="U51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="V51" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="X51" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y51" s="1" t="n">
         <v>46315</v>
@@ -7691,19 +7691,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="F52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="G52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="H52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="I52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="J52" t="n">
         <v>6.149</v>
@@ -7721,16 +7721,16 @@
         <v>6.149</v>
       </c>
       <c r="O52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="P52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="R52" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="S52" t="n">
         <v>6.149</v>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="X52" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y52" s="1" t="n">
         <v>46315</v>
@@ -7790,58 +7790,58 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="F53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="G53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="H53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="I53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="J53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="K53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="L53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="M53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="N53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="O53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="P53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="R53" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="S53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="T53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="U53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="V53" t="n">
-        <v>6.181</v>
+        <v>6.173</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y53" s="1" t="n">
         <v>46315</v>
@@ -7889,58 +7889,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="F54" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="G54" t="n">
-        <v>5.113</v>
+        <v>5.12</v>
       </c>
       <c r="H54" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="I54" t="n">
-        <v>5.113</v>
+        <v>5.12</v>
       </c>
       <c r="J54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="K54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="L54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="M54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="N54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="O54" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="P54" t="n">
-        <v>5.113</v>
+        <v>5.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="R54" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="S54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="T54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="U54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="V54" t="n">
-        <v>6.15</v>
+        <v>6.149</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y54" s="1" t="n">
         <v>46315</v>
@@ -7988,58 +7988,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="F55" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="G55" t="n">
-        <v>5.094</v>
+        <v>5.099</v>
       </c>
       <c r="H55" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="I55" t="n">
-        <v>5.094</v>
+        <v>5.099</v>
       </c>
       <c r="J55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="K55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="L55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="M55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="N55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="O55" t="n">
-        <v>5.094</v>
+        <v>5.099</v>
       </c>
       <c r="P55" t="n">
-        <v>5.094</v>
+        <v>5.099</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="R55" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="S55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="T55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="U55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="V55" t="n">
-        <v>6.131</v>
+        <v>6.128</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y55" s="1" t="n">
         <v>46315</v>
@@ -8087,58 +8087,58 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="F56" t="n">
-        <v>5.157</v>
+        <v>5.161</v>
       </c>
       <c r="G56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="H56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="I56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="J56" t="n">
-        <v>6.195</v>
+        <v>6.191</v>
       </c>
       <c r="K56" t="n">
-        <v>6.194</v>
+        <v>6.19</v>
       </c>
       <c r="L56" t="n">
-        <v>6.196</v>
+        <v>6.192</v>
       </c>
       <c r="M56" t="n">
-        <v>6.195</v>
+        <v>6.191</v>
       </c>
       <c r="N56" t="n">
-        <v>6.196</v>
+        <v>6.192</v>
       </c>
       <c r="O56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="P56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="R56" t="n">
-        <v>5.157</v>
+        <v>5.161</v>
       </c>
       <c r="S56" t="n">
-        <v>6.196</v>
+        <v>6.192</v>
       </c>
       <c r="T56" t="n">
-        <v>6.196</v>
+        <v>6.192</v>
       </c>
       <c r="U56" t="n">
-        <v>6.195</v>
+        <v>6.191</v>
       </c>
       <c r="V56" t="n">
-        <v>6.194</v>
+        <v>6.19</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y56" s="1" t="n">
         <v>46315</v>
@@ -8186,58 +8186,58 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="F57" t="n">
-        <v>5.35</v>
+        <v>5.355</v>
       </c>
       <c r="G57" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="H57" t="n">
-        <v>5.35</v>
+        <v>5.355</v>
       </c>
       <c r="I57" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="J57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="K57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="L57" t="n">
-        <v>6.388</v>
+        <v>6.386</v>
       </c>
       <c r="M57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="N57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="O57" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="P57" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.35</v>
+        <v>5.356</v>
       </c>
       <c r="R57" t="n">
-        <v>5.35</v>
+        <v>5.355</v>
       </c>
       <c r="S57" t="n">
-        <v>6.388</v>
+        <v>6.386</v>
       </c>
       <c r="T57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="U57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="V57" t="n">
-        <v>6.388</v>
+        <v>6.385</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="Y57" s="1" t="n">
         <v>46315</v>
@@ -8399,19 +8399,19 @@
         <v>4.614</v>
       </c>
       <c r="J59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="K59" t="n">
         <v>5.249</v>
       </c>
       <c r="L59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="M59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="N59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="O59" t="n">
         <v>4.614</v>
@@ -8426,13 +8426,13 @@
         <v>4.614</v>
       </c>
       <c r="S59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="T59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="U59" t="n">
-        <v>5.25</v>
+        <v>5.249</v>
       </c>
       <c r="V59" t="n">
         <v>5.249</v>
@@ -8483,58 +8483,58 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.628</v>
+        <v>4.627</v>
       </c>
       <c r="F60" t="n">
-        <v>4.628</v>
+        <v>4.626</v>
       </c>
       <c r="G60" t="n">
-        <v>4.63</v>
+        <v>4.629</v>
       </c>
       <c r="H60" t="n">
-        <v>4.628</v>
+        <v>4.626</v>
       </c>
       <c r="I60" t="n">
+        <v>4.627</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5.262</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5.261</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5.264</v>
+      </c>
+      <c r="M60" t="n">
+        <v>5.261</v>
+      </c>
+      <c r="N60" t="n">
+        <v>5.262</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4.626</v>
+      </c>
+      <c r="P60" t="n">
+        <v>4.626</v>
+      </c>
+      <c r="Q60" t="n">
         <v>4.629</v>
       </c>
-      <c r="J60" t="n">
+      <c r="R60" t="n">
+        <v>4.626</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5.261</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5.261</v>
+      </c>
+      <c r="U60" t="n">
         <v>5.264</v>
       </c>
-      <c r="K60" t="n">
-        <v>5.263</v>
-      </c>
-      <c r="L60" t="n">
-        <v>5.266</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5.263</v>
-      </c>
-      <c r="N60" t="n">
-        <v>5.264</v>
-      </c>
-      <c r="O60" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="P60" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R60" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="S60" t="n">
-        <v>5.263</v>
-      </c>
-      <c r="T60" t="n">
-        <v>5.263</v>
-      </c>
-      <c r="U60" t="n">
-        <v>5.266</v>
-      </c>
       <c r="V60" t="n">
-        <v>5.263</v>
+        <v>5.262</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -8582,13 +8582,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.682</v>
+        <v>4.681</v>
       </c>
       <c r="F61" t="n">
         <v>4.681</v>
       </c>
       <c r="G61" t="n">
-        <v>4.683</v>
+        <v>4.682</v>
       </c>
       <c r="H61" t="n">
         <v>4.681</v>
@@ -8597,19 +8597,19 @@
         <v>4.682</v>
       </c>
       <c r="J61" t="n">
+        <v>5.316</v>
+      </c>
+      <c r="K61" t="n">
+        <v>5.316</v>
+      </c>
+      <c r="L61" t="n">
         <v>5.317</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
+        <v>5.316</v>
+      </c>
+      <c r="N61" t="n">
         <v>5.317</v>
-      </c>
-      <c r="L61" t="n">
-        <v>5.318</v>
-      </c>
-      <c r="M61" t="n">
-        <v>5.317</v>
-      </c>
-      <c r="N61" t="n">
-        <v>5.318</v>
       </c>
       <c r="O61" t="n">
         <v>4.681</v>
@@ -8618,22 +8618,22 @@
         <v>4.681</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.683</v>
+        <v>4.682</v>
       </c>
       <c r="R61" t="n">
         <v>4.682</v>
       </c>
       <c r="S61" t="n">
+        <v>5.316</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5.316</v>
+      </c>
+      <c r="U61" t="n">
         <v>5.317</v>
       </c>
-      <c r="T61" t="n">
+      <c r="V61" t="n">
         <v>5.317</v>
-      </c>
-      <c r="U61" t="n">
-        <v>5.318</v>
-      </c>
-      <c r="V61" t="n">
-        <v>5.318</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -8681,58 +8681,58 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="F62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="G62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="H62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="I62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="J62" t="n">
-        <v>5.379</v>
+        <v>5.377</v>
       </c>
       <c r="K62" t="n">
-        <v>5.378</v>
+        <v>5.377</v>
       </c>
       <c r="L62" t="n">
-        <v>5.379</v>
+        <v>5.377</v>
       </c>
       <c r="M62" t="n">
-        <v>5.378</v>
+        <v>5.377</v>
       </c>
       <c r="N62" t="n">
-        <v>5.379</v>
+        <v>5.377</v>
       </c>
       <c r="O62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="P62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="R62" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="S62" t="n">
-        <v>5.378</v>
+        <v>5.377</v>
       </c>
       <c r="T62" t="n">
-        <v>5.378</v>
+        <v>5.377</v>
       </c>
       <c r="U62" t="n">
-        <v>5.379</v>
+        <v>5.377</v>
       </c>
       <c r="V62" t="n">
-        <v>5.379</v>
+        <v>5.377</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -8780,58 +8780,58 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="F63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="G63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="H63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="I63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="J63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="K63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="L63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="M63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="N63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="O63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="P63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="R63" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="S63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="T63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="U63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="V63" t="n">
-        <v>5.429</v>
+        <v>5.426</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -8879,58 +8879,58 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="F64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="G64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="H64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="I64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="J64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="K64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="L64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="M64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="N64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="O64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="P64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="R64" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
       <c r="S64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="T64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="U64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="V64" t="n">
-        <v>5.469</v>
+        <v>5.468</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="X65" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y65" s="1" t="n">
         <v>46315</v>
@@ -9077,58 +9077,58 @@
         </is>
       </c>
       <c r="E66" t="n">
+        <v>9.108000000000001</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.103</v>
+      </c>
+      <c r="G66" t="n">
+        <v>9.112</v>
+      </c>
+      <c r="H66" t="n">
+        <v>9.105</v>
+      </c>
+      <c r="I66" t="n">
+        <v>9.112</v>
+      </c>
+      <c r="J66" t="n">
+        <v>10.874</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10.869</v>
+      </c>
+      <c r="L66" t="n">
+        <v>10.878</v>
+      </c>
+      <c r="M66" t="n">
+        <v>10.871</v>
+      </c>
+      <c r="N66" t="n">
+        <v>10.878</v>
+      </c>
+      <c r="O66" t="n">
         <v>9.111000000000001</v>
       </c>
-      <c r="F66" t="n">
-        <v>9.106999999999999</v>
-      </c>
-      <c r="G66" t="n">
-        <v>9.115</v>
-      </c>
-      <c r="H66" t="n">
-        <v>9.109</v>
-      </c>
-      <c r="I66" t="n">
-        <v>9.115</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="P66" t="n">
+        <v>9.112</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>9.106</v>
+      </c>
+      <c r="R66" t="n">
+        <v>9.103</v>
+      </c>
+      <c r="S66" t="n">
         <v>10.878</v>
       </c>
-      <c r="K66" t="n">
-        <v>10.873</v>
-      </c>
-      <c r="L66" t="n">
-        <v>10.882</v>
-      </c>
-      <c r="M66" t="n">
-        <v>10.875</v>
-      </c>
-      <c r="N66" t="n">
-        <v>10.882</v>
-      </c>
-      <c r="O66" t="n">
-        <v>9.115</v>
-      </c>
-      <c r="P66" t="n">
-        <v>9.115</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>9.109</v>
-      </c>
-      <c r="R66" t="n">
-        <v>9.106999999999999</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10.882</v>
-      </c>
       <c r="T66" t="n">
-        <v>10.882</v>
+        <v>10.878</v>
       </c>
       <c r="U66" t="n">
-        <v>10.876</v>
+        <v>10.872</v>
       </c>
       <c r="V66" t="n">
-        <v>10.873</v>
+        <v>10.869</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="X66" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y66" s="1" t="n">
         <v>46315</v>
@@ -9179,10 +9179,10 @@
         <v>9.138999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>9.135999999999999</v>
+        <v>9.137</v>
       </c>
       <c r="G67" t="n">
-        <v>9.140000000000001</v>
+        <v>9.141</v>
       </c>
       <c r="H67" t="n">
         <v>9.138999999999999</v>
@@ -9191,7 +9191,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>10.906</v>
+        <v>10.905</v>
       </c>
       <c r="K67" t="n">
         <v>10.903</v>
@@ -9200,13 +9200,13 @@
         <v>10.907</v>
       </c>
       <c r="M67" t="n">
+        <v>10.905</v>
+      </c>
+      <c r="N67" t="n">
         <v>10.906</v>
       </c>
-      <c r="N67" t="n">
-        <v>10.907</v>
-      </c>
       <c r="O67" t="n">
-        <v>9.140000000000001</v>
+        <v>9.141</v>
       </c>
       <c r="P67" t="n">
         <v>9.140000000000001</v>
@@ -9215,16 +9215,16 @@
         <v>9.140000000000001</v>
       </c>
       <c r="R67" t="n">
-        <v>9.135999999999999</v>
+        <v>9.137</v>
       </c>
       <c r="S67" t="n">
         <v>10.907</v>
       </c>
       <c r="T67" t="n">
-        <v>10.907</v>
+        <v>10.906</v>
       </c>
       <c r="U67" t="n">
-        <v>10.907</v>
+        <v>10.906</v>
       </c>
       <c r="V67" t="n">
         <v>10.903</v>
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="X67" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y67" s="1" t="n">
         <v>46315</v>
@@ -9281,34 +9281,34 @@
         <v>9.164999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>9.186999999999999</v>
+        <v>9.186</v>
       </c>
       <c r="H68" t="n">
         <v>9.179</v>
       </c>
       <c r="I68" t="n">
-        <v>9.185</v>
+        <v>9.183999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>10.947</v>
+        <v>10.946</v>
       </c>
       <c r="K68" t="n">
-        <v>10.932</v>
+        <v>10.931</v>
       </c>
       <c r="L68" t="n">
-        <v>10.954</v>
+        <v>10.952</v>
       </c>
       <c r="M68" t="n">
-        <v>10.946</v>
+        <v>10.945</v>
       </c>
       <c r="N68" t="n">
         <v>10.951</v>
       </c>
       <c r="O68" t="n">
-        <v>9.186999999999999</v>
+        <v>9.186</v>
       </c>
       <c r="P68" t="n">
-        <v>9.183</v>
+        <v>9.183999999999999</v>
       </c>
       <c r="Q68" t="n">
         <v>9.183999999999999</v>
@@ -9317,16 +9317,16 @@
         <v>9.164999999999999</v>
       </c>
       <c r="S68" t="n">
-        <v>10.954</v>
+        <v>10.952</v>
       </c>
       <c r="T68" t="n">
         <v>10.95</v>
       </c>
       <c r="U68" t="n">
-        <v>10.951</v>
+        <v>10.95</v>
       </c>
       <c r="V68" t="n">
-        <v>10.932</v>
+        <v>10.931</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="X68" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y68" s="1" t="n">
         <v>46315</v>
@@ -9383,25 +9383,25 @@
         <v>9.221</v>
       </c>
       <c r="H69" t="n">
-        <v>9.208</v>
+        <v>9.207000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>9.214</v>
       </c>
       <c r="J69" t="n">
-        <v>10.978</v>
+        <v>10.977</v>
       </c>
       <c r="K69" t="n">
         <v>10.969</v>
       </c>
       <c r="L69" t="n">
-        <v>10.988</v>
+        <v>10.987</v>
       </c>
       <c r="M69" t="n">
-        <v>10.974</v>
+        <v>10.973</v>
       </c>
       <c r="N69" t="n">
-        <v>10.981</v>
+        <v>10.98</v>
       </c>
       <c r="O69" t="n">
         <v>9.221</v>
@@ -9416,13 +9416,13 @@
         <v>9.202</v>
       </c>
       <c r="S69" t="n">
-        <v>10.988</v>
+        <v>10.987</v>
       </c>
       <c r="T69" t="n">
-        <v>10.976</v>
+        <v>10.975</v>
       </c>
       <c r="U69" t="n">
-        <v>10.979</v>
+        <v>10.978</v>
       </c>
       <c r="V69" t="n">
         <v>10.969</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="X69" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y69" s="1" t="n">
         <v>46315</v>
@@ -9476,16 +9476,16 @@
         <v>9.236000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>9.233000000000001</v>
+        <v>9.234</v>
       </c>
       <c r="G70" t="n">
-        <v>9.242000000000001</v>
+        <v>9.243</v>
       </c>
       <c r="H70" t="n">
-        <v>9.233000000000001</v>
+        <v>9.234</v>
       </c>
       <c r="I70" t="n">
-        <v>9.236000000000001</v>
+        <v>9.237</v>
       </c>
       <c r="J70" t="n">
         <v>11.003</v>
@@ -9503,16 +9503,16 @@
         <v>11.003</v>
       </c>
       <c r="O70" t="n">
-        <v>9.242000000000001</v>
+        <v>9.243</v>
       </c>
       <c r="P70" t="n">
-        <v>9.233000000000001</v>
+        <v>9.234</v>
       </c>
       <c r="Q70" t="n">
         <v>9.234</v>
       </c>
       <c r="R70" t="n">
-        <v>9.233000000000001</v>
+        <v>9.234</v>
       </c>
       <c r="S70" t="n">
         <v>11.009</v>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="X70" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y70" s="1" t="n">
         <v>46315</v>
@@ -9575,7 +9575,7 @@
         <v>9.252000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>9.239000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="G71" t="n">
         <v>9.271000000000001</v>
@@ -9587,34 +9587,34 @@
         <v>9.254</v>
       </c>
       <c r="J71" t="n">
-        <v>11.019</v>
+        <v>11.018</v>
       </c>
       <c r="K71" t="n">
         <v>11.006</v>
       </c>
       <c r="L71" t="n">
-        <v>11.038</v>
+        <v>11.037</v>
       </c>
       <c r="M71" t="n">
-        <v>11.013</v>
+        <v>11.012</v>
       </c>
       <c r="N71" t="n">
-        <v>11.021</v>
+        <v>11.02</v>
       </c>
       <c r="O71" t="n">
         <v>9.271000000000001</v>
       </c>
       <c r="P71" t="n">
-        <v>9.249000000000001</v>
+        <v>9.247999999999999</v>
       </c>
       <c r="Q71" t="n">
-        <v>9.239000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="R71" t="n">
         <v>9.247999999999999</v>
       </c>
       <c r="S71" t="n">
-        <v>11.038</v>
+        <v>11.037</v>
       </c>
       <c r="T71" t="n">
         <v>11.015</v>
@@ -9623,7 +9623,7 @@
         <v>11.006</v>
       </c>
       <c r="V71" t="n">
-        <v>11.015</v>
+        <v>11.014</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="Y71" s="1" t="n">
         <v>46315</v>
@@ -9686,19 +9686,19 @@
         <v>3.478</v>
       </c>
       <c r="J72" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="K72" t="n">
         <v>5.39</v>
       </c>
       <c r="L72" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="M72" t="n">
         <v>5.39</v>
       </c>
       <c r="N72" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="O72" t="n">
         <v>3.477</v>
@@ -9713,13 +9713,13 @@
         <v>3.477</v>
       </c>
       <c r="S72" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="T72" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="U72" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="V72" t="n">
         <v>5.39</v>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y72" s="1" t="n">
         <v>46315</v>
@@ -9770,16 +9770,16 @@
         </is>
       </c>
       <c r="E73" t="n">
+        <v>3.586</v>
+      </c>
+      <c r="F73" t="n">
         <v>3.585</v>
       </c>
-      <c r="F73" t="n">
-        <v>3.584</v>
-      </c>
       <c r="G73" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="H73" t="n">
         <v>3.586</v>
-      </c>
-      <c r="H73" t="n">
-        <v>3.585</v>
       </c>
       <c r="I73" t="n">
         <v>3.586</v>
@@ -9803,13 +9803,13 @@
         <v>3.586</v>
       </c>
       <c r="P73" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="Q73" t="n">
         <v>3.586</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="R73" t="n">
         <v>3.585</v>
-      </c>
-      <c r="R73" t="n">
-        <v>3.584</v>
       </c>
       <c r="S73" t="n">
         <v>5.499</v>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y73" s="1" t="n">
         <v>46315</v>
@@ -9869,10 +9869,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.612</v>
+        <v>3.611</v>
       </c>
       <c r="F74" t="n">
-        <v>3.565</v>
+        <v>3.562</v>
       </c>
       <c r="G74" t="n">
         <v>3.649</v>
@@ -9881,22 +9881,22 @@
         <v>3.581</v>
       </c>
       <c r="I74" t="n">
-        <v>3.648</v>
+        <v>3.647</v>
       </c>
       <c r="J74" t="n">
-        <v>5.525</v>
+        <v>5.524</v>
       </c>
       <c r="K74" t="n">
-        <v>5.478</v>
+        <v>5.475</v>
       </c>
       <c r="L74" t="n">
-        <v>5.562</v>
+        <v>5.561</v>
       </c>
       <c r="M74" t="n">
-        <v>5.494</v>
+        <v>5.493</v>
       </c>
       <c r="N74" t="n">
-        <v>5.561</v>
+        <v>5.56</v>
       </c>
       <c r="O74" t="n">
         <v>3.647</v>
@@ -9908,19 +9908,19 @@
         <v>3.587</v>
       </c>
       <c r="R74" t="n">
-        <v>3.565</v>
+        <v>3.562</v>
       </c>
       <c r="S74" t="n">
-        <v>5.56</v>
+        <v>5.559</v>
       </c>
       <c r="T74" t="n">
-        <v>5.562</v>
+        <v>5.561</v>
       </c>
       <c r="U74" t="n">
         <v>5.5</v>
       </c>
       <c r="V74" t="n">
-        <v>5.478</v>
+        <v>5.475</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y74" s="1" t="n">
         <v>46315</v>
@@ -9968,55 +9968,55 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.557</v>
+        <v>3.555</v>
       </c>
       <c r="F75" t="n">
         <v>3.457</v>
       </c>
       <c r="G75" t="n">
-        <v>3.634</v>
+        <v>3.632</v>
       </c>
       <c r="H75" t="n">
         <v>3.495</v>
       </c>
       <c r="I75" t="n">
-        <v>3.629</v>
+        <v>3.627</v>
       </c>
       <c r="J75" t="n">
-        <v>5.47</v>
+        <v>5.468</v>
       </c>
       <c r="K75" t="n">
         <v>5.37</v>
       </c>
       <c r="L75" t="n">
-        <v>5.547</v>
+        <v>5.544</v>
       </c>
       <c r="M75" t="n">
-        <v>5.409</v>
+        <v>5.407</v>
       </c>
       <c r="N75" t="n">
-        <v>5.542</v>
+        <v>5.539</v>
       </c>
       <c r="O75" t="n">
-        <v>3.634</v>
+        <v>3.632</v>
       </c>
       <c r="P75" t="n">
-        <v>3.627</v>
+        <v>3.625</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.508</v>
+        <v>3.507</v>
       </c>
       <c r="R75" t="n">
         <v>3.457</v>
       </c>
       <c r="S75" t="n">
-        <v>5.547</v>
+        <v>5.544</v>
       </c>
       <c r="T75" t="n">
-        <v>5.54</v>
+        <v>5.538</v>
       </c>
       <c r="U75" t="n">
-        <v>5.421</v>
+        <v>5.42</v>
       </c>
       <c r="V75" t="n">
         <v>5.37</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="X75" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y75" s="1" t="n">
         <v>46315</v>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3.36</v>
+        <v>3.359</v>
       </c>
       <c r="F76" t="n">
         <v>3.208</v>
@@ -10076,22 +10076,22 @@
         <v>3.476</v>
       </c>
       <c r="H76" t="n">
-        <v>3.268</v>
+        <v>3.267</v>
       </c>
       <c r="I76" t="n">
-        <v>3.468</v>
+        <v>3.469</v>
       </c>
       <c r="J76" t="n">
-        <v>5.273</v>
+        <v>5.272</v>
       </c>
       <c r="K76" t="n">
         <v>5.121</v>
       </c>
       <c r="L76" t="n">
-        <v>5.389</v>
+        <v>5.388</v>
       </c>
       <c r="M76" t="n">
-        <v>5.181</v>
+        <v>5.18</v>
       </c>
       <c r="N76" t="n">
         <v>5.381</v>
@@ -10106,19 +10106,19 @@
         <v>3.208</v>
       </c>
       <c r="R76" t="n">
-        <v>3.288</v>
+        <v>3.287</v>
       </c>
       <c r="S76" t="n">
         <v>5.379</v>
       </c>
       <c r="T76" t="n">
-        <v>5.389</v>
+        <v>5.388</v>
       </c>
       <c r="U76" t="n">
         <v>5.121</v>
       </c>
       <c r="V76" t="n">
-        <v>5.201</v>
+        <v>5.199</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="X76" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y76" s="1" t="n">
         <v>46315</v>
@@ -10166,34 +10166,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2.974</v>
+        <v>2.973</v>
       </c>
       <c r="F77" t="n">
-        <v>2.796</v>
+        <v>2.797</v>
       </c>
       <c r="G77" t="n">
         <v>3.146</v>
       </c>
       <c r="H77" t="n">
-        <v>2.912</v>
+        <v>2.911</v>
       </c>
       <c r="I77" t="n">
-        <v>3.038</v>
+        <v>3.037</v>
       </c>
       <c r="J77" t="n">
-        <v>4.887</v>
+        <v>4.886</v>
       </c>
       <c r="K77" t="n">
         <v>4.709</v>
       </c>
       <c r="L77" t="n">
-        <v>5.059</v>
+        <v>5.058</v>
       </c>
       <c r="M77" t="n">
-        <v>4.825</v>
+        <v>4.824</v>
       </c>
       <c r="N77" t="n">
-        <v>4.951</v>
+        <v>4.95</v>
       </c>
       <c r="O77" t="n">
         <v>2.95</v>
@@ -10202,13 +10202,13 @@
         <v>3.001</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.796</v>
+        <v>2.797</v>
       </c>
       <c r="R77" t="n">
         <v>3.146</v>
       </c>
       <c r="S77" t="n">
-        <v>4.863</v>
+        <v>4.862</v>
       </c>
       <c r="T77" t="n">
         <v>4.914</v>
@@ -10217,7 +10217,7 @@
         <v>4.709</v>
       </c>
       <c r="V77" t="n">
-        <v>5.059</v>
+        <v>5.058</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y77" s="1" t="n">
         <v>46315</v>
@@ -10265,58 +10265,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2.602</v>
+        <v>2.603</v>
       </c>
       <c r="F78" t="n">
-        <v>2.124</v>
+        <v>2.126</v>
       </c>
       <c r="G78" t="n">
         <v>3.038</v>
       </c>
       <c r="H78" t="n">
-        <v>2.455</v>
+        <v>2.456</v>
       </c>
       <c r="I78" t="n">
-        <v>2.771</v>
+        <v>2.77</v>
       </c>
       <c r="J78" t="n">
         <v>4.515</v>
       </c>
       <c r="K78" t="n">
-        <v>4.037</v>
+        <v>4.039</v>
       </c>
       <c r="L78" t="n">
-        <v>4.951</v>
+        <v>4.95</v>
       </c>
       <c r="M78" t="n">
-        <v>4.368</v>
+        <v>4.369</v>
       </c>
       <c r="N78" t="n">
-        <v>4.684</v>
+        <v>4.682</v>
       </c>
       <c r="O78" t="n">
-        <v>2.565</v>
+        <v>2.566</v>
       </c>
       <c r="P78" t="n">
-        <v>2.682</v>
+        <v>2.68</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.124</v>
+        <v>2.126</v>
       </c>
       <c r="R78" t="n">
         <v>3.038</v>
       </c>
       <c r="S78" t="n">
-        <v>4.478</v>
+        <v>4.479</v>
       </c>
       <c r="T78" t="n">
-        <v>4.595</v>
+        <v>4.593</v>
       </c>
       <c r="U78" t="n">
-        <v>4.037</v>
+        <v>4.039</v>
       </c>
       <c r="V78" t="n">
-        <v>4.951</v>
+        <v>4.95</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="X78" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="Y78" s="1" t="n">
         <v>46315</v>
@@ -10382,16 +10382,16 @@
         <v>6.871</v>
       </c>
       <c r="K79" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="L79" t="n">
         <v>6.871</v>
-      </c>
-      <c r="L79" t="n">
-        <v>6.872</v>
       </c>
       <c r="M79" t="n">
         <v>6.871</v>
       </c>
       <c r="N79" t="n">
-        <v>6.872</v>
+        <v>6.871</v>
       </c>
       <c r="O79" t="n">
         <v>5.19</v>
@@ -10406,16 +10406,16 @@
         <v>5.19</v>
       </c>
       <c r="S79" t="n">
-        <v>6.872</v>
+        <v>6.871</v>
       </c>
       <c r="T79" t="n">
-        <v>6.872</v>
+        <v>6.871</v>
       </c>
       <c r="U79" t="n">
         <v>6.871</v>
       </c>
       <c r="V79" t="n">
-        <v>6.871</v>
+        <v>6.87</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -10463,58 +10463,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5.174</v>
+        <v>5.17</v>
       </c>
       <c r="F80" t="n">
-        <v>5.172</v>
+        <v>5.169</v>
       </c>
       <c r="G80" t="n">
-        <v>5.175</v>
+        <v>5.171</v>
       </c>
       <c r="H80" t="n">
-        <v>5.173</v>
+        <v>5.169</v>
       </c>
       <c r="I80" t="n">
-        <v>5.175</v>
+        <v>5.17</v>
       </c>
       <c r="J80" t="n">
-        <v>6.855</v>
+        <v>6.85</v>
       </c>
       <c r="K80" t="n">
-        <v>6.854</v>
+        <v>6.849</v>
       </c>
       <c r="L80" t="n">
-        <v>6.857</v>
+        <v>6.851</v>
       </c>
       <c r="M80" t="n">
-        <v>6.854</v>
+        <v>6.849</v>
       </c>
       <c r="N80" t="n">
-        <v>6.856</v>
+        <v>6.851</v>
       </c>
       <c r="O80" t="n">
-        <v>5.175</v>
+        <v>5.171</v>
       </c>
       <c r="P80" t="n">
-        <v>5.175</v>
+        <v>5.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.173</v>
+        <v>5.169</v>
       </c>
       <c r="R80" t="n">
-        <v>5.172</v>
+        <v>5.169</v>
       </c>
       <c r="S80" t="n">
-        <v>6.857</v>
+        <v>6.851</v>
       </c>
       <c r="T80" t="n">
-        <v>6.856</v>
+        <v>6.851</v>
       </c>
       <c r="U80" t="n">
-        <v>6.854</v>
+        <v>6.85</v>
       </c>
       <c r="V80" t="n">
-        <v>6.854</v>
+        <v>6.849</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -10562,58 +10562,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5.154</v>
+        <v>5.15</v>
       </c>
       <c r="F81" t="n">
+        <v>5.142</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5.162</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5.146</v>
+      </c>
+      <c r="I81" t="n">
+        <v>5.151</v>
+      </c>
+      <c r="J81" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6.823</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6.843</v>
+      </c>
+      <c r="M81" t="n">
+        <v>6.827</v>
+      </c>
+      <c r="N81" t="n">
+        <v>6.832</v>
+      </c>
+      <c r="O81" t="n">
+        <v>5.148</v>
+      </c>
+      <c r="P81" t="n">
         <v>5.147</v>
       </c>
-      <c r="G81" t="n">
-        <v>5.164</v>
-      </c>
-      <c r="H81" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="I81" t="n">
-        <v>5.155</v>
-      </c>
-      <c r="J81" t="n">
-        <v>6.835</v>
-      </c>
-      <c r="K81" t="n">
+      <c r="Q81" t="n">
+        <v>5.142</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5.162</v>
+      </c>
+      <c r="S81" t="n">
         <v>6.828</v>
       </c>
-      <c r="L81" t="n">
-        <v>6.845</v>
-      </c>
-      <c r="M81" t="n">
-        <v>6.832</v>
-      </c>
-      <c r="N81" t="n">
-        <v>6.837</v>
-      </c>
-      <c r="O81" t="n">
-        <v>5.152</v>
-      </c>
-      <c r="P81" t="n">
-        <v>5.152</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>5.147</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5.164</v>
-      </c>
-      <c r="S81" t="n">
-        <v>6.834</v>
-      </c>
       <c r="T81" t="n">
-        <v>6.833</v>
+        <v>6.828</v>
       </c>
       <c r="U81" t="n">
-        <v>6.828</v>
+        <v>6.823</v>
       </c>
       <c r="V81" t="n">
-        <v>6.845</v>
+        <v>6.843</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -10661,58 +10661,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5.161</v>
+        <v>5.158</v>
       </c>
       <c r="F82" t="n">
-        <v>5.137</v>
+        <v>5.136</v>
       </c>
       <c r="G82" t="n">
-        <v>5.18</v>
+        <v>5.176</v>
       </c>
       <c r="H82" t="n">
-        <v>5.149</v>
+        <v>5.145</v>
       </c>
       <c r="I82" t="n">
-        <v>5.177</v>
+        <v>5.173</v>
       </c>
       <c r="J82" t="n">
-        <v>6.843</v>
+        <v>6.839</v>
       </c>
       <c r="K82" t="n">
-        <v>6.818</v>
+        <v>6.817</v>
       </c>
       <c r="L82" t="n">
-        <v>6.862</v>
+        <v>6.856</v>
       </c>
       <c r="M82" t="n">
-        <v>6.83</v>
+        <v>6.826</v>
       </c>
       <c r="N82" t="n">
-        <v>6.859</v>
+        <v>6.853</v>
       </c>
       <c r="O82" t="n">
+        <v>5.172</v>
+      </c>
+      <c r="P82" t="n">
         <v>5.176</v>
       </c>
-      <c r="P82" t="n">
-        <v>5.18</v>
-      </c>
       <c r="Q82" t="n">
-        <v>5.137</v>
+        <v>5.136</v>
       </c>
       <c r="R82" t="n">
-        <v>5.153</v>
+        <v>5.148</v>
       </c>
       <c r="S82" t="n">
-        <v>6.858</v>
+        <v>6.852</v>
       </c>
       <c r="T82" t="n">
-        <v>6.862</v>
+        <v>6.856</v>
       </c>
       <c r="U82" t="n">
-        <v>6.818</v>
+        <v>6.817</v>
       </c>
       <c r="V82" t="n">
-        <v>6.834</v>
+        <v>6.829</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -10760,58 +10760,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5.217</v>
+        <v>5.215</v>
       </c>
       <c r="F83" t="n">
-        <v>5.132</v>
+        <v>5.131</v>
       </c>
       <c r="G83" t="n">
-        <v>5.322</v>
+        <v>5.32</v>
       </c>
       <c r="H83" t="n">
+        <v>5.141</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5.278</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="K83" t="n">
+        <v>6.812</v>
+      </c>
+      <c r="L83" t="n">
+        <v>7.001</v>
+      </c>
+      <c r="M83" t="n">
+        <v>6.821</v>
+      </c>
+      <c r="N83" t="n">
+        <v>6.958</v>
+      </c>
+      <c r="O83" t="n">
+        <v>5.264</v>
+      </c>
+      <c r="P83" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="R83" t="n">
         <v>5.144</v>
       </c>
-      <c r="I83" t="n">
-        <v>5.279</v>
-      </c>
-      <c r="J83" t="n">
-        <v>6.898</v>
-      </c>
-      <c r="K83" t="n">
-        <v>6.813</v>
-      </c>
-      <c r="L83" t="n">
-        <v>7.003</v>
-      </c>
-      <c r="M83" t="n">
-        <v>6.826</v>
-      </c>
-      <c r="N83" t="n">
-        <v>6.961</v>
-      </c>
-      <c r="O83" t="n">
-        <v>5.265</v>
-      </c>
-      <c r="P83" t="n">
-        <v>5.322</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>5.132</v>
-      </c>
-      <c r="R83" t="n">
-        <v>5.149</v>
-      </c>
       <c r="S83" t="n">
-        <v>6.947</v>
+        <v>6.944</v>
       </c>
       <c r="T83" t="n">
-        <v>7.003</v>
+        <v>7.001</v>
       </c>
       <c r="U83" t="n">
-        <v>6.813</v>
+        <v>6.812</v>
       </c>
       <c r="V83" t="n">
-        <v>6.83</v>
+        <v>6.825</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -10859,58 +10859,58 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5.253</v>
+        <v>5.252</v>
       </c>
       <c r="F84" t="n">
-        <v>5.068</v>
+        <v>5.067</v>
       </c>
       <c r="G84" t="n">
-        <v>5.42</v>
+        <v>5.419</v>
       </c>
       <c r="H84" t="n">
         <v>5.121</v>
       </c>
       <c r="I84" t="n">
-        <v>5.393</v>
+        <v>5.392</v>
       </c>
       <c r="J84" t="n">
-        <v>6.934</v>
+        <v>6.932</v>
       </c>
       <c r="K84" t="n">
-        <v>6.749</v>
+        <v>6.748</v>
       </c>
       <c r="L84" t="n">
-        <v>7.102</v>
+        <v>7.1</v>
       </c>
       <c r="M84" t="n">
-        <v>6.803</v>
+        <v>6.801</v>
       </c>
       <c r="N84" t="n">
-        <v>7.074</v>
+        <v>7.072</v>
       </c>
       <c r="O84" t="n">
         <v>5.383</v>
       </c>
       <c r="P84" t="n">
-        <v>5.42</v>
+        <v>5.419</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.068</v>
+        <v>5.067</v>
       </c>
       <c r="R84" t="n">
-        <v>5.139</v>
+        <v>5.138</v>
       </c>
       <c r="S84" t="n">
-        <v>7.065</v>
+        <v>7.063</v>
       </c>
       <c r="T84" t="n">
-        <v>7.102</v>
+        <v>7.1</v>
       </c>
       <c r="U84" t="n">
-        <v>6.749</v>
+        <v>6.748</v>
       </c>
       <c r="V84" t="n">
-        <v>6.821</v>
+        <v>6.819</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>5.292</v>
       </c>
       <c r="F85" t="n">
-        <v>5.057</v>
+        <v>5.056</v>
       </c>
       <c r="G85" t="n">
         <v>5.495</v>
@@ -10973,16 +10973,16 @@
         <v>5.486</v>
       </c>
       <c r="J85" t="n">
-        <v>6.974</v>
+        <v>6.973</v>
       </c>
       <c r="K85" t="n">
-        <v>6.738</v>
+        <v>6.737</v>
       </c>
       <c r="L85" t="n">
-        <v>7.177</v>
+        <v>7.175</v>
       </c>
       <c r="M85" t="n">
-        <v>6.797</v>
+        <v>6.796</v>
       </c>
       <c r="N85" t="n">
         <v>7.167</v>
@@ -10994,7 +10994,7 @@
         <v>5.495</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.057</v>
+        <v>5.056</v>
       </c>
       <c r="R85" t="n">
         <v>5.135</v>
@@ -11003,13 +11003,13 @@
         <v>7.164</v>
       </c>
       <c r="T85" t="n">
-        <v>7.177</v>
+        <v>7.175</v>
       </c>
       <c r="U85" t="n">
-        <v>6.738</v>
+        <v>6.737</v>
       </c>
       <c r="V85" t="n">
-        <v>6.816</v>
+        <v>6.815</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -11751,19 +11751,19 @@
         <v>4.568</v>
       </c>
       <c r="J93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="K93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="L93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="M93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="N93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="O93" t="n">
         <v>4.568</v>
@@ -11778,16 +11778,16 @@
         <v>4.567</v>
       </c>
       <c r="S93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="T93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="U93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="V93" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y93" s="1" t="n">
         <v>46315</v>
@@ -11835,58 +11835,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="F94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="G94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="H94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="I94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="J94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="K94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="L94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="M94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="N94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="O94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="P94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="R94" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="S94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="T94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="U94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="V94" t="n">
-        <v>3.651</v>
+        <v>3.652</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y94" s="1" t="n">
         <v>46315</v>
@@ -11934,58 +11934,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="F95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="G95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="H95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="I95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="J95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="K95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="L95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="M95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="N95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="O95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="P95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="R95" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="S95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="T95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="U95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="V95" t="n">
-        <v>3.724</v>
+        <v>3.726</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y95" s="1" t="n">
         <v>46315</v>
@@ -12033,58 +12033,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="F96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="G96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="H96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="I96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="J96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="K96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="L96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="M96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="N96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="O96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="P96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="R96" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="S96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="T96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="U96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="V96" t="n">
-        <v>3.814</v>
+        <v>3.816</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="X96" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y96" s="1" t="n">
         <v>46315</v>
@@ -12132,58 +12132,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="F97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="G97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="H97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="I97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="J97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="K97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="L97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="M97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="N97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="O97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="P97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="R97" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="S97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="T97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="U97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="V97" t="n">
-        <v>3.946</v>
+        <v>3.947</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y97" s="1" t="n">
         <v>46315</v>
@@ -12231,58 +12231,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="F98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="G98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="H98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="I98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="J98" t="n">
-        <v>4.148</v>
+        <v>4.149</v>
       </c>
       <c r="K98" t="n">
-        <v>4.148</v>
+        <v>4.149</v>
       </c>
       <c r="L98" t="n">
-        <v>4.148</v>
+        <v>4.15</v>
       </c>
       <c r="M98" t="n">
-        <v>4.148</v>
+        <v>4.149</v>
       </c>
       <c r="N98" t="n">
-        <v>4.148</v>
+        <v>4.15</v>
       </c>
       <c r="O98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="P98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="R98" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="S98" t="n">
-        <v>4.148</v>
+        <v>4.149</v>
       </c>
       <c r="T98" t="n">
-        <v>4.148</v>
+        <v>4.149</v>
       </c>
       <c r="U98" t="n">
-        <v>4.148</v>
+        <v>4.15</v>
       </c>
       <c r="V98" t="n">
-        <v>4.148</v>
+        <v>4.149</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="X98" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y98" s="1" t="n">
         <v>46315</v>
@@ -12330,58 +12330,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="F99" t="n">
-        <v>5.438</v>
+        <v>5.441</v>
       </c>
       <c r="G99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="H99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="I99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="J99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="K99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="L99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="M99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="N99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="O99" t="n">
-        <v>5.438</v>
+        <v>5.441</v>
       </c>
       <c r="P99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="R99" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
       <c r="S99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="T99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="U99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="V99" t="n">
-        <v>4.497</v>
+        <v>4.501</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="X99" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y99" s="1" t="n">
         <v>46315</v>
@@ -12444,19 +12444,19 @@
         <v>5.445</v>
       </c>
       <c r="J100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="K100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="L100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="M100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="N100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="O100" t="n">
         <v>5.445</v>
@@ -12471,16 +12471,16 @@
         <v>5.445</v>
       </c>
       <c r="S100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="T100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="U100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="V100" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="X100" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y100" s="1" t="n">
         <v>46315</v>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -12528,58 +12528,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="F101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="G101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="H101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="I101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="J101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="K101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="L101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="M101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="N101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="O101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="P101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="R101" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="S101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="T101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="U101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="V101" t="n">
-        <v>7.434</v>
+        <v>7.431</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="X101" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y101" s="1" t="n">
         <v>46315</v>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -12627,55 +12627,55 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="F102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="G102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="H102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="I102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="J102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="K102" t="n">
         <v>7.463</v>
       </c>
       <c r="L102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="M102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="N102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="O102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="P102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="Q102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="R102" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="S102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="T102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="U102" t="n">
-        <v>7.464</v>
+        <v>7.463</v>
       </c>
       <c r="V102" t="n">
         <v>7.463</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="X102" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y102" s="1" t="n">
         <v>46315</v>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -12735,28 +12735,28 @@
         <v>5.545</v>
       </c>
       <c r="H103" t="n">
-        <v>5.542</v>
+        <v>5.543</v>
       </c>
       <c r="I103" t="n">
         <v>5.545</v>
       </c>
       <c r="J103" t="n">
+        <v>7.497</v>
+      </c>
+      <c r="K103" t="n">
+        <v>7.492</v>
+      </c>
+      <c r="L103" t="n">
         <v>7.499</v>
       </c>
-      <c r="K103" t="n">
-        <v>7.493</v>
-      </c>
-      <c r="L103" t="n">
-        <v>7.501</v>
-      </c>
       <c r="M103" t="n">
-        <v>7.498</v>
+        <v>7.497</v>
       </c>
       <c r="N103" t="n">
-        <v>7.501</v>
+        <v>7.499</v>
       </c>
       <c r="O103" t="n">
-        <v>5.544</v>
+        <v>5.545</v>
       </c>
       <c r="P103" t="n">
         <v>5.545</v>
@@ -12768,16 +12768,16 @@
         <v>5.538</v>
       </c>
       <c r="S103" t="n">
-        <v>7.5</v>
+        <v>7.498</v>
       </c>
       <c r="T103" t="n">
-        <v>7.5</v>
+        <v>7.499</v>
       </c>
       <c r="U103" t="n">
-        <v>7.501</v>
+        <v>7.499</v>
       </c>
       <c r="V103" t="n">
-        <v>7.493</v>
+        <v>7.492</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="X103" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y103" s="1" t="n">
         <v>46315</v>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
         <v>5.594</v>
       </c>
       <c r="F104" t="n">
-        <v>5.593</v>
+        <v>5.594</v>
       </c>
       <c r="G104" t="n">
         <v>5.594</v>
@@ -12840,19 +12840,19 @@
         <v>5.594</v>
       </c>
       <c r="J104" t="n">
-        <v>7.55</v>
+        <v>7.548</v>
       </c>
       <c r="K104" t="n">
-        <v>7.549</v>
+        <v>7.548</v>
       </c>
       <c r="L104" t="n">
-        <v>7.55</v>
+        <v>7.548</v>
       </c>
       <c r="M104" t="n">
-        <v>7.549</v>
+        <v>7.548</v>
       </c>
       <c r="N104" t="n">
-        <v>7.55</v>
+        <v>7.548</v>
       </c>
       <c r="O104" t="n">
         <v>5.594</v>
@@ -12864,19 +12864,19 @@
         <v>5.594</v>
       </c>
       <c r="R104" t="n">
-        <v>5.593</v>
+        <v>5.594</v>
       </c>
       <c r="S104" t="n">
-        <v>7.549</v>
+        <v>7.548</v>
       </c>
       <c r="T104" t="n">
-        <v>7.55</v>
+        <v>7.548</v>
       </c>
       <c r="U104" t="n">
-        <v>7.55</v>
+        <v>7.548</v>
       </c>
       <c r="V104" t="n">
-        <v>7.549</v>
+        <v>7.548</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y104" s="1" t="n">
         <v>46315</v>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -12924,58 +12924,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5.645</v>
+        <v>5.641</v>
       </c>
       <c r="F105" t="n">
+        <v>5.641</v>
+      </c>
+      <c r="G105" t="n">
         <v>5.643</v>
       </c>
-      <c r="G105" t="n">
-        <v>5.647</v>
-      </c>
       <c r="H105" t="n">
-        <v>5.644</v>
+        <v>5.641</v>
       </c>
       <c r="I105" t="n">
-        <v>5.645</v>
+        <v>5.642</v>
       </c>
       <c r="J105" t="n">
-        <v>7.601</v>
+        <v>7.595</v>
       </c>
       <c r="K105" t="n">
-        <v>7.599</v>
+        <v>7.595</v>
       </c>
       <c r="L105" t="n">
-        <v>7.603</v>
+        <v>7.597</v>
       </c>
       <c r="M105" t="n">
-        <v>7.6</v>
+        <v>7.595</v>
       </c>
       <c r="N105" t="n">
-        <v>7.601</v>
+        <v>7.595</v>
       </c>
       <c r="O105" t="n">
+        <v>5.641</v>
+      </c>
+      <c r="P105" t="n">
+        <v>5.641</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>5.641</v>
+      </c>
+      <c r="R105" t="n">
         <v>5.643</v>
       </c>
-      <c r="P105" t="n">
-        <v>5.645</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>5.644</v>
-      </c>
-      <c r="R105" t="n">
-        <v>5.647</v>
-      </c>
       <c r="S105" t="n">
-        <v>7.599</v>
+        <v>7.595</v>
       </c>
       <c r="T105" t="n">
-        <v>7.601</v>
+        <v>7.595</v>
       </c>
       <c r="U105" t="n">
-        <v>7.6</v>
+        <v>7.595</v>
       </c>
       <c r="V105" t="n">
-        <v>7.603</v>
+        <v>7.597</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y105" s="1" t="n">
         <v>46315</v>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13038,19 +13038,19 @@
         <v>5.79</v>
       </c>
       <c r="J106" t="n">
-        <v>7.745</v>
+        <v>7.743</v>
       </c>
       <c r="K106" t="n">
-        <v>7.743</v>
+        <v>7.74</v>
       </c>
       <c r="L106" t="n">
-        <v>7.749</v>
+        <v>7.747</v>
       </c>
       <c r="M106" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="N106" t="n">
         <v>7.744</v>
-      </c>
-      <c r="N106" t="n">
-        <v>7.746</v>
       </c>
       <c r="O106" t="n">
         <v>5.787</v>
@@ -13065,16 +13065,16 @@
         <v>5.793</v>
       </c>
       <c r="S106" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="T106" t="n">
         <v>7.743</v>
       </c>
-      <c r="T106" t="n">
-        <v>7.745</v>
-      </c>
       <c r="U106" t="n">
-        <v>7.744</v>
+        <v>7.742</v>
       </c>
       <c r="V106" t="n">
-        <v>7.749</v>
+        <v>7.747</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="X106" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="Y106" s="1" t="n">
         <v>46315</v>
@@ -13100,7 +13100,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13122,19 +13122,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="F107" t="n">
-        <v>4.437</v>
+        <v>4.687</v>
       </c>
       <c r="G107" t="n">
-        <v>4.444</v>
+        <v>4.694</v>
       </c>
       <c r="H107" t="n">
-        <v>4.438</v>
+        <v>4.688</v>
       </c>
       <c r="I107" t="n">
-        <v>4.441</v>
+        <v>4.691</v>
       </c>
       <c r="J107" t="n">
         <v>7.007</v>
@@ -13143,7 +13143,7 @@
         <v>7.003</v>
       </c>
       <c r="L107" t="n">
-        <v>7.011</v>
+        <v>7.01</v>
       </c>
       <c r="M107" t="n">
         <v>7.005</v>
@@ -13152,22 +13152,22 @@
         <v>7.008</v>
       </c>
       <c r="O107" t="n">
-        <v>4.44</v>
+        <v>4.691</v>
       </c>
       <c r="P107" t="n">
-        <v>4.444</v>
+        <v>4.694</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.439</v>
+        <v>4.689</v>
       </c>
       <c r="R107" t="n">
-        <v>4.437</v>
+        <v>4.687</v>
       </c>
       <c r="S107" t="n">
         <v>7.007</v>
       </c>
       <c r="T107" t="n">
-        <v>7.011</v>
+        <v>7.01</v>
       </c>
       <c r="U107" t="n">
         <v>7.006</v>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
       <c r="X107" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y107" s="1" t="n">
         <v>46315</v>
@@ -13192,14 +13192,14 @@
         </is>
       </c>
       <c r="AA107" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB107" t="n">
         <v>0</v>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13221,19 +13221,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4.451</v>
+        <v>4.701</v>
       </c>
       <c r="F108" t="n">
-        <v>4.428</v>
+        <v>4.679</v>
       </c>
       <c r="G108" t="n">
-        <v>4.469</v>
+        <v>4.719</v>
       </c>
       <c r="H108" t="n">
-        <v>4.435</v>
+        <v>4.685</v>
       </c>
       <c r="I108" t="n">
-        <v>4.468</v>
+        <v>4.718</v>
       </c>
       <c r="J108" t="n">
         <v>7.017</v>
@@ -13242,7 +13242,7 @@
         <v>6.995</v>
       </c>
       <c r="L108" t="n">
-        <v>7.036</v>
+        <v>7.035</v>
       </c>
       <c r="M108" t="n">
         <v>7.001</v>
@@ -13251,25 +13251,25 @@
         <v>7.035</v>
       </c>
       <c r="O108" t="n">
-        <v>4.469</v>
+        <v>4.719</v>
       </c>
       <c r="P108" t="n">
-        <v>4.468</v>
+        <v>4.718</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.437</v>
+        <v>4.687</v>
       </c>
       <c r="R108" t="n">
-        <v>4.428</v>
+        <v>4.679</v>
       </c>
       <c r="S108" t="n">
-        <v>7.036</v>
+        <v>7.035</v>
       </c>
       <c r="T108" t="n">
         <v>7.035</v>
       </c>
       <c r="U108" t="n">
-        <v>7.004</v>
+        <v>7.003</v>
       </c>
       <c r="V108" t="n">
         <v>6.995</v>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y108" s="1" t="n">
         <v>46315</v>
@@ -13291,14 +13291,14 @@
         </is>
       </c>
       <c r="AA108" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13320,22 +13320,22 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4.428</v>
+        <v>4.678</v>
       </c>
       <c r="F109" t="n">
-        <v>4.393</v>
+        <v>4.643</v>
       </c>
       <c r="G109" t="n">
-        <v>4.465</v>
+        <v>4.715</v>
       </c>
       <c r="H109" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="I109" t="n">
-        <v>4.453</v>
+        <v>4.703</v>
       </c>
       <c r="J109" t="n">
-        <v>6.995</v>
+        <v>6.994</v>
       </c>
       <c r="K109" t="n">
         <v>6.96</v>
@@ -13350,16 +13350,16 @@
         <v>7.02</v>
       </c>
       <c r="O109" t="n">
-        <v>4.465</v>
+        <v>4.715</v>
       </c>
       <c r="P109" t="n">
-        <v>4.449</v>
+        <v>4.699</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.403</v>
+        <v>4.653</v>
       </c>
       <c r="R109" t="n">
-        <v>4.393</v>
+        <v>4.643</v>
       </c>
       <c r="S109" t="n">
         <v>7.032</v>
@@ -13368,7 +13368,7 @@
         <v>7.016</v>
       </c>
       <c r="U109" t="n">
-        <v>6.97</v>
+        <v>6.969</v>
       </c>
       <c r="V109" t="n">
         <v>6.96</v>
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="X109" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y109" s="1" t="n">
         <v>46315</v>
@@ -13390,14 +13390,14 @@
         </is>
       </c>
       <c r="AA109" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13419,19 +13419,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4.36</v>
+        <v>4.61</v>
       </c>
       <c r="F110" t="n">
-        <v>4.333</v>
+        <v>4.583</v>
       </c>
       <c r="G110" t="n">
-        <v>4.387</v>
+        <v>4.637</v>
       </c>
       <c r="H110" t="n">
-        <v>4.336</v>
+        <v>4.586</v>
       </c>
       <c r="I110" t="n">
-        <v>4.385</v>
+        <v>4.634</v>
       </c>
       <c r="J110" t="n">
         <v>6.927</v>
@@ -13449,16 +13449,16 @@
         <v>6.951</v>
       </c>
       <c r="O110" t="n">
-        <v>4.387</v>
+        <v>4.637</v>
       </c>
       <c r="P110" t="n">
-        <v>4.384</v>
+        <v>4.633</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.338</v>
+        <v>4.587</v>
       </c>
       <c r="R110" t="n">
-        <v>4.333</v>
+        <v>4.583</v>
       </c>
       <c r="S110" t="n">
         <v>6.954</v>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="X110" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y110" s="1" t="n">
         <v>46315</v>
@@ -13489,14 +13489,14 @@
         </is>
       </c>
       <c r="AA110" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13518,55 +13518,55 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4.202</v>
+        <v>4.452</v>
       </c>
       <c r="F111" t="n">
-        <v>4.133</v>
+        <v>4.383</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24</v>
+        <v>4.49</v>
       </c>
       <c r="H111" t="n">
-        <v>4.19</v>
+        <v>4.438</v>
       </c>
       <c r="I111" t="n">
-        <v>4.232</v>
+        <v>4.481</v>
       </c>
       <c r="J111" t="n">
-        <v>6.769</v>
+        <v>6.768</v>
       </c>
       <c r="K111" t="n">
-        <v>6.7</v>
+        <v>6.699</v>
       </c>
       <c r="L111" t="n">
         <v>6.806</v>
       </c>
       <c r="M111" t="n">
-        <v>6.756</v>
+        <v>6.754</v>
       </c>
       <c r="N111" t="n">
         <v>6.798</v>
       </c>
       <c r="O111" t="n">
-        <v>4.208</v>
+        <v>4.456</v>
       </c>
       <c r="P111" t="n">
-        <v>4.229</v>
+        <v>4.479</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.133</v>
+        <v>4.383</v>
       </c>
       <c r="R111" t="n">
-        <v>4.24</v>
+        <v>4.49</v>
       </c>
       <c r="S111" t="n">
-        <v>6.775</v>
+        <v>6.772</v>
       </c>
       <c r="T111" t="n">
-        <v>6.796</v>
+        <v>6.795</v>
       </c>
       <c r="U111" t="n">
-        <v>6.7</v>
+        <v>6.699</v>
       </c>
       <c r="V111" t="n">
         <v>6.806</v>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y111" s="1" t="n">
         <v>46315</v>
@@ -13588,14 +13588,14 @@
         </is>
       </c>
       <c r="AA111" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13617,19 +13617,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4.028</v>
+        <v>4.278</v>
       </c>
       <c r="F112" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="G112" t="n">
-        <v>4.165</v>
+        <v>4.414</v>
       </c>
       <c r="H112" t="n">
-        <v>3.972</v>
+        <v>4.221</v>
       </c>
       <c r="I112" t="n">
-        <v>4.086</v>
+        <v>4.336</v>
       </c>
       <c r="J112" t="n">
         <v>6.595</v>
@@ -13647,16 +13647,16 @@
         <v>6.653</v>
       </c>
       <c r="O112" t="n">
-        <v>3.999</v>
+        <v>4.249</v>
       </c>
       <c r="P112" t="n">
-        <v>4.06</v>
+        <v>4.31</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="R112" t="n">
-        <v>4.165</v>
+        <v>4.414</v>
       </c>
       <c r="S112" t="n">
         <v>6.565</v>
@@ -13676,7 +13676,7 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y112" s="1" t="n">
         <v>46315</v>
@@ -13687,14 +13687,14 @@
         </is>
       </c>
       <c r="AA112" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB112" t="n">
         <v>0</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13716,55 +13716,55 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3.719</v>
+        <v>3.968</v>
       </c>
       <c r="F113" t="n">
-        <v>3.407</v>
+        <v>3.654</v>
       </c>
       <c r="G113" t="n">
-        <v>4.06</v>
+        <v>4.31</v>
       </c>
       <c r="H113" t="n">
-        <v>3.557</v>
+        <v>3.805</v>
       </c>
       <c r="I113" t="n">
-        <v>3.866</v>
+        <v>4.116</v>
       </c>
       <c r="J113" t="n">
-        <v>6.286</v>
+        <v>6.284</v>
       </c>
       <c r="K113" t="n">
-        <v>5.974</v>
+        <v>5.97</v>
       </c>
       <c r="L113" t="n">
         <v>6.627</v>
       </c>
       <c r="M113" t="n">
-        <v>6.124</v>
+        <v>6.122</v>
       </c>
       <c r="N113" t="n">
-        <v>6.433</v>
+        <v>6.432</v>
       </c>
       <c r="O113" t="n">
-        <v>3.607</v>
+        <v>3.856</v>
       </c>
       <c r="P113" t="n">
-        <v>3.802</v>
+        <v>4.051</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.407</v>
+        <v>3.654</v>
       </c>
       <c r="R113" t="n">
-        <v>4.06</v>
+        <v>4.31</v>
       </c>
       <c r="S113" t="n">
-        <v>6.174</v>
+        <v>6.172</v>
       </c>
       <c r="T113" t="n">
-        <v>6.369</v>
+        <v>6.367</v>
       </c>
       <c r="U113" t="n">
-        <v>5.974</v>
+        <v>5.97</v>
       </c>
       <c r="V113" t="n">
         <v>6.627</v>
@@ -13775,7 +13775,7 @@
         </is>
       </c>
       <c r="X113" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="Y113" s="1" t="n">
         <v>46315</v>
@@ -13786,14 +13786,14 @@
         </is>
       </c>
       <c r="AA113" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -13830,19 +13830,19 @@
         <v>1.95</v>
       </c>
       <c r="J114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="K114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="L114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="M114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="N114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="O114" t="n">
         <v>1.95</v>
@@ -13857,16 +13857,16 @@
         <v>1.95</v>
       </c>
       <c r="S114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="T114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="U114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="V114" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         </is>
       </c>
       <c r="X114" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y114" s="1" t="n">
         <v>46315</v>
@@ -13914,58 +13914,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="F115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="G115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="H115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="I115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="J115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="K115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="L115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="M115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="N115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="O115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="P115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="R115" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="S115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="T115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="U115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="V115" t="n">
-        <v>5.777</v>
+        <v>5.774</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="X115" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y115" s="1" t="n">
         <v>46315</v>
@@ -14013,58 +14013,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2.023</v>
+        <v>2.021</v>
       </c>
       <c r="F116" t="n">
         <v>2</v>
       </c>
       <c r="G116" t="n">
-        <v>2.04</v>
+        <v>2.037</v>
       </c>
       <c r="H116" t="n">
-        <v>2.012</v>
+        <v>2.008</v>
       </c>
       <c r="I116" t="n">
-        <v>2.038</v>
+        <v>2.036</v>
       </c>
       <c r="J116" t="n">
-        <v>5.813</v>
+        <v>5.81</v>
       </c>
       <c r="K116" t="n">
-        <v>5.79</v>
+        <v>5.789</v>
       </c>
       <c r="L116" t="n">
-        <v>5.829</v>
+        <v>5.827</v>
       </c>
       <c r="M116" t="n">
-        <v>5.802</v>
+        <v>5.798</v>
       </c>
       <c r="N116" t="n">
-        <v>5.828</v>
+        <v>5.825</v>
       </c>
       <c r="O116" t="n">
-        <v>2.04</v>
+        <v>2.037</v>
       </c>
       <c r="P116" t="n">
-        <v>2.038</v>
+        <v>2.035</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.016</v>
+        <v>2.011</v>
       </c>
       <c r="R116" t="n">
         <v>2</v>
       </c>
       <c r="S116" t="n">
-        <v>5.829</v>
+        <v>5.827</v>
       </c>
       <c r="T116" t="n">
-        <v>5.827</v>
+        <v>5.825</v>
       </c>
       <c r="U116" t="n">
-        <v>5.806</v>
+        <v>5.8</v>
       </c>
       <c r="V116" t="n">
-        <v>5.79</v>
+        <v>5.789</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="X116" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y116" s="1" t="n">
         <v>46315</v>
@@ -14133,7 +14133,7 @@
         <v>5.881</v>
       </c>
       <c r="L117" t="n">
-        <v>5.894</v>
+        <v>5.893</v>
       </c>
       <c r="M117" t="n">
         <v>5.883</v>
@@ -14154,7 +14154,7 @@
         <v>2.091</v>
       </c>
       <c r="S117" t="n">
-        <v>5.894</v>
+        <v>5.893</v>
       </c>
       <c r="T117" t="n">
         <v>5.886</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y117" s="1" t="n">
         <v>46315</v>
@@ -14220,19 +14220,19 @@
         <v>2.118</v>
       </c>
       <c r="H118" t="n">
-        <v>2.112</v>
+        <v>2.111</v>
       </c>
       <c r="I118" t="n">
         <v>2.116</v>
       </c>
       <c r="J118" t="n">
-        <v>5.904</v>
+        <v>5.903</v>
       </c>
       <c r="K118" t="n">
-        <v>5.9</v>
+        <v>5.899</v>
       </c>
       <c r="L118" t="n">
-        <v>5.908</v>
+        <v>5.907</v>
       </c>
       <c r="M118" t="n">
         <v>5.901</v>
@@ -14253,16 +14253,16 @@
         <v>2.11</v>
       </c>
       <c r="S118" t="n">
-        <v>5.908</v>
+        <v>5.907</v>
       </c>
       <c r="T118" t="n">
-        <v>5.902</v>
+        <v>5.901</v>
       </c>
       <c r="U118" t="n">
-        <v>5.906</v>
+        <v>5.905</v>
       </c>
       <c r="V118" t="n">
-        <v>5.9</v>
+        <v>5.899</v>
       </c>
       <c r="W118" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y118" s="1" t="n">
         <v>46315</v>
@@ -14310,31 +14310,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2.13</v>
+        <v>2.129</v>
       </c>
       <c r="F119" t="n">
-        <v>2.124</v>
+        <v>2.123</v>
       </c>
       <c r="G119" t="n">
         <v>2.139</v>
       </c>
       <c r="H119" t="n">
-        <v>2.124</v>
+        <v>2.123</v>
       </c>
       <c r="I119" t="n">
         <v>2.134</v>
       </c>
       <c r="J119" t="n">
-        <v>5.919</v>
+        <v>5.918</v>
       </c>
       <c r="K119" t="n">
+        <v>5.912</v>
+      </c>
+      <c r="L119" t="n">
+        <v>5.928</v>
+      </c>
+      <c r="M119" t="n">
         <v>5.913</v>
-      </c>
-      <c r="L119" t="n">
-        <v>5.929</v>
-      </c>
-      <c r="M119" t="n">
-        <v>5.914</v>
       </c>
       <c r="N119" t="n">
         <v>5.923</v>
@@ -14343,25 +14343,25 @@
         <v>2.139</v>
       </c>
       <c r="P119" t="n">
-        <v>2.124</v>
+        <v>2.123</v>
       </c>
       <c r="Q119" t="n">
         <v>2.132</v>
       </c>
       <c r="R119" t="n">
-        <v>2.124</v>
+        <v>2.123</v>
       </c>
       <c r="S119" t="n">
-        <v>5.929</v>
+        <v>5.928</v>
       </c>
       <c r="T119" t="n">
-        <v>5.914</v>
+        <v>5.913</v>
       </c>
       <c r="U119" t="n">
-        <v>5.922</v>
+        <v>5.921</v>
       </c>
       <c r="V119" t="n">
-        <v>5.913</v>
+        <v>5.912</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         </is>
       </c>
       <c r="X119" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y119" s="1" t="n">
         <v>46315</v>
@@ -14409,19 +14409,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2.167</v>
+        <v>2.166</v>
       </c>
       <c r="F120" t="n">
-        <v>2.149</v>
+        <v>2.148</v>
       </c>
       <c r="G120" t="n">
         <v>2.184</v>
       </c>
       <c r="H120" t="n">
-        <v>2.162</v>
+        <v>2.161</v>
       </c>
       <c r="I120" t="n">
-        <v>2.172</v>
+        <v>2.171</v>
       </c>
       <c r="J120" t="n">
         <v>5.956</v>
@@ -14430,28 +14430,28 @@
         <v>5.938</v>
       </c>
       <c r="L120" t="n">
-        <v>5.974</v>
+        <v>5.973</v>
       </c>
       <c r="M120" t="n">
         <v>5.951</v>
       </c>
       <c r="N120" t="n">
-        <v>5.962</v>
+        <v>5.961</v>
       </c>
       <c r="O120" t="n">
         <v>2.184</v>
       </c>
       <c r="P120" t="n">
-        <v>2.168</v>
+        <v>2.167</v>
       </c>
       <c r="Q120" t="n">
-        <v>2.149</v>
+        <v>2.148</v>
       </c>
       <c r="R120" t="n">
         <v>2.166</v>
       </c>
       <c r="S120" t="n">
-        <v>5.974</v>
+        <v>5.973</v>
       </c>
       <c r="T120" t="n">
         <v>5.957</v>
@@ -14460,7 +14460,7 @@
         <v>5.938</v>
       </c>
       <c r="V120" t="n">
-        <v>5.956</v>
+        <v>5.955</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="Y120" s="1" t="n">
         <v>46315</v>
@@ -14523,19 +14523,19 @@
         <v>1.51</v>
       </c>
       <c r="J121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="K121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="L121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="M121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="N121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="O121" t="n">
         <v>1.51</v>
@@ -14550,16 +14550,16 @@
         <v>1.51</v>
       </c>
       <c r="S121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="T121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="U121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="V121" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="W121" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="X121" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y121" s="1" t="n">
         <v>46315</v>
@@ -14607,58 +14607,58 @@
         </is>
       </c>
       <c r="E122" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="G122" t="n">
         <v>1.496</v>
       </c>
-      <c r="F122" t="n">
+      <c r="H122" t="n">
         <v>1.495</v>
       </c>
-      <c r="G122" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>1.496</v>
       </c>
-      <c r="I122" t="n">
-        <v>1.497</v>
-      </c>
       <c r="J122" t="n">
-        <v>3.04</v>
+        <v>3.038</v>
       </c>
       <c r="K122" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="L122" t="n">
         <v>3.039</v>
       </c>
-      <c r="L122" t="n">
-        <v>3.04</v>
-      </c>
       <c r="M122" t="n">
-        <v>3.04</v>
+        <v>3.038</v>
       </c>
       <c r="N122" t="n">
-        <v>3.04</v>
+        <v>3.039</v>
       </c>
       <c r="O122" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="P122" t="n">
         <v>1.496</v>
       </c>
-      <c r="P122" t="n">
-        <v>1.497</v>
-      </c>
       <c r="Q122" t="n">
-        <v>1.497</v>
+        <v>1.496</v>
       </c>
       <c r="R122" t="n">
-        <v>1.495</v>
+        <v>1.493</v>
       </c>
       <c r="S122" t="n">
-        <v>3.04</v>
+        <v>3.038</v>
       </c>
       <c r="T122" t="n">
-        <v>3.04</v>
+        <v>3.039</v>
       </c>
       <c r="U122" t="n">
-        <v>3.04</v>
+        <v>3.039</v>
       </c>
       <c r="V122" t="n">
-        <v>3.039</v>
+        <v>3.036</v>
       </c>
       <c r="W122" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="X122" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y122" s="1" t="n">
         <v>46315</v>
@@ -14715,25 +14715,25 @@
         <v>1.482</v>
       </c>
       <c r="H123" t="n">
-        <v>1.482</v>
+        <v>1.481</v>
       </c>
       <c r="I123" t="n">
         <v>1.482</v>
       </c>
       <c r="J123" t="n">
-        <v>3.026</v>
+        <v>3.025</v>
       </c>
       <c r="K123" t="n">
+        <v>3.024</v>
+      </c>
+      <c r="L123" t="n">
         <v>3.025</v>
       </c>
-      <c r="L123" t="n">
-        <v>3.026</v>
-      </c>
       <c r="M123" t="n">
-        <v>3.026</v>
+        <v>3.025</v>
       </c>
       <c r="N123" t="n">
-        <v>3.026</v>
+        <v>3.025</v>
       </c>
       <c r="O123" t="n">
         <v>1.482</v>
@@ -14748,16 +14748,16 @@
         <v>1.481</v>
       </c>
       <c r="S123" t="n">
-        <v>3.026</v>
+        <v>3.025</v>
       </c>
       <c r="T123" t="n">
-        <v>3.026</v>
+        <v>3.025</v>
       </c>
       <c r="U123" t="n">
-        <v>3.026</v>
+        <v>3.025</v>
       </c>
       <c r="V123" t="n">
-        <v>3.025</v>
+        <v>3.024</v>
       </c>
       <c r="W123" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         </is>
       </c>
       <c r="X123" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y123" s="1" t="n">
         <v>46315</v>
@@ -14805,34 +14805,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1.485</v>
+        <v>1.484</v>
       </c>
       <c r="F124" t="n">
         <v>1.483</v>
       </c>
       <c r="G124" t="n">
-        <v>1.489</v>
+        <v>1.487</v>
       </c>
       <c r="H124" t="n">
         <v>1.483</v>
       </c>
       <c r="I124" t="n">
-        <v>1.485</v>
+        <v>1.484</v>
       </c>
       <c r="J124" t="n">
-        <v>3.029</v>
+        <v>3.027</v>
       </c>
       <c r="K124" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="L124" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="N124" t="n">
         <v>3.027</v>
-      </c>
-      <c r="L124" t="n">
-        <v>3.033</v>
-      </c>
-      <c r="M124" t="n">
-        <v>3.027</v>
-      </c>
-      <c r="N124" t="n">
-        <v>3.029</v>
       </c>
       <c r="O124" t="n">
         <v>1.483</v>
@@ -14841,22 +14841,22 @@
         <v>1.483</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.489</v>
+        <v>1.487</v>
       </c>
       <c r="R124" t="n">
         <v>1.483</v>
       </c>
       <c r="S124" t="n">
-        <v>3.027</v>
+        <v>3.026</v>
       </c>
       <c r="T124" t="n">
-        <v>3.027</v>
+        <v>3.026</v>
       </c>
       <c r="U124" t="n">
-        <v>3.033</v>
+        <v>3.03</v>
       </c>
       <c r="V124" t="n">
-        <v>3.027</v>
+        <v>3.026</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="X124" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y124" s="1" t="n">
         <v>46315</v>
@@ -14919,19 +14919,19 @@
         <v>1.514</v>
       </c>
       <c r="J125" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="L125" t="n">
         <v>3.057</v>
       </c>
-      <c r="K125" t="n">
+      <c r="M125" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="N125" t="n">
         <v>3.057</v>
-      </c>
-      <c r="L125" t="n">
-        <v>3.058</v>
-      </c>
-      <c r="M125" t="n">
-        <v>3.057</v>
-      </c>
-      <c r="N125" t="n">
-        <v>3.058</v>
       </c>
       <c r="O125" t="n">
         <v>1.513</v>
@@ -14946,24 +14946,24 @@
         <v>1.514</v>
       </c>
       <c r="S125" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="T125" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="U125" t="n">
         <v>3.057</v>
       </c>
-      <c r="T125" t="n">
+      <c r="V125" t="n">
         <v>3.057</v>
       </c>
-      <c r="U125" t="n">
-        <v>3.058</v>
-      </c>
-      <c r="V125" t="n">
-        <v>3.058</v>
-      </c>
       <c r="W125" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="X125" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y125" s="1" t="n">
         <v>46315</v>
@@ -15021,13 +15021,13 @@
         <v>3.159</v>
       </c>
       <c r="K126" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="L126" t="n">
         <v>3.159</v>
       </c>
-      <c r="L126" t="n">
-        <v>3.16</v>
-      </c>
       <c r="M126" t="n">
-        <v>3.159</v>
+        <v>3.158</v>
       </c>
       <c r="N126" t="n">
         <v>3.159</v>
@@ -15045,24 +15045,24 @@
         <v>1.616</v>
       </c>
       <c r="S126" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="T126" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="U126" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="V126" t="n">
         <v>3.159</v>
       </c>
-      <c r="T126" t="n">
-        <v>3.159</v>
-      </c>
-      <c r="U126" t="n">
-        <v>3.159</v>
-      </c>
-      <c r="V126" t="n">
-        <v>3.16</v>
-      </c>
       <c r="W126" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="X126" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y126" s="1" t="n">
         <v>46315</v>
@@ -15102,66 +15102,66 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1.649</v>
+        <v>1.648</v>
       </c>
       <c r="F127" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="H127" t="n">
         <v>1.646</v>
       </c>
-      <c r="G127" t="n">
-        <v>1.653</v>
-      </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>1.648</v>
       </c>
-      <c r="I127" t="n">
-        <v>1.65</v>
-      </c>
       <c r="J127" t="n">
-        <v>3.193</v>
+        <v>3.191</v>
       </c>
       <c r="K127" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3.189</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3.191</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="S127" t="n">
         <v>3.19</v>
       </c>
-      <c r="L127" t="n">
-        <v>3.197</v>
-      </c>
-      <c r="M127" t="n">
-        <v>3.191</v>
-      </c>
-      <c r="N127" t="n">
+      <c r="T127" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U127" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="V127" t="n">
         <v>3.194</v>
       </c>
-      <c r="O127" t="n">
-        <v>1.648</v>
-      </c>
-      <c r="P127" t="n">
-        <v>1.649</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>1.646</v>
-      </c>
-      <c r="R127" t="n">
-        <v>1.653</v>
-      </c>
-      <c r="S127" t="n">
-        <v>3.192</v>
-      </c>
-      <c r="T127" t="n">
-        <v>3.193</v>
-      </c>
-      <c r="U127" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="V127" t="n">
-        <v>3.197</v>
-      </c>
       <c r="W127" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="X127" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="Y127" s="1" t="n">
         <v>46315</v>
@@ -15216,19 +15216,19 @@
         <v>5.58</v>
       </c>
       <c r="J128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="K128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="L128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="M128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="N128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="O128" t="n">
         <v>5.58</v>
@@ -15243,16 +15243,16 @@
         <v>5.58</v>
       </c>
       <c r="S128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="T128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="U128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="V128" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="X128" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y128" s="1" t="n">
         <v>46315</v>
@@ -15300,7 +15300,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5.584</v>
+        <v>5.583</v>
       </c>
       <c r="F129" t="n">
         <v>5.583</v>
@@ -15312,7 +15312,7 @@
         <v>5.583</v>
       </c>
       <c r="I129" t="n">
-        <v>5.584</v>
+        <v>5.583</v>
       </c>
       <c r="J129" t="n">
         <v>7.86</v>
@@ -15336,7 +15336,7 @@
         <v>5.584</v>
       </c>
       <c r="Q129" t="n">
-        <v>5.584</v>
+        <v>5.583</v>
       </c>
       <c r="R129" t="n">
         <v>5.583</v>
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="X129" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y129" s="1" t="n">
         <v>46315</v>
@@ -15402,7 +15402,7 @@
         <v>5.593</v>
       </c>
       <c r="F130" t="n">
-        <v>5.592</v>
+        <v>5.59</v>
       </c>
       <c r="G130" t="n">
         <v>5.594</v>
@@ -15414,16 +15414,16 @@
         <v>5.594</v>
       </c>
       <c r="J130" t="n">
+        <v>7.869</v>
+      </c>
+      <c r="K130" t="n">
+        <v>7.866</v>
+      </c>
+      <c r="L130" t="n">
         <v>7.87</v>
       </c>
-      <c r="K130" t="n">
-        <v>7.868</v>
-      </c>
-      <c r="L130" t="n">
-        <v>7.871</v>
-      </c>
       <c r="M130" t="n">
-        <v>7.87</v>
+        <v>7.869</v>
       </c>
       <c r="N130" t="n">
         <v>7.87</v>
@@ -15438,19 +15438,19 @@
         <v>5.594</v>
       </c>
       <c r="R130" t="n">
-        <v>5.592</v>
+        <v>5.59</v>
       </c>
       <c r="S130" t="n">
         <v>7.87</v>
       </c>
       <c r="T130" t="n">
-        <v>7.871</v>
+        <v>7.87</v>
       </c>
       <c r="U130" t="n">
         <v>7.87</v>
       </c>
       <c r="V130" t="n">
-        <v>7.868</v>
+        <v>7.866</v>
       </c>
       <c r="W130" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="X130" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y130" s="1" t="n">
         <v>46315</v>
@@ -15498,7 +15498,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5.591</v>
+        <v>5.59</v>
       </c>
       <c r="F131" t="n">
         <v>5.583</v>
@@ -15507,7 +15507,7 @@
         <v>5.594</v>
       </c>
       <c r="H131" t="n">
-        <v>5.59</v>
+        <v>5.588</v>
       </c>
       <c r="I131" t="n">
         <v>5.594</v>
@@ -15522,10 +15522,10 @@
         <v>7.871</v>
       </c>
       <c r="M131" t="n">
-        <v>7.866</v>
+        <v>7.865</v>
       </c>
       <c r="N131" t="n">
-        <v>7.871</v>
+        <v>7.87</v>
       </c>
       <c r="O131" t="n">
         <v>5.594</v>
@@ -15534,19 +15534,19 @@
         <v>5.594</v>
       </c>
       <c r="Q131" t="n">
-        <v>5.592</v>
+        <v>5.59</v>
       </c>
       <c r="R131" t="n">
         <v>5.583</v>
       </c>
       <c r="S131" t="n">
-        <v>7.871</v>
+        <v>7.87</v>
       </c>
       <c r="T131" t="n">
         <v>7.871</v>
       </c>
       <c r="U131" t="n">
-        <v>7.868</v>
+        <v>7.866</v>
       </c>
       <c r="V131" t="n">
         <v>7.86</v>
@@ -15557,7 +15557,7 @@
         </is>
       </c>
       <c r="X131" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y131" s="1" t="n">
         <v>46315</v>
@@ -15612,13 +15612,13 @@
         <v>5.594</v>
       </c>
       <c r="J132" t="n">
-        <v>7.865</v>
+        <v>7.864</v>
       </c>
       <c r="K132" t="n">
         <v>7.858</v>
       </c>
       <c r="L132" t="n">
-        <v>7.871</v>
+        <v>7.87</v>
       </c>
       <c r="M132" t="n">
         <v>7.859</v>
@@ -15642,7 +15642,7 @@
         <v>7.87</v>
       </c>
       <c r="T132" t="n">
-        <v>7.871</v>
+        <v>7.87</v>
       </c>
       <c r="U132" t="n">
         <v>7.859</v>
@@ -15656,7 +15656,7 @@
         </is>
       </c>
       <c r="X132" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y132" s="1" t="n">
         <v>46315</v>
@@ -15711,7 +15711,7 @@
         <v>5.582</v>
       </c>
       <c r="J133" t="n">
-        <v>7.858</v>
+        <v>7.857</v>
       </c>
       <c r="K133" t="n">
         <v>7.855</v>
@@ -15723,7 +15723,7 @@
         <v>7.857</v>
       </c>
       <c r="N133" t="n">
-        <v>7.859</v>
+        <v>7.858</v>
       </c>
       <c r="O133" t="n">
         <v>5.582</v>
@@ -15747,7 +15747,7 @@
         <v>7.855</v>
       </c>
       <c r="V133" t="n">
-        <v>7.858</v>
+        <v>7.857</v>
       </c>
       <c r="W133" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         </is>
       </c>
       <c r="X133" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y133" s="1" t="n">
         <v>46315</v>
@@ -15813,19 +15813,19 @@
         <v>7.849</v>
       </c>
       <c r="K134" t="n">
-        <v>7.834</v>
+        <v>7.833</v>
       </c>
       <c r="L134" t="n">
         <v>7.86</v>
       </c>
       <c r="M134" t="n">
-        <v>7.844</v>
+        <v>7.843</v>
       </c>
       <c r="N134" t="n">
         <v>7.856</v>
       </c>
       <c r="O134" t="n">
-        <v>5.571</v>
+        <v>5.57</v>
       </c>
       <c r="P134" t="n">
         <v>5.579</v>
@@ -15843,7 +15843,7 @@
         <v>7.855</v>
       </c>
       <c r="U134" t="n">
-        <v>7.834</v>
+        <v>7.833</v>
       </c>
       <c r="V134" t="n">
         <v>7.86</v>
@@ -15854,7 +15854,7 @@
         </is>
       </c>
       <c r="X134" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="Y134" s="1" t="n">
         <v>46315</v>
@@ -16680,7 +16680,7 @@
         <v>3.229</v>
       </c>
       <c r="F3" t="n">
-        <v>3.239</v>
+        <v>3.24</v>
       </c>
       <c r="G3" t="n">
         <v>3.264</v>
@@ -16708,16 +16708,16 @@
         <v>3.797</v>
       </c>
       <c r="E4" t="n">
-        <v>3.868</v>
+        <v>3.867</v>
       </c>
       <c r="F4" t="n">
-        <v>3.866</v>
+        <v>3.865</v>
       </c>
       <c r="G4" t="n">
         <v>3.829</v>
       </c>
       <c r="H4" t="n">
-        <v>3.801</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
         <v>3.771</v>
@@ -16736,22 +16736,22 @@
         <v>6.975</v>
       </c>
       <c r="D5" t="n">
-        <v>6.899</v>
+        <v>6.897</v>
       </c>
       <c r="E5" t="n">
-        <v>6.709</v>
+        <v>6.712</v>
       </c>
       <c r="F5" t="n">
-        <v>6.647</v>
+        <v>6.65</v>
       </c>
       <c r="G5" t="n">
-        <v>6.532</v>
+        <v>6.53</v>
       </c>
       <c r="H5" t="n">
-        <v>6.415</v>
+        <v>6.417</v>
       </c>
       <c r="I5" t="n">
-        <v>6.274</v>
+        <v>6.275</v>
       </c>
     </row>
     <row r="6">
@@ -16773,16 +16773,16 @@
         <v>4.266</v>
       </c>
       <c r="F6" t="n">
-        <v>4.376</v>
+        <v>4.374</v>
       </c>
       <c r="G6" t="n">
-        <v>4.409</v>
+        <v>4.408</v>
       </c>
       <c r="H6" t="n">
-        <v>4.228</v>
+        <v>4.225</v>
       </c>
       <c r="I6" t="n">
-        <v>3.884</v>
+        <v>3.881</v>
       </c>
     </row>
     <row r="7">
@@ -16832,13 +16832,13 @@
         <v>6.348</v>
       </c>
       <c r="E8" t="n">
-        <v>6.283</v>
+        <v>6.282</v>
       </c>
       <c r="F8" t="n">
-        <v>6.225</v>
+        <v>6.224</v>
       </c>
       <c r="G8" t="n">
-        <v>6.107</v>
+        <v>6.108</v>
       </c>
       <c r="H8" t="n">
         <v>6.047</v>
@@ -16860,22 +16860,22 @@
         <v>5.103</v>
       </c>
       <c r="D9" t="n">
-        <v>5.112</v>
+        <v>5.119</v>
       </c>
       <c r="E9" t="n">
-        <v>5.144</v>
+        <v>5.143</v>
       </c>
       <c r="F9" t="n">
-        <v>5.112</v>
+        <v>5.12</v>
       </c>
       <c r="G9" t="n">
-        <v>5.093</v>
+        <v>5.098</v>
       </c>
       <c r="H9" t="n">
-        <v>5.158</v>
+        <v>5.162</v>
       </c>
       <c r="I9" t="n">
-        <v>5.351</v>
+        <v>5.356</v>
       </c>
     </row>
     <row r="10">
@@ -16894,19 +16894,19 @@
         <v>4.614</v>
       </c>
       <c r="E10" t="n">
-        <v>4.628</v>
+        <v>4.627</v>
       </c>
       <c r="F10" t="n">
-        <v>4.682</v>
+        <v>4.681</v>
       </c>
       <c r="G10" t="n">
-        <v>4.743</v>
+        <v>4.742</v>
       </c>
       <c r="H10" t="n">
-        <v>4.794</v>
+        <v>4.791</v>
       </c>
       <c r="I10" t="n">
-        <v>4.834</v>
+        <v>4.833</v>
       </c>
     </row>
     <row r="11">
@@ -16922,7 +16922,7 @@
         <v>9.061999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>9.111000000000001</v>
+        <v>9.108000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>9.138999999999999</v>
@@ -16953,22 +16953,22 @@
         <v>3.478</v>
       </c>
       <c r="D12" t="n">
-        <v>3.585</v>
+        <v>3.586</v>
       </c>
       <c r="E12" t="n">
-        <v>3.612</v>
+        <v>3.611</v>
       </c>
       <c r="F12" t="n">
-        <v>3.557</v>
+        <v>3.555</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36</v>
+        <v>3.359</v>
       </c>
       <c r="H12" t="n">
-        <v>2.974</v>
+        <v>2.973</v>
       </c>
       <c r="I12" t="n">
-        <v>2.602</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="13">
@@ -16984,19 +16984,19 @@
         <v>5.19</v>
       </c>
       <c r="D13" t="n">
-        <v>5.174</v>
+        <v>5.17</v>
       </c>
       <c r="E13" t="n">
-        <v>5.154</v>
+        <v>5.15</v>
       </c>
       <c r="F13" t="n">
-        <v>5.161</v>
+        <v>5.158</v>
       </c>
       <c r="G13" t="n">
-        <v>5.217</v>
+        <v>5.215</v>
       </c>
       <c r="H13" t="n">
-        <v>5.253</v>
+        <v>5.252</v>
       </c>
       <c r="I13" t="n">
         <v>5.292</v>
@@ -17046,22 +17046,22 @@
         <v>4.568</v>
       </c>
       <c r="D15" t="n">
-        <v>4.592</v>
+        <v>4.593</v>
       </c>
       <c r="E15" t="n">
-        <v>4.665</v>
+        <v>4.666</v>
       </c>
       <c r="F15" t="n">
-        <v>4.755</v>
+        <v>4.757</v>
       </c>
       <c r="G15" t="n">
-        <v>4.887</v>
+        <v>4.888</v>
       </c>
       <c r="H15" t="n">
-        <v>5.089</v>
+        <v>5.09</v>
       </c>
       <c r="I15" t="n">
-        <v>5.438</v>
+        <v>5.442</v>
       </c>
     </row>
     <row r="16">
@@ -17077,10 +17077,10 @@
         <v>5.445</v>
       </c>
       <c r="D16" t="n">
-        <v>5.478</v>
+        <v>5.477</v>
       </c>
       <c r="E16" t="n">
-        <v>5.508</v>
+        <v>5.509</v>
       </c>
       <c r="F16" t="n">
         <v>5.543</v>
@@ -17089,7 +17089,7 @@
         <v>5.594</v>
       </c>
       <c r="H16" t="n">
-        <v>5.645</v>
+        <v>5.641</v>
       </c>
       <c r="I16" t="n">
         <v>5.789</v>
@@ -17105,25 +17105,25 @@
         <v>9037738</v>
       </c>
       <c r="C17" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="D17" t="n">
-        <v>4.451</v>
+        <v>4.701</v>
       </c>
       <c r="E17" t="n">
-        <v>4.428</v>
+        <v>4.678</v>
       </c>
       <c r="F17" t="n">
-        <v>4.36</v>
+        <v>4.61</v>
       </c>
       <c r="G17" t="n">
-        <v>4.202</v>
+        <v>4.452</v>
       </c>
       <c r="H17" t="n">
-        <v>4.028</v>
+        <v>4.278</v>
       </c>
       <c r="I17" t="n">
-        <v>3.719</v>
+        <v>3.968</v>
       </c>
     </row>
     <row r="18">
@@ -17139,10 +17139,10 @@
         <v>1.95</v>
       </c>
       <c r="D18" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="E18" t="n">
-        <v>2.023</v>
+        <v>2.021</v>
       </c>
       <c r="F18" t="n">
         <v>2.097</v>
@@ -17151,10 +17151,10 @@
         <v>2.114</v>
       </c>
       <c r="H18" t="n">
-        <v>2.13</v>
+        <v>2.129</v>
       </c>
       <c r="I18" t="n">
-        <v>2.167</v>
+        <v>2.166</v>
       </c>
     </row>
     <row r="19">
@@ -17170,13 +17170,13 @@
         <v>1.51</v>
       </c>
       <c r="D19" t="n">
-        <v>1.496</v>
+        <v>1.495</v>
       </c>
       <c r="E19" t="n">
         <v>1.482</v>
       </c>
       <c r="F19" t="n">
-        <v>1.485</v>
+        <v>1.484</v>
       </c>
       <c r="G19" t="n">
         <v>1.513</v>
@@ -17185,7 +17185,7 @@
         <v>1.615</v>
       </c>
       <c r="I19" t="n">
-        <v>1.649</v>
+        <v>1.648</v>
       </c>
     </row>
     <row r="20">
@@ -17201,13 +17201,13 @@
         <v>5.58</v>
       </c>
       <c r="D20" t="n">
-        <v>5.584</v>
+        <v>5.583</v>
       </c>
       <c r="E20" t="n">
         <v>5.593</v>
       </c>
       <c r="F20" t="n">
-        <v>5.591</v>
+        <v>5.59</v>
       </c>
       <c r="G20" t="n">
         <v>5.588</v>
@@ -17345,10 +17345,10 @@
         <v>5.445</v>
       </c>
       <c r="F2" t="n">
-        <v>7.401</v>
+        <v>7.399</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.956</v>
+        <v>-1.954</v>
       </c>
       <c r="H2" t="n">
         <v>5.445</v>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Offset alto: -1.96 m. Revisar estación.</t>
+          <t>Offset alto: -1.95 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -17389,10 +17389,10 @@
         <v>3.23</v>
       </c>
       <c r="F3" t="n">
-        <v>5.57</v>
+        <v>5.569</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.34</v>
+        <v>-2.339</v>
       </c>
       <c r="H3" t="n">
         <v>3.23</v>
@@ -17433,10 +17433,10 @@
         <v>5.58</v>
       </c>
       <c r="F4" t="n">
-        <v>7.857</v>
+        <v>7.856</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.277</v>
+        <v>-2.276</v>
       </c>
       <c r="H4" t="n">
         <v>5.58</v>
@@ -17477,10 +17477,10 @@
         <v>3.478</v>
       </c>
       <c r="F5" t="n">
-        <v>5.391</v>
+        <v>5.39</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.913</v>
+        <v>-1.912</v>
       </c>
       <c r="H5" t="n">
         <v>3.478</v>
@@ -17518,16 +17518,16 @@
         <v>46315</v>
       </c>
       <c r="E6" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="F6" t="n">
         <v>7.007</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.567</v>
+        <v>-2.317</v>
       </c>
       <c r="H6" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Offset alto: -2.57 m. Revisar estación.</t>
+          <t>Offset alto: -2.32 m. Revisar estación.</t>
         </is>
       </c>
     </row>
@@ -17565,10 +17565,10 @@
         <v>4.1</v>
       </c>
       <c r="F7" t="n">
-        <v>5.339</v>
+        <v>5.336</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.239</v>
+        <v>-1.236</v>
       </c>
       <c r="H7" t="n">
         <v>4.1</v>
@@ -17609,10 +17609,10 @@
         <v>1.51</v>
       </c>
       <c r="F8" t="n">
-        <v>3.054</v>
+        <v>3.053</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.544</v>
+        <v>-1.543</v>
       </c>
       <c r="H8" t="n">
         <v>1.51</v>
@@ -17656,7 +17656,7 @@
         <v>10.829</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.767</v>
+        <v>-1.766</v>
       </c>
       <c r="H9" t="n">
         <v>9.061999999999999</v>
@@ -17697,10 +17697,10 @@
         <v>1.95</v>
       </c>
       <c r="F10" t="n">
-        <v>5.74</v>
+        <v>5.739</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.79</v>
+        <v>-3.789</v>
       </c>
       <c r="H10" t="n">
         <v>1.95</v>
@@ -17741,7 +17741,7 @@
         <v>3.618</v>
       </c>
       <c r="F11" t="n">
-        <v>5.586</v>
+        <v>5.585</v>
       </c>
       <c r="G11" t="n">
         <v>-1.968</v>
@@ -17785,10 +17785,10 @@
         <v>4.568</v>
       </c>
       <c r="F12" t="n">
-        <v>3.626</v>
+        <v>3.627</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>4.568</v>
@@ -18045,10 +18045,10 @@
         <v>5.103</v>
       </c>
       <c r="F18" t="n">
-        <v>6.14</v>
+        <v>6.132</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.037</v>
+        <v>-1.029</v>
       </c>
       <c r="H18" t="n">
         <v>5.103</v>
@@ -18173,10 +18173,10 @@
         <v>6.975</v>
       </c>
       <c r="F21" t="n">
-        <v>9.156000000000001</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.181</v>
+        <v>-2.174</v>
       </c>
       <c r="H21" t="n">
         <v>6.975</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Offset alto: -2.18 m. Revisar estación.</t>
+          <t>Offset alto: -2.17 m. Revisar estación.</t>
         </is>
       </c>
     </row>
